--- a/minio-report-tracker/xlxs/dev01.xlsx
+++ b/minio-report-tracker/xlxs/dev01.xlsx
@@ -648,7 +648,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI10"/>
+  <dimension ref="A1:AR10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -670,22 +670,31 @@
     <col width="4" customWidth="1" min="17" max="17"/>
     <col width="2" customWidth="1" min="18" max="18"/>
     <col width="15" customWidth="1" min="19" max="19"/>
-    <col width="10" customWidth="1" min="20" max="20"/>
+    <col width="16" customWidth="1" min="20" max="20"/>
     <col width="6" customWidth="1" min="21" max="21"/>
-    <col width="6" customWidth="1" min="22" max="22"/>
+    <col width="5" customWidth="1" min="22" max="22"/>
     <col width="5" customWidth="1" min="23" max="23"/>
     <col width="5" customWidth="1" min="24" max="24"/>
-    <col width="5" customWidth="1" min="25" max="25"/>
-    <col width="5" customWidth="1" min="26" max="26"/>
+    <col width="4" customWidth="1" min="25" max="25"/>
+    <col width="4" customWidth="1" min="26" max="26"/>
     <col width="2" customWidth="1" min="27" max="27"/>
     <col width="15" customWidth="1" min="28" max="28"/>
-    <col width="16" customWidth="1" min="29" max="29"/>
-    <col width="5" customWidth="1" min="30" max="30"/>
-    <col width="5" customWidth="1" min="31" max="31"/>
+    <col width="10" customWidth="1" min="29" max="29"/>
+    <col width="6" customWidth="1" min="30" max="30"/>
+    <col width="6" customWidth="1" min="31" max="31"/>
     <col width="5" customWidth="1" min="32" max="32"/>
     <col width="5" customWidth="1" min="33" max="33"/>
     <col width="5" customWidth="1" min="34" max="34"/>
     <col width="5" customWidth="1" min="35" max="35"/>
+    <col width="2" customWidth="1" min="36" max="36"/>
+    <col width="15" customWidth="1" min="37" max="37"/>
+    <col width="16" customWidth="1" min="38" max="38"/>
+    <col width="5" customWidth="1" min="39" max="39"/>
+    <col width="5" customWidth="1" min="40" max="40"/>
+    <col width="5" customWidth="1" min="41" max="41"/>
+    <col width="5" customWidth="1" min="42" max="42"/>
+    <col width="5" customWidth="1" min="43" max="43"/>
+    <col width="5" customWidth="1" min="44" max="44"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -849,164 +858,244 @@
           <t>KI</t>
         </is>
       </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>Module</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>KI</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>01-April-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>494</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>31-March-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>114</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>161</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>323</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>30-March-2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>113</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>161</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>324</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>27-March-2026</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>597</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="AH2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AI2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AK2" t="inlineStr">
         <is>
           <t>26-March-2026</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AL2" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AM2" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
+      <c r="AN2" t="inlineStr">
         <is>
           <t>335</t>
         </is>
       </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AH2" t="inlineStr">
+      <c r="AQ2" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="AI2" t="inlineStr">
+      <c r="AR2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1015,160 +1104,200 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>01-April-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>231</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>31-March-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>30-March-2026</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
         <is>
           <t>27-March-2026</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>216</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="AF3" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="AG3" t="inlineStr">
         <is>
           <t>63</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
+      <c r="AH3" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="AI3" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AK3" t="inlineStr">
         <is>
           <t>26-March-2026</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
+      <c r="AL3" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="AD3" t="inlineStr">
+      <c r="AM3" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="AE3" t="inlineStr">
+      <c r="AN3" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="AI3" t="inlineStr">
+      <c r="AR3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1177,160 +1306,200 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>01-April-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>930</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>31-March-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
         <is>
           <t>30-March-2026</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
         <is>
           <t>27-March-2026</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="AE4" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
         <is>
           <t>26-March-2026</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
+      <c r="AL4" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="AD4" t="inlineStr">
+      <c r="AM4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="AE4" t="inlineStr">
+      <c r="AN4" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr">
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1339,160 +1508,200 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>01-April-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>31-March-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
         <is>
           <t>30-March-2026</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
         <is>
           <t>27-March-2026</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>209</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="AE5" t="inlineStr">
         <is>
           <t>163</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
+      <c r="AH5" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
+      <c r="AI5" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AK5" t="inlineStr">
         <is>
           <t>26-March-2026</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
+      <c r="AL5" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="AD5" t="inlineStr">
+      <c r="AM5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="AE5" t="inlineStr">
+      <c r="AN5" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr">
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ5" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="AI5" t="inlineStr">
+      <c r="AR5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1501,144 +1710,184 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>01-April-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>930</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>31-March-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
         <is>
           <t>30-March-2026</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S6" t="n">
-        <v/>
-      </c>
-      <c r="T6" t="n">
-        <v/>
-      </c>
-      <c r="U6" t="n">
-        <v/>
-      </c>
-      <c r="V6" t="n">
-        <v/>
-      </c>
-      <c r="W6" t="n">
-        <v/>
-      </c>
-      <c r="X6" t="n">
-        <v/>
-      </c>
-      <c r="Y6" t="n">
-        <v/>
-      </c>
-      <c r="Z6" t="n">
-        <v/>
-      </c>
-      <c r="AB6" t="inlineStr">
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB6" t="n">
+        <v/>
+      </c>
+      <c r="AC6" t="n">
+        <v/>
+      </c>
+      <c r="AD6" t="n">
+        <v/>
+      </c>
+      <c r="AE6" t="n">
+        <v/>
+      </c>
+      <c r="AF6" t="n">
+        <v/>
+      </c>
+      <c r="AG6" t="n">
+        <v/>
+      </c>
+      <c r="AH6" t="n">
+        <v/>
+      </c>
+      <c r="AI6" t="n">
+        <v/>
+      </c>
+      <c r="AK6" t="inlineStr">
         <is>
           <t>26-March-2026</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
+      <c r="AL6" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="AD6" t="inlineStr">
+      <c r="AM6" t="inlineStr">
         <is>
           <t>509</t>
         </is>
       </c>
-      <c r="AE6" t="inlineStr">
+      <c r="AN6" t="inlineStr">
         <is>
           <t>496</t>
         </is>
       </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG6" t="inlineStr">
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
         <is>
           <t>12</t>
         </is>
@@ -1647,108 +1896,124 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>01-April-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>509</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>495</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>31-March-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>509</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>496</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>30-March-2026</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>509</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>496</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="S7" t="n">
-        <v/>
-      </c>
-      <c r="T7" t="n">
-        <v/>
-      </c>
-      <c r="U7" t="n">
-        <v/>
-      </c>
-      <c r="V7" t="n">
-        <v/>
-      </c>
-      <c r="W7" t="n">
-        <v/>
-      </c>
-      <c r="X7" t="n">
-        <v/>
-      </c>
-      <c r="Y7" t="n">
-        <v/>
-      </c>
-      <c r="Z7" t="n">
-        <v/>
-      </c>
       <c r="AB7" t="n">
         <v/>
       </c>
@@ -1771,114 +2036,154 @@
         <v/>
       </c>
       <c r="AI7" t="n">
+        <v/>
+      </c>
+      <c r="AK7" t="n">
+        <v/>
+      </c>
+      <c r="AL7" t="n">
+        <v/>
+      </c>
+      <c r="AM7" t="n">
+        <v/>
+      </c>
+      <c r="AN7" t="n">
+        <v/>
+      </c>
+      <c r="AO7" t="n">
+        <v/>
+      </c>
+      <c r="AP7" t="n">
+        <v/>
+      </c>
+      <c r="AQ7" t="n">
+        <v/>
+      </c>
+      <c r="AR7" t="n">
         <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>01-April-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>31-March-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>30-March-2026</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="S8" t="n">
-        <v/>
-      </c>
-      <c r="T8" t="n">
-        <v/>
-      </c>
-      <c r="U8" t="n">
-        <v/>
-      </c>
-      <c r="V8" t="n">
-        <v/>
-      </c>
-      <c r="W8" t="n">
-        <v/>
-      </c>
-      <c r="X8" t="n">
-        <v/>
-      </c>
-      <c r="Y8" t="n">
-        <v/>
-      </c>
-      <c r="Z8" t="n">
-        <v/>
-      </c>
       <c r="AB8" t="n">
         <v/>
       </c>
@@ -1901,113 +2206,153 @@
         <v/>
       </c>
       <c r="AI8" t="n">
+        <v/>
+      </c>
+      <c r="AK8" t="n">
+        <v/>
+      </c>
+      <c r="AL8" t="n">
+        <v/>
+      </c>
+      <c r="AM8" t="n">
+        <v/>
+      </c>
+      <c r="AN8" t="n">
+        <v/>
+      </c>
+      <c r="AO8" t="n">
+        <v/>
+      </c>
+      <c r="AP8" t="n">
+        <v/>
+      </c>
+      <c r="AQ8" t="n">
+        <v/>
+      </c>
+      <c r="AR8" t="n">
         <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>01-April-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>resident</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1142</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>163</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>510</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>469</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>31-March-2026</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>211</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>211</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>720</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
         <is>
           <t>30-March-2026</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>211</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>211</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="X9" t="inlineStr">
         <is>
           <t>720</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S9" t="n">
-        <v/>
-      </c>
-      <c r="T9" t="n">
-        <v/>
-      </c>
-      <c r="U9" t="n">
-        <v/>
-      </c>
-      <c r="V9" t="n">
-        <v/>
-      </c>
-      <c r="W9" t="n">
-        <v/>
-      </c>
-      <c r="X9" t="n">
-        <v/>
-      </c>
-      <c r="Y9" t="n">
-        <v/>
-      </c>
-      <c r="Z9" t="n">
-        <v/>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="AB9" t="n">
         <v/>
@@ -2031,114 +2376,154 @@
         <v/>
       </c>
       <c r="AI9" t="n">
+        <v/>
+      </c>
+      <c r="AK9" t="n">
+        <v/>
+      </c>
+      <c r="AL9" t="n">
+        <v/>
+      </c>
+      <c r="AM9" t="n">
+        <v/>
+      </c>
+      <c r="AN9" t="n">
+        <v/>
+      </c>
+      <c r="AO9" t="n">
+        <v/>
+      </c>
+      <c r="AP9" t="n">
+        <v/>
+      </c>
+      <c r="AQ9" t="n">
+        <v/>
+      </c>
+      <c r="AR9" t="n">
         <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>01-April-2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>dsl</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>31-March-2026</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>209</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>109</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
         <is>
           <t>70</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>30-March-2026</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>209</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>106</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
         <is>
           <t>73</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="S10" t="n">
-        <v/>
-      </c>
-      <c r="T10" t="n">
-        <v/>
-      </c>
-      <c r="U10" t="n">
-        <v/>
-      </c>
-      <c r="V10" t="n">
-        <v/>
-      </c>
-      <c r="W10" t="n">
-        <v/>
-      </c>
-      <c r="X10" t="n">
-        <v/>
-      </c>
-      <c r="Y10" t="n">
-        <v/>
-      </c>
-      <c r="Z10" t="n">
-        <v/>
-      </c>
       <c r="AB10" t="n">
         <v/>
       </c>
@@ -2161,6 +2546,30 @@
         <v/>
       </c>
       <c r="AI10" t="n">
+        <v/>
+      </c>
+      <c r="AK10" t="n">
+        <v/>
+      </c>
+      <c r="AL10" t="n">
+        <v/>
+      </c>
+      <c r="AM10" t="n">
+        <v/>
+      </c>
+      <c r="AN10" t="n">
+        <v/>
+      </c>
+      <c r="AO10" t="n">
+        <v/>
+      </c>
+      <c r="AP10" t="n">
+        <v/>
+      </c>
+      <c r="AQ10" t="n">
+        <v/>
+      </c>
+      <c r="AR10" t="n">
         <v/>
       </c>
     </row>

--- a/minio-report-tracker/xlxs/dev01.xlsx
+++ b/minio-report-tracker/xlxs/dev01.xlsx
@@ -654,9 +654,9 @@
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="6" customWidth="1" min="3" max="3"/>
-    <col width="5" customWidth="1" min="4" max="4"/>
-    <col width="5" customWidth="1" min="5" max="5"/>
-    <col width="5" customWidth="1" min="6" max="6"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="3" customWidth="1" min="5" max="5"/>
+    <col width="4" customWidth="1" min="6" max="6"/>
     <col width="4" customWidth="1" min="7" max="7"/>
     <col width="4" customWidth="1" min="8" max="8"/>
     <col width="2" customWidth="1" min="9" max="9"/>
@@ -679,18 +679,18 @@
     <col width="4" customWidth="1" min="26" max="26"/>
     <col width="2" customWidth="1" min="27" max="27"/>
     <col width="15" customWidth="1" min="28" max="28"/>
-    <col width="10" customWidth="1" min="29" max="29"/>
+    <col width="16" customWidth="1" min="29" max="29"/>
     <col width="6" customWidth="1" min="30" max="30"/>
-    <col width="6" customWidth="1" min="31" max="31"/>
+    <col width="5" customWidth="1" min="31" max="31"/>
     <col width="5" customWidth="1" min="32" max="32"/>
     <col width="5" customWidth="1" min="33" max="33"/>
-    <col width="5" customWidth="1" min="34" max="34"/>
-    <col width="5" customWidth="1" min="35" max="35"/>
+    <col width="4" customWidth="1" min="34" max="34"/>
+    <col width="4" customWidth="1" min="35" max="35"/>
     <col width="2" customWidth="1" min="36" max="36"/>
     <col width="15" customWidth="1" min="37" max="37"/>
-    <col width="16" customWidth="1" min="38" max="38"/>
-    <col width="5" customWidth="1" min="39" max="39"/>
-    <col width="5" customWidth="1" min="40" max="40"/>
+    <col width="10" customWidth="1" min="38" max="38"/>
+    <col width="6" customWidth="1" min="39" max="39"/>
+    <col width="6" customWidth="1" min="40" max="40"/>
     <col width="5" customWidth="1" min="41" max="41"/>
     <col width="5" customWidth="1" min="42" max="42"/>
     <col width="5" customWidth="1" min="43" max="43"/>
@@ -902,588 +902,588 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>02-April-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>597</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>01-April-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>494</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>69</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>31-March-2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>114</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>161</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>323</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>30-March-2026</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>113</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
         <is>
           <t>161</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="AG2" t="inlineStr">
         <is>
           <t>324</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="AH2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AI2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AK2" t="inlineStr">
         <is>
           <t>27-March-2026</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AL2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AM2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
+      <c r="AN2" t="inlineStr">
         <is>
           <t>597</t>
         </is>
       </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AH2" t="inlineStr">
+      <c r="AQ2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AI2" t="inlineStr">
+      <c r="AR2" t="inlineStr">
         <is>
           <t>9</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>26-March-2026</t>
-        </is>
-      </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>idrepo</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>414</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>335</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>02-April-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>333</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>01-April-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>73</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>231</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>31-March-2026</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
         <is>
           <t>30-March-2026</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
         <is>
           <t>27-March-2026</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
+      <c r="AL3" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="AD3" t="inlineStr">
+      <c r="AM3" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="AE3" t="inlineStr">
+      <c r="AN3" t="inlineStr">
         <is>
           <t>216</t>
         </is>
       </c>
-      <c r="AF3" t="inlineStr">
+      <c r="AO3" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AG3" t="inlineStr">
+      <c r="AP3" t="inlineStr">
         <is>
           <t>63</t>
         </is>
       </c>
-      <c r="AH3" t="inlineStr">
+      <c r="AQ3" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AI3" t="inlineStr">
+      <c r="AR3" t="inlineStr">
         <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>26-March-2026</t>
-        </is>
-      </c>
-      <c r="AL3" t="inlineStr">
-        <is>
-          <t>masterdata-ara</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>930</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AP3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ3" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>02-April-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>930</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>01-April-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
         <is>
           <t>31-March-2026</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
         <is>
           <t>30-March-2026</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="AE4" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
         <is>
           <t>27-March-2026</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
+      <c r="AL4" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="AD4" t="inlineStr">
+      <c r="AM4" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="AE4" t="inlineStr">
+      <c r="AN4" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>26-March-2026</t>
-        </is>
-      </c>
-      <c r="AL4" t="inlineStr">
-        <is>
-          <t>masterdata-eng</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>944</t>
-        </is>
-      </c>
       <c r="AO4" t="inlineStr">
         <is>
           <t>0</t>
@@ -1491,7 +1491,7 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
@@ -1508,535 +1508,551 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>02-April-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>01-April-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
         <is>
           <t>31-March-2026</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
         <is>
           <t>30-March-2026</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="AE5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
         <is>
           <t>27-March-2026</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
+      <c r="AL5" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="AD5" t="inlineStr">
+      <c r="AM5" t="inlineStr">
         <is>
           <t>209</t>
         </is>
       </c>
-      <c r="AE5" t="inlineStr">
+      <c r="AN5" t="inlineStr">
         <is>
           <t>163</t>
         </is>
       </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG5" t="inlineStr">
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="AH5" t="inlineStr">
+      <c r="AQ5" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="AI5" t="inlineStr">
+      <c r="AR5" t="inlineStr">
         <is>
           <t>20</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>26-March-2026</t>
-        </is>
-      </c>
-      <c r="AL5" t="inlineStr">
-        <is>
-          <t>masterdata-fra</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>930</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AP5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ5" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>02-April-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>930</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>01-April-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
         <is>
           <t>31-March-2026</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
         <is>
           <t>30-March-2026</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="AE6" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB6" t="n">
-        <v/>
-      </c>
-      <c r="AC6" t="n">
-        <v/>
-      </c>
-      <c r="AD6" t="n">
-        <v/>
-      </c>
-      <c r="AE6" t="n">
-        <v/>
-      </c>
-      <c r="AF6" t="n">
-        <v/>
-      </c>
-      <c r="AG6" t="n">
-        <v/>
-      </c>
-      <c r="AH6" t="n">
-        <v/>
-      </c>
-      <c r="AI6" t="n">
-        <v/>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>26-March-2026</t>
-        </is>
-      </c>
-      <c r="AL6" t="inlineStr">
-        <is>
-          <t>partner</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>509</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>496</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AP6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AQ6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK6" t="n">
+        <v/>
+      </c>
+      <c r="AL6" t="n">
+        <v/>
+      </c>
+      <c r="AM6" t="n">
+        <v/>
+      </c>
+      <c r="AN6" t="n">
+        <v/>
+      </c>
+      <c r="AO6" t="n">
+        <v/>
+      </c>
+      <c r="AP6" t="n">
+        <v/>
+      </c>
+      <c r="AQ6" t="n">
+        <v/>
+      </c>
+      <c r="AR6" t="n">
+        <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>02-April-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>509</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>495</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>01-April-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>509</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>495</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>31-March-2026</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>509</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>496</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>30-March-2026</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>509</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="AE7" t="inlineStr">
         <is>
           <t>496</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
-      </c>
-      <c r="AB7" t="n">
-        <v/>
-      </c>
-      <c r="AC7" t="n">
-        <v/>
-      </c>
-      <c r="AD7" t="n">
-        <v/>
-      </c>
-      <c r="AE7" t="n">
-        <v/>
-      </c>
-      <c r="AF7" t="n">
-        <v/>
-      </c>
-      <c r="AG7" t="n">
-        <v/>
-      </c>
-      <c r="AH7" t="n">
-        <v/>
-      </c>
-      <c r="AI7" t="n">
-        <v/>
       </c>
       <c r="AK7" t="n">
         <v/>
@@ -2066,147 +2082,163 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>02-April-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>01-April-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>105</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>161</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>31-March-2026</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>30-March-2026</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="AD8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="AE8" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="AI8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
-      </c>
-      <c r="AB8" t="n">
-        <v/>
-      </c>
-      <c r="AC8" t="n">
-        <v/>
-      </c>
-      <c r="AD8" t="n">
-        <v/>
-      </c>
-      <c r="AE8" t="n">
-        <v/>
-      </c>
-      <c r="AF8" t="n">
-        <v/>
-      </c>
-      <c r="AG8" t="n">
-        <v/>
-      </c>
-      <c r="AH8" t="n">
-        <v/>
-      </c>
-      <c r="AI8" t="n">
-        <v/>
       </c>
       <c r="AK8" t="n">
         <v/>
@@ -2236,147 +2268,163 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>02-April-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>resident</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1142</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>1140</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>01-April-2026</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>163</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>510</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>469</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
         <is>
           <t>31-March-2026</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>211</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>211</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="X9" t="inlineStr">
         <is>
           <t>720</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
         <is>
           <t>30-March-2026</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="AC9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="AD9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="AE9" t="inlineStr">
         <is>
           <t>211</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="AF9" t="inlineStr">
         <is>
           <t>211</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="AG9" t="inlineStr">
         <is>
           <t>720</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB9" t="n">
-        <v/>
-      </c>
-      <c r="AC9" t="n">
-        <v/>
-      </c>
-      <c r="AD9" t="n">
-        <v/>
-      </c>
-      <c r="AE9" t="n">
-        <v/>
-      </c>
-      <c r="AF9" t="n">
-        <v/>
-      </c>
-      <c r="AG9" t="n">
-        <v/>
-      </c>
-      <c r="AH9" t="n">
-        <v/>
-      </c>
-      <c r="AI9" t="n">
-        <v/>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="AK9" t="n">
         <v/>
@@ -2406,147 +2454,163 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>02-April-2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>dsl</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>138</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>01-April-2026</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>209</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>62</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>110</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>31-March-2026</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>209</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>109</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
         <is>
           <t>70</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="AB10" t="inlineStr">
         <is>
           <t>30-March-2026</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="AC10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="AD10" t="inlineStr">
         <is>
           <t>209</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="AE10" t="inlineStr">
         <is>
           <t>106</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
         <is>
           <t>73</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
         <is>
           <t>30</t>
         </is>
-      </c>
-      <c r="AB10" t="n">
-        <v/>
-      </c>
-      <c r="AC10" t="n">
-        <v/>
-      </c>
-      <c r="AD10" t="n">
-        <v/>
-      </c>
-      <c r="AE10" t="n">
-        <v/>
-      </c>
-      <c r="AF10" t="n">
-        <v/>
-      </c>
-      <c r="AG10" t="n">
-        <v/>
-      </c>
-      <c r="AH10" t="n">
-        <v/>
-      </c>
-      <c r="AI10" t="n">
-        <v/>
       </c>
       <c r="AK10" t="n">
         <v/>

--- a/minio-report-tracker/xlxs/dev01.xlsx
+++ b/minio-report-tracker/xlxs/dev01.xlsx
@@ -655,7 +655,7 @@
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="6" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
-    <col width="3" customWidth="1" min="5" max="5"/>
+    <col width="5" customWidth="1" min="5" max="5"/>
     <col width="4" customWidth="1" min="6" max="6"/>
     <col width="4" customWidth="1" min="7" max="7"/>
     <col width="4" customWidth="1" min="8" max="8"/>
@@ -663,9 +663,9 @@
     <col width="15" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
     <col width="6" customWidth="1" min="12" max="12"/>
-    <col width="5" customWidth="1" min="13" max="13"/>
-    <col width="5" customWidth="1" min="14" max="14"/>
-    <col width="5" customWidth="1" min="15" max="15"/>
+    <col width="6" customWidth="1" min="13" max="13"/>
+    <col width="3" customWidth="1" min="14" max="14"/>
+    <col width="4" customWidth="1" min="15" max="15"/>
     <col width="4" customWidth="1" min="16" max="16"/>
     <col width="4" customWidth="1" min="17" max="17"/>
     <col width="2" customWidth="1" min="18" max="18"/>
@@ -688,13 +688,13 @@
     <col width="4" customWidth="1" min="35" max="35"/>
     <col width="2" customWidth="1" min="36" max="36"/>
     <col width="15" customWidth="1" min="37" max="37"/>
-    <col width="10" customWidth="1" min="38" max="38"/>
+    <col width="16" customWidth="1" min="38" max="38"/>
     <col width="6" customWidth="1" min="39" max="39"/>
-    <col width="6" customWidth="1" min="40" max="40"/>
+    <col width="5" customWidth="1" min="40" max="40"/>
     <col width="5" customWidth="1" min="41" max="41"/>
     <col width="5" customWidth="1" min="42" max="42"/>
-    <col width="5" customWidth="1" min="43" max="43"/>
-    <col width="5" customWidth="1" min="44" max="44"/>
+    <col width="4" customWidth="1" min="43" max="43"/>
+    <col width="4" customWidth="1" min="44" max="44"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -902,192 +902,192 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>03-April-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>597</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>02-April-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>597</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>01-April-2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>494</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>69</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>31-March-2026</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>114</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
         <is>
           <t>161</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="AG2" t="inlineStr">
         <is>
           <t>323</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="AH2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AI2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AK2" t="inlineStr">
         <is>
           <t>30-March-2026</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AL2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AM2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
+      <c r="AN2" t="inlineStr">
         <is>
           <t>113</t>
         </is>
       </c>
-      <c r="AF2" t="inlineStr">
+      <c r="AO2" t="inlineStr">
         <is>
           <t>161</t>
         </is>
       </c>
-      <c r="AG2" t="inlineStr">
+      <c r="AP2" t="inlineStr">
         <is>
           <t>324</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>27-March-2026</t>
-        </is>
-      </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>auth</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>612</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>597</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
@@ -1104,399 +1104,399 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>03-April-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>336</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>02-April-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>333</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>01-April-2026</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>73</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>231</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
         <is>
           <t>31-March-2026</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
         <is>
           <t>30-March-2026</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
+      <c r="AL3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="AD3" t="inlineStr">
+      <c r="AM3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="AE3" t="inlineStr">
+      <c r="AN3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>27-March-2026</t>
-        </is>
-      </c>
-      <c r="AL3" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>288</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>216</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AP3" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="AQ3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>03-April-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>930</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>02-April-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
         <is>
           <t>01-April-2026</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
         <is>
           <t>31-March-2026</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="AE4" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
         <is>
           <t>30-March-2026</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
+      <c r="AL4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="AD4" t="inlineStr">
+      <c r="AM4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="AE4" t="inlineStr">
+      <c r="AN4" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
         <is>
           <t>15</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>27-March-2026</t>
-        </is>
-      </c>
-      <c r="AL4" t="inlineStr">
-        <is>
-          <t>resident</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>1142</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>1142</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AP4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ4" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
@@ -1508,184 +1508,184 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>03-April-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>02-April-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
         <is>
           <t>01-April-2026</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
         <is>
           <t>31-March-2026</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="AE5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
         <is>
           <t>30-March-2026</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
+      <c r="AL5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="AD5" t="inlineStr">
+      <c r="AM5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="AE5" t="inlineStr">
+      <c r="AN5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>27-March-2026</t>
-        </is>
-      </c>
-      <c r="AL5" t="inlineStr">
-        <is>
-          <t>dsl</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>209</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>163</t>
-        </is>
-      </c>
       <c r="AO5" t="inlineStr">
         <is>
           <t>0</t>
@@ -1693,948 +1693,1028 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>03-April-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>930</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>02-April-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
         <is>
           <t>01-April-2026</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
         <is>
           <t>31-March-2026</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="AE6" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
         <is>
           <t>30-March-2026</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
+      <c r="AL6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="AD6" t="inlineStr">
+      <c r="AM6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="AE6" t="inlineStr">
+      <c r="AN6" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH6" t="inlineStr">
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK6" t="n">
-        <v/>
-      </c>
-      <c r="AL6" t="n">
-        <v/>
-      </c>
-      <c r="AM6" t="n">
-        <v/>
-      </c>
-      <c r="AN6" t="n">
-        <v/>
-      </c>
-      <c r="AO6" t="n">
-        <v/>
-      </c>
-      <c r="AP6" t="n">
-        <v/>
-      </c>
-      <c r="AQ6" t="n">
-        <v/>
-      </c>
-      <c r="AR6" t="n">
-        <v/>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>03-April-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>509</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>350</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>02-April-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>509</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>495</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>01-April-2026</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>509</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>495</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>31-March-2026</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>509</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="AE7" t="inlineStr">
         <is>
           <t>496</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AK7" t="inlineStr">
         <is>
           <t>30-March-2026</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
+      <c r="AL7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="AD7" t="inlineStr">
+      <c r="AM7" t="inlineStr">
         <is>
           <t>509</t>
         </is>
       </c>
-      <c r="AE7" t="inlineStr">
+      <c r="AN7" t="inlineStr">
         <is>
           <t>496</t>
         </is>
       </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG7" t="inlineStr">
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
-      </c>
-      <c r="AK7" t="n">
-        <v/>
-      </c>
-      <c r="AL7" t="n">
-        <v/>
-      </c>
-      <c r="AM7" t="n">
-        <v/>
-      </c>
-      <c r="AN7" t="n">
-        <v/>
-      </c>
-      <c r="AO7" t="n">
-        <v/>
-      </c>
-      <c r="AP7" t="n">
-        <v/>
-      </c>
-      <c r="AQ7" t="n">
-        <v/>
-      </c>
-      <c r="AR7" t="n">
-        <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>03-April-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>02-April-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>01-April-2026</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>105</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>161</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>31-March-2026</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="AD8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="AE8" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="AI8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AK8" t="inlineStr">
         <is>
           <t>30-March-2026</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
+      <c r="AL8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="AD8" t="inlineStr">
+      <c r="AM8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="AE8" t="inlineStr">
+      <c r="AN8" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH8" t="inlineStr">
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AI8" t="inlineStr">
+      <c r="AR8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
-      </c>
-      <c r="AK8" t="n">
-        <v/>
-      </c>
-      <c r="AL8" t="n">
-        <v/>
-      </c>
-      <c r="AM8" t="n">
-        <v/>
-      </c>
-      <c r="AN8" t="n">
-        <v/>
-      </c>
-      <c r="AO8" t="n">
-        <v/>
-      </c>
-      <c r="AP8" t="n">
-        <v/>
-      </c>
-      <c r="AQ8" t="n">
-        <v/>
-      </c>
-      <c r="AR8" t="n">
-        <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>03-April-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>resident</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1142</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>1136</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>02-April-2026</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>1140</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
         <is>
           <t>01-April-2026</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>163</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>510</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="X9" t="inlineStr">
         <is>
           <t>469</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
         <is>
           <t>31-March-2026</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="AC9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="AD9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="AE9" t="inlineStr">
         <is>
           <t>211</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="AF9" t="inlineStr">
         <is>
           <t>211</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="AG9" t="inlineStr">
         <is>
           <t>720</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
         <is>
           <t>30-March-2026</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
+      <c r="AL9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="AD9" t="inlineStr">
+      <c r="AM9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="AE9" t="inlineStr">
+      <c r="AN9" t="inlineStr">
         <is>
           <t>211</t>
         </is>
       </c>
-      <c r="AF9" t="inlineStr">
+      <c r="AO9" t="inlineStr">
         <is>
           <t>211</t>
         </is>
       </c>
-      <c r="AG9" t="inlineStr">
+      <c r="AP9" t="inlineStr">
         <is>
           <t>720</t>
         </is>
       </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK9" t="n">
-        <v/>
-      </c>
-      <c r="AL9" t="n">
-        <v/>
-      </c>
-      <c r="AM9" t="n">
-        <v/>
-      </c>
-      <c r="AN9" t="n">
-        <v/>
-      </c>
-      <c r="AO9" t="n">
-        <v/>
-      </c>
-      <c r="AP9" t="n">
-        <v/>
-      </c>
-      <c r="AQ9" t="n">
-        <v/>
-      </c>
-      <c r="AR9" t="n">
-        <v/>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>03-April-2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>dsl</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>163</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>02-April-2026</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>209</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>138</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
         <is>
           <t>41</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>01-April-2026</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>209</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>62</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="X10" t="inlineStr">
         <is>
           <t>110</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="AB10" t="inlineStr">
         <is>
           <t>31-March-2026</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="AC10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="AD10" t="inlineStr">
         <is>
           <t>209</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="AE10" t="inlineStr">
         <is>
           <t>109</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
         <is>
           <t>70</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AK10" t="inlineStr">
         <is>
           <t>30-March-2026</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
+      <c r="AL10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="AD10" t="inlineStr">
+      <c r="AM10" t="inlineStr">
         <is>
           <t>209</t>
         </is>
       </c>
-      <c r="AE10" t="inlineStr">
+      <c r="AN10" t="inlineStr">
         <is>
           <t>106</t>
         </is>
       </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG10" t="inlineStr">
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AP10" t="inlineStr">
         <is>
           <t>73</t>
         </is>
       </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
+      <c r="AQ10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
         <is>
           <t>30</t>
         </is>
-      </c>
-      <c r="AK10" t="n">
-        <v/>
-      </c>
-      <c r="AL10" t="n">
-        <v/>
-      </c>
-      <c r="AM10" t="n">
-        <v/>
-      </c>
-      <c r="AN10" t="n">
-        <v/>
-      </c>
-      <c r="AO10" t="n">
-        <v/>
-      </c>
-      <c r="AP10" t="n">
-        <v/>
-      </c>
-      <c r="AQ10" t="n">
-        <v/>
-      </c>
-      <c r="AR10" t="n">
-        <v/>
       </c>
     </row>
   </sheetData>

--- a/minio-report-tracker/xlxs/dev01.xlsx
+++ b/minio-report-tracker/xlxs/dev01.xlsx
@@ -653,18 +653,18 @@
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="6" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="5" customWidth="1" min="3" max="3"/>
+    <col width="5" customWidth="1" min="4" max="4"/>
     <col width="5" customWidth="1" min="5" max="5"/>
-    <col width="4" customWidth="1" min="6" max="6"/>
-    <col width="4" customWidth="1" min="7" max="7"/>
-    <col width="4" customWidth="1" min="8" max="8"/>
+    <col width="5" customWidth="1" min="6" max="6"/>
+    <col width="5" customWidth="1" min="7" max="7"/>
+    <col width="5" customWidth="1" min="8" max="8"/>
     <col width="2" customWidth="1" min="9" max="9"/>
     <col width="15" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
     <col width="6" customWidth="1" min="12" max="12"/>
     <col width="6" customWidth="1" min="13" max="13"/>
-    <col width="3" customWidth="1" min="14" max="14"/>
+    <col width="5" customWidth="1" min="14" max="14"/>
     <col width="4" customWidth="1" min="15" max="15"/>
     <col width="4" customWidth="1" min="16" max="16"/>
     <col width="4" customWidth="1" min="17" max="17"/>
@@ -672,9 +672,9 @@
     <col width="15" customWidth="1" min="19" max="19"/>
     <col width="16" customWidth="1" min="20" max="20"/>
     <col width="6" customWidth="1" min="21" max="21"/>
-    <col width="5" customWidth="1" min="22" max="22"/>
-    <col width="5" customWidth="1" min="23" max="23"/>
-    <col width="5" customWidth="1" min="24" max="24"/>
+    <col width="6" customWidth="1" min="22" max="22"/>
+    <col width="3" customWidth="1" min="23" max="23"/>
+    <col width="4" customWidth="1" min="24" max="24"/>
     <col width="4" customWidth="1" min="25" max="25"/>
     <col width="4" customWidth="1" min="26" max="26"/>
     <col width="2" customWidth="1" min="27" max="27"/>
@@ -902,192 +902,192 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>06-April-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>930</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>03-April-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>597</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>02-April-2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>597</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>01-April-2026</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
         <is>
           <t>494</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="AG2" t="inlineStr">
         <is>
           <t>69</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="AH2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AI2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AK2" t="inlineStr">
         <is>
           <t>31-March-2026</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AL2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AM2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
+      <c r="AN2" t="inlineStr">
         <is>
           <t>114</t>
         </is>
       </c>
-      <c r="AF2" t="inlineStr">
+      <c r="AO2" t="inlineStr">
         <is>
           <t>161</t>
         </is>
       </c>
-      <c r="AG2" t="inlineStr">
+      <c r="AP2" t="inlineStr">
         <is>
           <t>323</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>30-March-2026</t>
-        </is>
-      </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>auth</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>612</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>113</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>161</t>
-        </is>
-      </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>324</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
@@ -1104,167 +1104,167 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>06-April-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>03-April-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>02-April-2026</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>333</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
         <is>
           <t>01-April-2026</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>73</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="AF3" t="inlineStr">
         <is>
           <t>231</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="AG3" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
+      <c r="AH3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
         <is>
           <t>31-March-2026</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>idrepo</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>414</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>336</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>30-March-2026</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
@@ -1306,167 +1306,167 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>06-April-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>930</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>03-April-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
         <is>
           <t>02-April-2026</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
         <is>
           <t>01-April-2026</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="AE4" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
         <is>
           <t>31-March-2026</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>masterdata-ara</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>930</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>30-March-2026</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
@@ -1508,167 +1508,167 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>06-April-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>509</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>350</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>03-April-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
         <is>
           <t>02-April-2026</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
         <is>
           <t>01-April-2026</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="AE5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
         <is>
           <t>31-March-2026</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>masterdata-eng</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>30-March-2026</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
@@ -1710,167 +1710,167 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>06-April-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>03-April-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
         <is>
           <t>02-April-2026</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
         <is>
           <t>01-April-2026</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="AE6" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
         <is>
           <t>31-March-2026</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>masterdata-fra</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>930</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>30-March-2026</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
@@ -1912,167 +1912,167 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>06-April-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>dsl</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>152</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>03-April-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>509</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>350</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>116</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>02-April-2026</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>509</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>495</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>01-April-2026</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>509</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="AE7" t="inlineStr">
         <is>
           <t>495</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AK7" t="inlineStr">
         <is>
           <t>31-March-2026</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>partner</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>509</t>
-        </is>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>496</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>30-March-2026</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
@@ -2112,169 +2112,153 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" t="n">
+        <v/>
+      </c>
+      <c r="B8" t="n">
+        <v/>
+      </c>
+      <c r="C8" t="n">
+        <v/>
+      </c>
+      <c r="D8" t="n">
+        <v/>
+      </c>
+      <c r="E8" t="n">
+        <v/>
+      </c>
+      <c r="F8" t="n">
+        <v/>
+      </c>
+      <c r="G8" t="n">
+        <v/>
+      </c>
+      <c r="H8" t="n">
+        <v/>
+      </c>
+      <c r="J8" t="inlineStr">
         <is>
           <t>03-April-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>02-April-2026</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>01-April-2026</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="AD8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="AE8" t="inlineStr">
         <is>
           <t>105</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="AF8" t="inlineStr">
         <is>
           <t>161</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="AG8" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
+      <c r="AH8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="AI8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AK8" t="inlineStr">
         <is>
           <t>31-March-2026</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="AD8" t="inlineStr">
-        <is>
-          <t>288</t>
-        </is>
-      </c>
-      <c r="AE8" t="inlineStr">
-        <is>
-          <t>282</t>
-        </is>
-      </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>30-March-2026</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
@@ -2314,169 +2298,153 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" t="n">
+        <v/>
+      </c>
+      <c r="B9" t="n">
+        <v/>
+      </c>
+      <c r="C9" t="n">
+        <v/>
+      </c>
+      <c r="D9" t="n">
+        <v/>
+      </c>
+      <c r="E9" t="n">
+        <v/>
+      </c>
+      <c r="F9" t="n">
+        <v/>
+      </c>
+      <c r="G9" t="n">
+        <v/>
+      </c>
+      <c r="H9" t="n">
+        <v/>
+      </c>
+      <c r="J9" t="inlineStr">
         <is>
           <t>03-April-2026</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>1136</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
         <is>
           <t>02-April-2026</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>1140</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
         <is>
           <t>01-April-2026</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="AC9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="AD9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="AE9" t="inlineStr">
         <is>
           <t>163</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="AF9" t="inlineStr">
         <is>
           <t>510</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="AG9" t="inlineStr">
         <is>
           <t>469</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
         <is>
           <t>31-March-2026</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>resident</t>
-        </is>
-      </c>
-      <c r="AD9" t="inlineStr">
-        <is>
-          <t>1142</t>
-        </is>
-      </c>
-      <c r="AE9" t="inlineStr">
-        <is>
-          <t>211</t>
-        </is>
-      </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>211</t>
-        </is>
-      </c>
-      <c r="AG9" t="inlineStr">
-        <is>
-          <t>720</t>
-        </is>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>30-March-2026</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
@@ -2516,194 +2484,178 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" t="n">
+        <v/>
+      </c>
+      <c r="B10" t="n">
+        <v/>
+      </c>
+      <c r="C10" t="n">
+        <v/>
+      </c>
+      <c r="D10" t="n">
+        <v/>
+      </c>
+      <c r="E10" t="n">
+        <v/>
+      </c>
+      <c r="F10" t="n">
+        <v/>
+      </c>
+      <c r="G10" t="n">
+        <v/>
+      </c>
+      <c r="H10" t="n">
+        <v/>
+      </c>
+      <c r="J10" t="inlineStr">
         <is>
           <t>03-April-2026</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>209</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>163</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>02-April-2026</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>209</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>138</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
         <is>
           <t>41</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="AB10" t="inlineStr">
         <is>
           <t>01-April-2026</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="AC10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="AD10" t="inlineStr">
         <is>
           <t>209</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="AE10" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
+      <c r="AF10" t="inlineStr">
         <is>
           <t>62</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
+      <c r="AG10" t="inlineStr">
         <is>
           <t>110</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AK10" t="inlineStr">
         <is>
           <t>31-March-2026</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
+      <c r="AL10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="AD10" t="inlineStr">
+      <c r="AM10" t="inlineStr">
         <is>
           <t>209</t>
         </is>
       </c>
-      <c r="AE10" t="inlineStr">
+      <c r="AN10" t="inlineStr">
         <is>
           <t>109</t>
         </is>
       </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG10" t="inlineStr">
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AP10" t="inlineStr">
         <is>
           <t>70</t>
-        </is>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>30-March-2026</t>
-        </is>
-      </c>
-      <c r="AL10" t="inlineStr">
-        <is>
-          <t>dsl</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>209</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>106</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AP10" t="inlineStr">
-        <is>
-          <t>73</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">

--- a/minio-report-tracker/xlxs/dev01.xlsx
+++ b/minio-report-tracker/xlxs/dev01.xlsx
@@ -653,27 +653,27 @@
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="5" customWidth="1" min="3" max="3"/>
-    <col width="5" customWidth="1" min="4" max="4"/>
+    <col width="6" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
     <col width="5" customWidth="1" min="5" max="5"/>
-    <col width="5" customWidth="1" min="6" max="6"/>
-    <col width="5" customWidth="1" min="7" max="7"/>
-    <col width="5" customWidth="1" min="8" max="8"/>
+    <col width="4" customWidth="1" min="6" max="6"/>
+    <col width="4" customWidth="1" min="7" max="7"/>
+    <col width="4" customWidth="1" min="8" max="8"/>
     <col width="2" customWidth="1" min="9" max="9"/>
     <col width="15" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="6" customWidth="1" min="12" max="12"/>
-    <col width="6" customWidth="1" min="13" max="13"/>
+    <col width="5" customWidth="1" min="12" max="12"/>
+    <col width="5" customWidth="1" min="13" max="13"/>
     <col width="5" customWidth="1" min="14" max="14"/>
-    <col width="4" customWidth="1" min="15" max="15"/>
-    <col width="4" customWidth="1" min="16" max="16"/>
-    <col width="4" customWidth="1" min="17" max="17"/>
+    <col width="5" customWidth="1" min="15" max="15"/>
+    <col width="5" customWidth="1" min="16" max="16"/>
+    <col width="5" customWidth="1" min="17" max="17"/>
     <col width="2" customWidth="1" min="18" max="18"/>
     <col width="15" customWidth="1" min="19" max="19"/>
     <col width="16" customWidth="1" min="20" max="20"/>
     <col width="6" customWidth="1" min="21" max="21"/>
     <col width="6" customWidth="1" min="22" max="22"/>
-    <col width="3" customWidth="1" min="23" max="23"/>
+    <col width="5" customWidth="1" min="23" max="23"/>
     <col width="4" customWidth="1" min="24" max="24"/>
     <col width="4" customWidth="1" min="25" max="25"/>
     <col width="4" customWidth="1" min="26" max="26"/>
@@ -681,9 +681,9 @@
     <col width="15" customWidth="1" min="28" max="28"/>
     <col width="16" customWidth="1" min="29" max="29"/>
     <col width="6" customWidth="1" min="30" max="30"/>
-    <col width="5" customWidth="1" min="31" max="31"/>
-    <col width="5" customWidth="1" min="32" max="32"/>
-    <col width="5" customWidth="1" min="33" max="33"/>
+    <col width="6" customWidth="1" min="31" max="31"/>
+    <col width="3" customWidth="1" min="32" max="32"/>
+    <col width="4" customWidth="1" min="33" max="33"/>
     <col width="4" customWidth="1" min="34" max="34"/>
     <col width="4" customWidth="1" min="35" max="35"/>
     <col width="2" customWidth="1" min="36" max="36"/>
@@ -902,192 +902,192 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>07-April-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>284</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>06-April-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
         <is>
           <t>03-April-2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>597</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>02-April-2026</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>597</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="AH2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AI2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AK2" t="inlineStr">
         <is>
           <t>01-April-2026</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AL2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AM2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
+      <c r="AN2" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="AF2" t="inlineStr">
+      <c r="AO2" t="inlineStr">
         <is>
           <t>494</t>
         </is>
       </c>
-      <c r="AG2" t="inlineStr">
+      <c r="AP2" t="inlineStr">
         <is>
           <t>69</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>31-March-2026</t>
-        </is>
-      </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>auth</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>612</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>114</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>161</t>
-        </is>
-      </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>323</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
@@ -1104,192 +1104,192 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>07-April-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>336</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>06-April-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>03-April-2026</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
         <is>
           <t>02-April-2026</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>333</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
+      <c r="AH3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
         <is>
           <t>01-April-2026</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
+      <c r="AL3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="AD3" t="inlineStr">
+      <c r="AM3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="AE3" t="inlineStr">
+      <c r="AN3" t="inlineStr">
         <is>
           <t>73</t>
         </is>
       </c>
-      <c r="AF3" t="inlineStr">
+      <c r="AO3" t="inlineStr">
         <is>
           <t>231</t>
         </is>
       </c>
-      <c r="AG3" t="inlineStr">
+      <c r="AP3" t="inlineStr">
         <is>
           <t>32</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>31-March-2026</t>
-        </is>
-      </c>
-      <c r="AL3" t="inlineStr">
-        <is>
-          <t>idrepo</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>414</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>336</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AP3" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
@@ -1306,167 +1306,167 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>07-April-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>930</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>06-April-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
         <is>
           <t>03-April-2026</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
         <is>
           <t>02-April-2026</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="AE4" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
         <is>
           <t>01-April-2026</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>masterdata-ara</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>930</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>31-March-2026</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
@@ -1508,167 +1508,167 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>07-April-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>06-April-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>509</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>350</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>116</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>03-April-2026</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
         <is>
           <t>02-April-2026</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="AE5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
         <is>
           <t>01-April-2026</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>masterdata-eng</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>31-March-2026</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
@@ -1710,167 +1710,167 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>07-April-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>930</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>06-April-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>03-April-2026</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
         <is>
           <t>02-April-2026</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="AE6" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
         <is>
           <t>01-April-2026</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>masterdata-fra</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>930</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>31-March-2026</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
@@ -1912,192 +1912,192 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>07-April-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>509</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>495</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>06-April-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>209</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
         <is>
           <t>152</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>03-April-2026</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>509</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>350</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>116</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>02-April-2026</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>509</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="AE7" t="inlineStr">
         <is>
           <t>495</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AK7" t="inlineStr">
         <is>
           <t>01-April-2026</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
+      <c r="AL7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="AD7" t="inlineStr">
+      <c r="AM7" t="inlineStr">
         <is>
           <t>509</t>
         </is>
       </c>
-      <c r="AE7" t="inlineStr">
+      <c r="AN7" t="inlineStr">
         <is>
           <t>495</t>
         </is>
       </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG7" t="inlineStr">
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>31-March-2026</t>
-        </is>
-      </c>
-      <c r="AL7" t="inlineStr">
-        <is>
-          <t>partner</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>509</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>496</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AP7" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
@@ -2112,178 +2112,178 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="n">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>07-April-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
         <v/>
       </c>
-      <c r="B8" t="n">
+      <c r="K8" t="n">
         <v/>
       </c>
-      <c r="C8" t="n">
+      <c r="L8" t="n">
         <v/>
       </c>
-      <c r="D8" t="n">
+      <c r="M8" t="n">
         <v/>
       </c>
-      <c r="E8" t="n">
+      <c r="N8" t="n">
         <v/>
       </c>
-      <c r="F8" t="n">
+      <c r="O8" t="n">
         <v/>
       </c>
-      <c r="G8" t="n">
+      <c r="P8" t="n">
         <v/>
       </c>
-      <c r="H8" t="n">
+      <c r="Q8" t="n">
         <v/>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>03-April-2026</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>02-April-2026</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="AD8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="AE8" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="AI8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AK8" t="inlineStr">
         <is>
           <t>01-April-2026</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
+      <c r="AL8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="AD8" t="inlineStr">
+      <c r="AM8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="AE8" t="inlineStr">
+      <c r="AN8" t="inlineStr">
         <is>
           <t>105</t>
         </is>
       </c>
-      <c r="AF8" t="inlineStr">
+      <c r="AO8" t="inlineStr">
         <is>
           <t>161</t>
         </is>
       </c>
-      <c r="AG8" t="inlineStr">
+      <c r="AP8" t="inlineStr">
         <is>
           <t>16</t>
-        </is>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>31-March-2026</t>
-        </is>
-      </c>
-      <c r="AL8" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>288</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>282</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AP8" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
@@ -2298,178 +2298,178 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="n">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>07-April-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>resident</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1142</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>1139</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
         <v/>
       </c>
-      <c r="B9" t="n">
+      <c r="K9" t="n">
         <v/>
       </c>
-      <c r="C9" t="n">
+      <c r="L9" t="n">
         <v/>
       </c>
-      <c r="D9" t="n">
+      <c r="M9" t="n">
         <v/>
       </c>
-      <c r="E9" t="n">
+      <c r="N9" t="n">
         <v/>
       </c>
-      <c r="F9" t="n">
+      <c r="O9" t="n">
         <v/>
       </c>
-      <c r="G9" t="n">
+      <c r="P9" t="n">
         <v/>
       </c>
-      <c r="H9" t="n">
+      <c r="Q9" t="n">
         <v/>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>03-April-2026</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>1136</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
         <is>
           <t>02-April-2026</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="AC9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="AD9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="AE9" t="inlineStr">
         <is>
           <t>1140</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
         <is>
           <t>01-April-2026</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
+      <c r="AL9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="AD9" t="inlineStr">
+      <c r="AM9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="AE9" t="inlineStr">
+      <c r="AN9" t="inlineStr">
         <is>
           <t>163</t>
         </is>
       </c>
-      <c r="AF9" t="inlineStr">
+      <c r="AO9" t="inlineStr">
         <is>
           <t>510</t>
         </is>
       </c>
-      <c r="AG9" t="inlineStr">
+      <c r="AP9" t="inlineStr">
         <is>
           <t>469</t>
-        </is>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>31-March-2026</t>
-        </is>
-      </c>
-      <c r="AL9" t="inlineStr">
-        <is>
-          <t>resident</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>1142</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>211</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>211</t>
-        </is>
-      </c>
-      <c r="AP9" t="inlineStr">
-        <is>
-          <t>720</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
@@ -2484,178 +2484,178 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="n">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>07-April-2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>dsl</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>178</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
         <v/>
       </c>
-      <c r="B10" t="n">
+      <c r="K10" t="n">
         <v/>
       </c>
-      <c r="C10" t="n">
+      <c r="L10" t="n">
         <v/>
       </c>
-      <c r="D10" t="n">
+      <c r="M10" t="n">
         <v/>
       </c>
-      <c r="E10" t="n">
+      <c r="N10" t="n">
         <v/>
       </c>
-      <c r="F10" t="n">
+      <c r="O10" t="n">
         <v/>
       </c>
-      <c r="G10" t="n">
+      <c r="P10" t="n">
         <v/>
       </c>
-      <c r="H10" t="n">
+      <c r="Q10" t="n">
         <v/>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>03-April-2026</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>209</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>163</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="AB10" t="inlineStr">
         <is>
           <t>02-April-2026</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="AC10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="AD10" t="inlineStr">
         <is>
           <t>209</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="AE10" t="inlineStr">
         <is>
           <t>138</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
         <is>
           <t>41</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AK10" t="inlineStr">
         <is>
           <t>01-April-2026</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
+      <c r="AL10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="AD10" t="inlineStr">
+      <c r="AM10" t="inlineStr">
         <is>
           <t>209</t>
         </is>
       </c>
-      <c r="AE10" t="inlineStr">
+      <c r="AN10" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AF10" t="inlineStr">
+      <c r="AO10" t="inlineStr">
         <is>
           <t>62</t>
         </is>
       </c>
-      <c r="AG10" t="inlineStr">
+      <c r="AP10" t="inlineStr">
         <is>
           <t>110</t>
-        </is>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>31-March-2026</t>
-        </is>
-      </c>
-      <c r="AL10" t="inlineStr">
-        <is>
-          <t>dsl</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>209</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AP10" t="inlineStr">
-        <is>
-          <t>70</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">

--- a/minio-report-tracker/xlxs/dev01.xlsx
+++ b/minio-report-tracker/xlxs/dev01.xlsx
@@ -655,34 +655,34 @@
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="6" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
-    <col width="5" customWidth="1" min="5" max="5"/>
+    <col width="3" customWidth="1" min="5" max="5"/>
     <col width="4" customWidth="1" min="6" max="6"/>
     <col width="4" customWidth="1" min="7" max="7"/>
     <col width="4" customWidth="1" min="8" max="8"/>
     <col width="2" customWidth="1" min="9" max="9"/>
     <col width="15" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="5" customWidth="1" min="12" max="12"/>
-    <col width="5" customWidth="1" min="13" max="13"/>
+    <col width="6" customWidth="1" min="12" max="12"/>
+    <col width="6" customWidth="1" min="13" max="13"/>
     <col width="5" customWidth="1" min="14" max="14"/>
-    <col width="5" customWidth="1" min="15" max="15"/>
-    <col width="5" customWidth="1" min="16" max="16"/>
-    <col width="5" customWidth="1" min="17" max="17"/>
+    <col width="4" customWidth="1" min="15" max="15"/>
+    <col width="4" customWidth="1" min="16" max="16"/>
+    <col width="4" customWidth="1" min="17" max="17"/>
     <col width="2" customWidth="1" min="18" max="18"/>
     <col width="15" customWidth="1" min="19" max="19"/>
     <col width="16" customWidth="1" min="20" max="20"/>
-    <col width="6" customWidth="1" min="21" max="21"/>
-    <col width="6" customWidth="1" min="22" max="22"/>
+    <col width="5" customWidth="1" min="21" max="21"/>
+    <col width="5" customWidth="1" min="22" max="22"/>
     <col width="5" customWidth="1" min="23" max="23"/>
-    <col width="4" customWidth="1" min="24" max="24"/>
-    <col width="4" customWidth="1" min="25" max="25"/>
-    <col width="4" customWidth="1" min="26" max="26"/>
+    <col width="5" customWidth="1" min="24" max="24"/>
+    <col width="5" customWidth="1" min="25" max="25"/>
+    <col width="5" customWidth="1" min="26" max="26"/>
     <col width="2" customWidth="1" min="27" max="27"/>
     <col width="15" customWidth="1" min="28" max="28"/>
     <col width="16" customWidth="1" min="29" max="29"/>
     <col width="6" customWidth="1" min="30" max="30"/>
     <col width="6" customWidth="1" min="31" max="31"/>
-    <col width="3" customWidth="1" min="32" max="32"/>
+    <col width="5" customWidth="1" min="32" max="32"/>
     <col width="4" customWidth="1" min="33" max="33"/>
     <col width="4" customWidth="1" min="34" max="34"/>
     <col width="4" customWidth="1" min="35" max="35"/>
@@ -690,9 +690,9 @@
     <col width="15" customWidth="1" min="37" max="37"/>
     <col width="16" customWidth="1" min="38" max="38"/>
     <col width="6" customWidth="1" min="39" max="39"/>
-    <col width="5" customWidth="1" min="40" max="40"/>
-    <col width="5" customWidth="1" min="41" max="41"/>
-    <col width="5" customWidth="1" min="42" max="42"/>
+    <col width="6" customWidth="1" min="40" max="40"/>
+    <col width="3" customWidth="1" min="41" max="41"/>
+    <col width="4" customWidth="1" min="42" max="42"/>
     <col width="4" customWidth="1" min="43" max="43"/>
     <col width="4" customWidth="1" min="44" max="44"/>
   </cols>
@@ -902,192 +902,192 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>08-April-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>592</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>07-April-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>284</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>37</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>06-April-2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
         <is>
           <t>03-April-2026</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>597</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="AH2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AI2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AK2" t="inlineStr">
         <is>
           <t>02-April-2026</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AL2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AM2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
+      <c r="AN2" t="inlineStr">
         <is>
           <t>597</t>
         </is>
       </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>01-April-2026</t>
-        </is>
-      </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>auth</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>612</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>494</t>
-        </is>
-      </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>69</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
@@ -1104,192 +1104,192 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>08-April-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>336</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>07-April-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>06-April-2026</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
         <is>
           <t>03-April-2026</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
         <is>
           <t>02-April-2026</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
+      <c r="AL3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="AD3" t="inlineStr">
+      <c r="AM3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="AE3" t="inlineStr">
+      <c r="AN3" t="inlineStr">
         <is>
           <t>333</t>
         </is>
       </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
         <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>01-April-2026</t>
-        </is>
-      </c>
-      <c r="AL3" t="inlineStr">
-        <is>
-          <t>idrepo</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>414</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>231</t>
-        </is>
-      </c>
-      <c r="AP3" t="inlineStr">
-        <is>
-          <t>32</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
@@ -1306,167 +1306,167 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>08-April-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>930</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>07-April-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
         <is>
           <t>06-April-2026</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
         <is>
           <t>03-April-2026</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="AE4" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
         <is>
           <t>02-April-2026</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>masterdata-ara</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>930</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>01-April-2026</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
@@ -1508,167 +1508,167 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>08-April-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>07-April-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
         <is>
           <t>06-April-2026</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>509</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>350</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>116</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="AB5" t="inlineStr">
         <is>
           <t>03-April-2026</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="AE5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
         <is>
           <t>02-April-2026</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>masterdata-eng</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>01-April-2026</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
@@ -1710,167 +1710,167 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>08-April-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>930</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>07-April-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
         <is>
           <t>06-April-2026</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="Z6" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="AB6" t="inlineStr">
         <is>
           <t>03-April-2026</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="AE6" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
         <is>
           <t>02-April-2026</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>masterdata-fra</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>930</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>01-April-2026</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
@@ -1912,167 +1912,167 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>08-April-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>509</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>496</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>07-April-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>509</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>495</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>06-April-2026</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>209</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
         <is>
           <t>152</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>03-April-2026</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>509</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="AE7" t="inlineStr">
         <is>
           <t>350</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="AF7" t="inlineStr">
         <is>
           <t>116</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="AG7" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AK7" t="inlineStr">
         <is>
           <t>02-April-2026</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>partner</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>509</t>
-        </is>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>495</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>01-April-2026</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
@@ -2114,176 +2114,176 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>08-April-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>07-April-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J8" t="n">
+      <c r="S8" t="n">
         <v/>
       </c>
-      <c r="K8" t="n">
+      <c r="T8" t="n">
         <v/>
       </c>
-      <c r="L8" t="n">
+      <c r="U8" t="n">
         <v/>
       </c>
-      <c r="M8" t="n">
+      <c r="V8" t="n">
         <v/>
       </c>
-      <c r="N8" t="n">
+      <c r="W8" t="n">
         <v/>
       </c>
-      <c r="O8" t="n">
+      <c r="X8" t="n">
         <v/>
       </c>
-      <c r="P8" t="n">
+      <c r="Y8" t="n">
         <v/>
       </c>
-      <c r="Q8" t="n">
+      <c r="Z8" t="n">
         <v/>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>03-April-2026</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="AD8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="AE8" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="AI8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AK8" t="inlineStr">
         <is>
           <t>02-April-2026</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
+      <c r="AL8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="AD8" t="inlineStr">
+      <c r="AM8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="AE8" t="inlineStr">
+      <c r="AN8" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>01-April-2026</t>
-        </is>
-      </c>
-      <c r="AL8" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>288</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>105</t>
-        </is>
-      </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
@@ -2300,176 +2300,176 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>08-April-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>resident</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1142</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>1139</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>07-April-2026</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>1139</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J9" t="n">
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S9" t="n">
         <v/>
       </c>
-      <c r="K9" t="n">
+      <c r="T9" t="n">
         <v/>
       </c>
-      <c r="L9" t="n">
+      <c r="U9" t="n">
         <v/>
       </c>
-      <c r="M9" t="n">
+      <c r="V9" t="n">
         <v/>
       </c>
-      <c r="N9" t="n">
+      <c r="W9" t="n">
         <v/>
       </c>
-      <c r="O9" t="n">
+      <c r="X9" t="n">
         <v/>
       </c>
-      <c r="P9" t="n">
+      <c r="Y9" t="n">
         <v/>
       </c>
-      <c r="Q9" t="n">
+      <c r="Z9" t="n">
         <v/>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="AB9" t="inlineStr">
         <is>
           <t>03-April-2026</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="AC9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="AD9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="AE9" t="inlineStr">
         <is>
           <t>1136</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
         <is>
           <t>02-April-2026</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
+      <c r="AL9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="AD9" t="inlineStr">
+      <c r="AM9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="AE9" t="inlineStr">
+      <c r="AN9" t="inlineStr">
         <is>
           <t>1140</t>
         </is>
       </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG9" t="inlineStr">
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>01-April-2026</t>
-        </is>
-      </c>
-      <c r="AL9" t="inlineStr">
-        <is>
-          <t>resident</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>1142</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>163</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>510</t>
-        </is>
-      </c>
-      <c r="AP9" t="inlineStr">
-        <is>
-          <t>469</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
@@ -2486,176 +2486,176 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>08-April-2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>dsl</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>163</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>07-April-2026</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>209</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>178</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="J10" t="n">
+      <c r="S10" t="n">
         <v/>
       </c>
-      <c r="K10" t="n">
+      <c r="T10" t="n">
         <v/>
       </c>
-      <c r="L10" t="n">
+      <c r="U10" t="n">
         <v/>
       </c>
-      <c r="M10" t="n">
+      <c r="V10" t="n">
         <v/>
       </c>
-      <c r="N10" t="n">
+      <c r="W10" t="n">
         <v/>
       </c>
-      <c r="O10" t="n">
+      <c r="X10" t="n">
         <v/>
       </c>
-      <c r="P10" t="n">
+      <c r="Y10" t="n">
         <v/>
       </c>
-      <c r="Q10" t="n">
+      <c r="Z10" t="n">
         <v/>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="AB10" t="inlineStr">
         <is>
           <t>03-April-2026</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="AC10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="AD10" t="inlineStr">
         <is>
           <t>209</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="AE10" t="inlineStr">
         <is>
           <t>163</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AK10" t="inlineStr">
         <is>
           <t>02-April-2026</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
+      <c r="AL10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="AD10" t="inlineStr">
+      <c r="AM10" t="inlineStr">
         <is>
           <t>209</t>
         </is>
       </c>
-      <c r="AE10" t="inlineStr">
+      <c r="AN10" t="inlineStr">
         <is>
           <t>138</t>
         </is>
       </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG10" t="inlineStr">
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AP10" t="inlineStr">
         <is>
           <t>41</t>
-        </is>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>01-April-2026</t>
-        </is>
-      </c>
-      <c r="AL10" t="inlineStr">
-        <is>
-          <t>dsl</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>209</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="AP10" t="inlineStr">
-        <is>
-          <t>110</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">

--- a/minio-report-tracker/xlxs/dev01.xlsx
+++ b/minio-report-tracker/xlxs/dev01.xlsx
@@ -655,7 +655,7 @@
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="6" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
-    <col width="3" customWidth="1" min="5" max="5"/>
+    <col width="5" customWidth="1" min="5" max="5"/>
     <col width="4" customWidth="1" min="6" max="6"/>
     <col width="4" customWidth="1" min="7" max="7"/>
     <col width="4" customWidth="1" min="8" max="8"/>
@@ -664,34 +664,34 @@
     <col width="16" customWidth="1" min="11" max="11"/>
     <col width="6" customWidth="1" min="12" max="12"/>
     <col width="6" customWidth="1" min="13" max="13"/>
-    <col width="5" customWidth="1" min="14" max="14"/>
+    <col width="3" customWidth="1" min="14" max="14"/>
     <col width="4" customWidth="1" min="15" max="15"/>
     <col width="4" customWidth="1" min="16" max="16"/>
     <col width="4" customWidth="1" min="17" max="17"/>
     <col width="2" customWidth="1" min="18" max="18"/>
     <col width="15" customWidth="1" min="19" max="19"/>
     <col width="16" customWidth="1" min="20" max="20"/>
-    <col width="5" customWidth="1" min="21" max="21"/>
-    <col width="5" customWidth="1" min="22" max="22"/>
+    <col width="6" customWidth="1" min="21" max="21"/>
+    <col width="6" customWidth="1" min="22" max="22"/>
     <col width="5" customWidth="1" min="23" max="23"/>
-    <col width="5" customWidth="1" min="24" max="24"/>
-    <col width="5" customWidth="1" min="25" max="25"/>
-    <col width="5" customWidth="1" min="26" max="26"/>
+    <col width="4" customWidth="1" min="24" max="24"/>
+    <col width="4" customWidth="1" min="25" max="25"/>
+    <col width="4" customWidth="1" min="26" max="26"/>
     <col width="2" customWidth="1" min="27" max="27"/>
     <col width="15" customWidth="1" min="28" max="28"/>
     <col width="16" customWidth="1" min="29" max="29"/>
-    <col width="6" customWidth="1" min="30" max="30"/>
-    <col width="6" customWidth="1" min="31" max="31"/>
+    <col width="5" customWidth="1" min="30" max="30"/>
+    <col width="5" customWidth="1" min="31" max="31"/>
     <col width="5" customWidth="1" min="32" max="32"/>
-    <col width="4" customWidth="1" min="33" max="33"/>
-    <col width="4" customWidth="1" min="34" max="34"/>
-    <col width="4" customWidth="1" min="35" max="35"/>
+    <col width="5" customWidth="1" min="33" max="33"/>
+    <col width="5" customWidth="1" min="34" max="34"/>
+    <col width="5" customWidth="1" min="35" max="35"/>
     <col width="2" customWidth="1" min="36" max="36"/>
     <col width="15" customWidth="1" min="37" max="37"/>
     <col width="16" customWidth="1" min="38" max="38"/>
     <col width="6" customWidth="1" min="39" max="39"/>
     <col width="6" customWidth="1" min="40" max="40"/>
-    <col width="3" customWidth="1" min="41" max="41"/>
+    <col width="5" customWidth="1" min="41" max="41"/>
     <col width="4" customWidth="1" min="42" max="42"/>
     <col width="4" customWidth="1" min="43" max="43"/>
     <col width="4" customWidth="1" min="44" max="44"/>
@@ -902,167 +902,167 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>09-April-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>408</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>147</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>08-April-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>592</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>07-April-2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>284</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>37</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>06-April-2026</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
         <is>
           <t>03-April-2026</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>auth</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>612</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>597</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>02-April-2026</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
@@ -1104,184 +1104,184 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>09-April-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>336</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>08-April-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>07-April-2026</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
         <is>
           <t>06-April-2026</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
         <is>
           <t>03-April-2026</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
+      <c r="AL3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="AD3" t="inlineStr">
+      <c r="AM3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="AE3" t="inlineStr">
+      <c r="AN3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>02-April-2026</t>
-        </is>
-      </c>
-      <c r="AL3" t="inlineStr">
-        <is>
-          <t>idrepo</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>414</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>333</t>
-        </is>
-      </c>
       <c r="AO3" t="inlineStr">
         <is>
           <t>0</t>
@@ -1289,7 +1289,7 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
@@ -1306,167 +1306,167 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>09-April-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>930</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>08-April-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
         <is>
           <t>07-April-2026</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
         <is>
           <t>06-April-2026</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="AE4" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
         <is>
           <t>03-April-2026</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>masterdata-ara</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>930</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>02-April-2026</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
@@ -1508,167 +1508,167 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>09-April-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>08-April-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
         <is>
           <t>07-April-2026</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
         <is>
           <t>06-April-2026</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>509</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="AE5" t="inlineStr">
         <is>
           <t>350</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="AF5" t="inlineStr">
         <is>
           <t>116</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="AG5" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AK5" t="inlineStr">
         <is>
           <t>03-April-2026</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>masterdata-eng</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>02-April-2026</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
@@ -1710,167 +1710,167 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>09-April-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>930</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>08-April-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
         <is>
           <t>07-April-2026</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
         <is>
           <t>06-April-2026</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="AE6" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
+      <c r="AI6" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AK6" t="inlineStr">
         <is>
           <t>03-April-2026</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>masterdata-fra</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>930</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>02-April-2026</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
@@ -1912,192 +1912,192 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>09-April-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>509</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>496</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>08-April-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>509</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>496</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>07-April-2026</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>509</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>495</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>06-April-2026</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>209</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
         <is>
           <t>152</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="AG7" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AK7" t="inlineStr">
         <is>
           <t>03-April-2026</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
+      <c r="AL7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="AD7" t="inlineStr">
+      <c r="AM7" t="inlineStr">
         <is>
           <t>509</t>
         </is>
       </c>
-      <c r="AE7" t="inlineStr">
+      <c r="AN7" t="inlineStr">
         <is>
           <t>350</t>
         </is>
       </c>
-      <c r="AF7" t="inlineStr">
+      <c r="AO7" t="inlineStr">
         <is>
           <t>116</t>
         </is>
       </c>
-      <c r="AG7" t="inlineStr">
+      <c r="AP7" t="inlineStr">
         <is>
           <t>31</t>
-        </is>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>02-April-2026</t>
-        </is>
-      </c>
-      <c r="AL7" t="inlineStr">
-        <is>
-          <t>partner</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>509</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>495</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AP7" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
@@ -2114,151 +2114,151 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>09-April-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>08-April-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>07-April-2026</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="S8" t="n">
+      <c r="AB8" t="n">
         <v/>
       </c>
-      <c r="T8" t="n">
+      <c r="AC8" t="n">
         <v/>
       </c>
-      <c r="U8" t="n">
+      <c r="AD8" t="n">
         <v/>
       </c>
-      <c r="V8" t="n">
+      <c r="AE8" t="n">
         <v/>
       </c>
-      <c r="W8" t="n">
+      <c r="AF8" t="n">
         <v/>
       </c>
-      <c r="X8" t="n">
+      <c r="AG8" t="n">
         <v/>
       </c>
-      <c r="Y8" t="n">
+      <c r="AH8" t="n">
         <v/>
       </c>
-      <c r="Z8" t="n">
+      <c r="AI8" t="n">
         <v/>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AK8" t="inlineStr">
         <is>
           <t>03-April-2026</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="AD8" t="inlineStr">
-        <is>
-          <t>288</t>
-        </is>
-      </c>
-      <c r="AE8" t="inlineStr">
-        <is>
-          <t>282</t>
-        </is>
-      </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>02-April-2026</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
@@ -2300,176 +2300,176 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>09-April-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>resident</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1142</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>1135</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>08-April-2026</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>1139</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
         <is>
           <t>07-April-2026</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>1139</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S9" t="n">
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB9" t="n">
         <v/>
       </c>
-      <c r="T9" t="n">
+      <c r="AC9" t="n">
         <v/>
       </c>
-      <c r="U9" t="n">
+      <c r="AD9" t="n">
         <v/>
       </c>
-      <c r="V9" t="n">
+      <c r="AE9" t="n">
         <v/>
       </c>
-      <c r="W9" t="n">
+      <c r="AF9" t="n">
         <v/>
       </c>
-      <c r="X9" t="n">
+      <c r="AG9" t="n">
         <v/>
       </c>
-      <c r="Y9" t="n">
+      <c r="AH9" t="n">
         <v/>
       </c>
-      <c r="Z9" t="n">
+      <c r="AI9" t="n">
         <v/>
       </c>
-      <c r="AB9" t="inlineStr">
+      <c r="AK9" t="inlineStr">
         <is>
           <t>03-April-2026</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
+      <c r="AL9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="AD9" t="inlineStr">
+      <c r="AM9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="AE9" t="inlineStr">
+      <c r="AN9" t="inlineStr">
         <is>
           <t>1136</t>
         </is>
       </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG9" t="inlineStr">
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
         <is>
           <t>6</t>
-        </is>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>02-April-2026</t>
-        </is>
-      </c>
-      <c r="AL9" t="inlineStr">
-        <is>
-          <t>resident</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>1142</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>1140</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AP9" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
@@ -2486,176 +2486,176 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>09-April-2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>dsl</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>178</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>08-April-2026</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>209</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>163</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>07-April-2026</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>209</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>178</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="S10" t="n">
+      <c r="AB10" t="n">
         <v/>
       </c>
-      <c r="T10" t="n">
+      <c r="AC10" t="n">
         <v/>
       </c>
-      <c r="U10" t="n">
+      <c r="AD10" t="n">
         <v/>
       </c>
-      <c r="V10" t="n">
+      <c r="AE10" t="n">
         <v/>
       </c>
-      <c r="W10" t="n">
+      <c r="AF10" t="n">
         <v/>
       </c>
-      <c r="X10" t="n">
+      <c r="AG10" t="n">
         <v/>
       </c>
-      <c r="Y10" t="n">
+      <c r="AH10" t="n">
         <v/>
       </c>
-      <c r="Z10" t="n">
+      <c r="AI10" t="n">
         <v/>
       </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AK10" t="inlineStr">
         <is>
           <t>03-April-2026</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
+      <c r="AL10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="AD10" t="inlineStr">
+      <c r="AM10" t="inlineStr">
         <is>
           <t>209</t>
         </is>
       </c>
-      <c r="AE10" t="inlineStr">
+      <c r="AN10" t="inlineStr">
         <is>
           <t>163</t>
         </is>
       </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG10" t="inlineStr">
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AP10" t="inlineStr">
         <is>
           <t>16</t>
-        </is>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>02-April-2026</t>
-        </is>
-      </c>
-      <c r="AL10" t="inlineStr">
-        <is>
-          <t>dsl</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>209</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>138</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AP10" t="inlineStr">
-        <is>
-          <t>41</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">

--- a/minio-report-tracker/xlxs/dev01.xlsx
+++ b/minio-report-tracker/xlxs/dev01.xlsx
@@ -655,7 +655,7 @@
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="6" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
-    <col width="5" customWidth="1" min="5" max="5"/>
+    <col width="3" customWidth="1" min="5" max="5"/>
     <col width="4" customWidth="1" min="6" max="6"/>
     <col width="4" customWidth="1" min="7" max="7"/>
     <col width="4" customWidth="1" min="8" max="8"/>
@@ -664,7 +664,7 @@
     <col width="16" customWidth="1" min="11" max="11"/>
     <col width="6" customWidth="1" min="12" max="12"/>
     <col width="6" customWidth="1" min="13" max="13"/>
-    <col width="3" customWidth="1" min="14" max="14"/>
+    <col width="5" customWidth="1" min="14" max="14"/>
     <col width="4" customWidth="1" min="15" max="15"/>
     <col width="4" customWidth="1" min="16" max="16"/>
     <col width="4" customWidth="1" min="17" max="17"/>
@@ -673,28 +673,28 @@
     <col width="16" customWidth="1" min="20" max="20"/>
     <col width="6" customWidth="1" min="21" max="21"/>
     <col width="6" customWidth="1" min="22" max="22"/>
-    <col width="5" customWidth="1" min="23" max="23"/>
+    <col width="3" customWidth="1" min="23" max="23"/>
     <col width="4" customWidth="1" min="24" max="24"/>
     <col width="4" customWidth="1" min="25" max="25"/>
     <col width="4" customWidth="1" min="26" max="26"/>
     <col width="2" customWidth="1" min="27" max="27"/>
     <col width="15" customWidth="1" min="28" max="28"/>
     <col width="16" customWidth="1" min="29" max="29"/>
-    <col width="5" customWidth="1" min="30" max="30"/>
-    <col width="5" customWidth="1" min="31" max="31"/>
+    <col width="6" customWidth="1" min="30" max="30"/>
+    <col width="6" customWidth="1" min="31" max="31"/>
     <col width="5" customWidth="1" min="32" max="32"/>
-    <col width="5" customWidth="1" min="33" max="33"/>
-    <col width="5" customWidth="1" min="34" max="34"/>
-    <col width="5" customWidth="1" min="35" max="35"/>
+    <col width="4" customWidth="1" min="33" max="33"/>
+    <col width="4" customWidth="1" min="34" max="34"/>
+    <col width="4" customWidth="1" min="35" max="35"/>
     <col width="2" customWidth="1" min="36" max="36"/>
     <col width="15" customWidth="1" min="37" max="37"/>
     <col width="16" customWidth="1" min="38" max="38"/>
-    <col width="6" customWidth="1" min="39" max="39"/>
-    <col width="6" customWidth="1" min="40" max="40"/>
+    <col width="5" customWidth="1" min="39" max="39"/>
+    <col width="5" customWidth="1" min="40" max="40"/>
     <col width="5" customWidth="1" min="41" max="41"/>
-    <col width="4" customWidth="1" min="42" max="42"/>
-    <col width="4" customWidth="1" min="43" max="43"/>
-    <col width="4" customWidth="1" min="44" max="44"/>
+    <col width="5" customWidth="1" min="42" max="42"/>
+    <col width="5" customWidth="1" min="43" max="43"/>
+    <col width="5" customWidth="1" min="44" max="44"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -902,386 +902,386 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>10-April-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>597</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>09-April-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>408</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>147</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>43</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>08-April-2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>592</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>07-April-2026</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
         <is>
           <t>284</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="AG2" t="inlineStr">
         <is>
           <t>37</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AK2" t="inlineStr">
         <is>
           <t>06-April-2026</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AL2" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AM2" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
+      <c r="AN2" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>03-April-2026</t>
-        </is>
-      </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>auth</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>612</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>597</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>10-April-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>336</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>09-April-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>08-April-2026</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
         <is>
           <t>07-April-2026</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
         <is>
           <t>06-April-2026</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
+      <c r="AL3" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="AD3" t="inlineStr">
+      <c r="AM3" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="AE3" t="inlineStr">
+      <c r="AN3" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>03-April-2026</t>
-        </is>
-      </c>
-      <c r="AL3" t="inlineStr">
-        <is>
-          <t>idrepo</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>414</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>336</t>
-        </is>
-      </c>
       <c r="AO3" t="inlineStr">
         <is>
           <t>0</t>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
@@ -1306,172 +1306,172 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>10-April-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>930</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>09-April-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
         <is>
           <t>08-April-2026</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
         <is>
           <t>07-April-2026</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="AE4" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
         <is>
           <t>06-April-2026</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
+      <c r="AL4" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>930</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>03-April-2026</t>
-        </is>
-      </c>
-      <c r="AL4" t="inlineStr">
-        <is>
-          <t>masterdata-ara</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
@@ -1508,1165 +1508,1165 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>10-April-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>09-April-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
         <is>
           <t>08-April-2026</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
         <is>
           <t>07-April-2026</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="AE5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
         <is>
           <t>06-April-2026</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
+      <c r="AL5" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="AD5" t="inlineStr">
+      <c r="AM5" t="inlineStr">
         <is>
           <t>509</t>
         </is>
       </c>
-      <c r="AE5" t="inlineStr">
+      <c r="AN5" t="inlineStr">
         <is>
           <t>350</t>
         </is>
       </c>
-      <c r="AF5" t="inlineStr">
+      <c r="AO5" t="inlineStr">
         <is>
           <t>116</t>
         </is>
       </c>
-      <c r="AG5" t="inlineStr">
+      <c r="AP5" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
         <is>
           <t>12</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>03-April-2026</t>
-        </is>
-      </c>
-      <c r="AL5" t="inlineStr">
-        <is>
-          <t>masterdata-eng</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AP5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>10-April-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>930</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>09-April-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
         <is>
           <t>08-April-2026</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
         <is>
           <t>07-April-2026</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="AE6" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
         <is>
           <t>06-April-2026</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
+      <c r="AL6" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="AD6" t="inlineStr">
+      <c r="AM6" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="AE6" t="inlineStr">
+      <c r="AN6" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH6" t="inlineStr">
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AI6" t="inlineStr">
+      <c r="AR6" t="inlineStr">
         <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>03-April-2026</t>
-        </is>
-      </c>
-      <c r="AL6" t="inlineStr">
-        <is>
-          <t>masterdata-fra</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>930</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AP6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ6" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>10-April-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>509</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>495</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>09-April-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>509</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>496</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>08-April-2026</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>509</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>496</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>07-April-2026</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>509</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="AE7" t="inlineStr">
         <is>
           <t>495</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AK7" t="inlineStr">
         <is>
           <t>06-April-2026</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
+      <c r="AL7" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="AD7" t="inlineStr">
+      <c r="AM7" t="inlineStr">
         <is>
           <t>209</t>
         </is>
       </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr">
+      <c r="AN7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
         <is>
           <t>152</t>
         </is>
       </c>
-      <c r="AG7" t="inlineStr">
+      <c r="AP7" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
         <is>
           <t>30</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>03-April-2026</t>
-        </is>
-      </c>
-      <c r="AL7" t="inlineStr">
-        <is>
-          <t>partner</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>509</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>350</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
-      <c r="AP7" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="AQ7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>12</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>10-April-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>09-April-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>08-April-2026</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>07-April-2026</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="AD8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="AE8" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="AI8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AB8" t="n">
+      <c r="AK8" t="n">
         <v/>
       </c>
-      <c r="AC8" t="n">
+      <c r="AL8" t="n">
         <v/>
       </c>
-      <c r="AD8" t="n">
+      <c r="AM8" t="n">
         <v/>
       </c>
-      <c r="AE8" t="n">
+      <c r="AN8" t="n">
         <v/>
       </c>
-      <c r="AF8" t="n">
+      <c r="AO8" t="n">
         <v/>
       </c>
-      <c r="AG8" t="n">
+      <c r="AP8" t="n">
         <v/>
       </c>
-      <c r="AH8" t="n">
+      <c r="AQ8" t="n">
         <v/>
       </c>
-      <c r="AI8" t="n">
+      <c r="AR8" t="n">
         <v/>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>03-April-2026</t>
-        </is>
-      </c>
-      <c r="AL8" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>288</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>282</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AP8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>10-April-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>resident</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1142</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>1119</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>09-April-2026</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>1135</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
         <is>
           <t>08-April-2026</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>1139</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
         <is>
           <t>07-April-2026</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="AC9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="AD9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="AE9" t="inlineStr">
         <is>
           <t>1139</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB9" t="n">
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK9" t="n">
         <v/>
       </c>
-      <c r="AC9" t="n">
+      <c r="AL9" t="n">
         <v/>
       </c>
-      <c r="AD9" t="n">
+      <c r="AM9" t="n">
         <v/>
       </c>
-      <c r="AE9" t="n">
+      <c r="AN9" t="n">
         <v/>
       </c>
-      <c r="AF9" t="n">
+      <c r="AO9" t="n">
         <v/>
       </c>
-      <c r="AG9" t="n">
+      <c r="AP9" t="n">
         <v/>
       </c>
-      <c r="AH9" t="n">
+      <c r="AQ9" t="n">
         <v/>
       </c>
-      <c r="AI9" t="n">
+      <c r="AR9" t="n">
         <v/>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>03-April-2026</t>
-        </is>
-      </c>
-      <c r="AL9" t="inlineStr">
-        <is>
-          <t>resident</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>1142</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>1136</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AP9" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AQ9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>10-April-2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>dsl</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>148</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>09-April-2026</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>209</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>178</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>08-April-2026</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>209</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>163</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="AB10" t="inlineStr">
         <is>
           <t>07-April-2026</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="AC10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="AD10" t="inlineStr">
         <is>
           <t>209</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="AE10" t="inlineStr">
         <is>
           <t>178</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="AB10" t="n">
+      <c r="AK10" t="n">
         <v/>
       </c>
-      <c r="AC10" t="n">
+      <c r="AL10" t="n">
         <v/>
       </c>
-      <c r="AD10" t="n">
+      <c r="AM10" t="n">
         <v/>
       </c>
-      <c r="AE10" t="n">
+      <c r="AN10" t="n">
         <v/>
       </c>
-      <c r="AF10" t="n">
+      <c r="AO10" t="n">
         <v/>
       </c>
-      <c r="AG10" t="n">
+      <c r="AP10" t="n">
         <v/>
       </c>
-      <c r="AH10" t="n">
+      <c r="AQ10" t="n">
         <v/>
       </c>
-      <c r="AI10" t="n">
+      <c r="AR10" t="n">
         <v/>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>03-April-2026</t>
-        </is>
-      </c>
-      <c r="AL10" t="inlineStr">
-        <is>
-          <t>dsl</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>209</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>163</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AP10" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AQ10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR10" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
       </c>
     </row>
   </sheetData>

--- a/minio-report-tracker/xlxs/dev01.xlsx
+++ b/minio-report-tracker/xlxs/dev01.xlsx
@@ -655,7 +655,7 @@
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="6" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
-    <col width="3" customWidth="1" min="5" max="5"/>
+    <col width="5" customWidth="1" min="5" max="5"/>
     <col width="4" customWidth="1" min="6" max="6"/>
     <col width="4" customWidth="1" min="7" max="7"/>
     <col width="4" customWidth="1" min="8" max="8"/>
@@ -664,7 +664,7 @@
     <col width="16" customWidth="1" min="11" max="11"/>
     <col width="6" customWidth="1" min="12" max="12"/>
     <col width="6" customWidth="1" min="13" max="13"/>
-    <col width="5" customWidth="1" min="14" max="14"/>
+    <col width="3" customWidth="1" min="14" max="14"/>
     <col width="4" customWidth="1" min="15" max="15"/>
     <col width="4" customWidth="1" min="16" max="16"/>
     <col width="4" customWidth="1" min="17" max="17"/>
@@ -673,7 +673,7 @@
     <col width="16" customWidth="1" min="20" max="20"/>
     <col width="6" customWidth="1" min="21" max="21"/>
     <col width="6" customWidth="1" min="22" max="22"/>
-    <col width="3" customWidth="1" min="23" max="23"/>
+    <col width="5" customWidth="1" min="23" max="23"/>
     <col width="4" customWidth="1" min="24" max="24"/>
     <col width="4" customWidth="1" min="25" max="25"/>
     <col width="4" customWidth="1" min="26" max="26"/>
@@ -682,19 +682,19 @@
     <col width="16" customWidth="1" min="29" max="29"/>
     <col width="6" customWidth="1" min="30" max="30"/>
     <col width="6" customWidth="1" min="31" max="31"/>
-    <col width="5" customWidth="1" min="32" max="32"/>
+    <col width="3" customWidth="1" min="32" max="32"/>
     <col width="4" customWidth="1" min="33" max="33"/>
     <col width="4" customWidth="1" min="34" max="34"/>
     <col width="4" customWidth="1" min="35" max="35"/>
     <col width="2" customWidth="1" min="36" max="36"/>
     <col width="15" customWidth="1" min="37" max="37"/>
     <col width="16" customWidth="1" min="38" max="38"/>
-    <col width="5" customWidth="1" min="39" max="39"/>
-    <col width="5" customWidth="1" min="40" max="40"/>
+    <col width="6" customWidth="1" min="39" max="39"/>
+    <col width="6" customWidth="1" min="40" max="40"/>
     <col width="5" customWidth="1" min="41" max="41"/>
-    <col width="5" customWidth="1" min="42" max="42"/>
-    <col width="5" customWidth="1" min="43" max="43"/>
-    <col width="5" customWidth="1" min="44" max="44"/>
+    <col width="4" customWidth="1" min="42" max="42"/>
+    <col width="4" customWidth="1" min="43" max="43"/>
+    <col width="4" customWidth="1" min="44" max="44"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -902,399 +902,399 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>13-April-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>597</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>10-April-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>597</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>09-April-2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>408</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>147</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>43</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>08-April-2026</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>592</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="AH2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AI2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AK2" t="inlineStr">
         <is>
           <t>07-April-2026</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AL2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AM2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
+      <c r="AN2" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="AF2" t="inlineStr">
+      <c r="AO2" t="inlineStr">
         <is>
           <t>284</t>
         </is>
       </c>
-      <c r="AG2" t="inlineStr">
+      <c r="AP2" t="inlineStr">
         <is>
           <t>37</t>
         </is>
       </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
         <is>
           <t>9</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>06-April-2026</t>
-        </is>
-      </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>masterdata-ara</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>930</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>13-April-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>336</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>10-April-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>09-April-2026</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
         <is>
           <t>08-April-2026</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
         <is>
           <t>07-April-2026</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
+      <c r="AL3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="AD3" t="inlineStr">
+      <c r="AM3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="AE3" t="inlineStr">
+      <c r="AN3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
         <is>
           <t>78</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>06-April-2026</t>
-        </is>
-      </c>
-      <c r="AL3" t="inlineStr">
-        <is>
-          <t>masterdata-eng</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AP3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ3" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
@@ -1306,172 +1306,172 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>13-April-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>930</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>10-April-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
         <is>
           <t>09-April-2026</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
         <is>
           <t>08-April-2026</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="AE4" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
         <is>
           <t>07-April-2026</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
+      <c r="AL4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>930</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>06-April-2026</t>
-        </is>
-      </c>
-      <c r="AL4" t="inlineStr">
-        <is>
-          <t>masterdata-fra</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
@@ -1508,192 +1508,192 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>13-April-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>10-April-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
         <is>
           <t>09-April-2026</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
         <is>
           <t>08-April-2026</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="AE5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
         <is>
           <t>07-April-2026</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
+      <c r="AL5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="AD5" t="inlineStr">
+      <c r="AM5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="AE5" t="inlineStr">
+      <c r="AN5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>06-April-2026</t>
-        </is>
-      </c>
-      <c r="AL5" t="inlineStr">
-        <is>
-          <t>partner</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>509</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>350</t>
-        </is>
-      </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
@@ -1703,970 +1703,1018 @@
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>13-April-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>930</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>10-April-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
         <is>
           <t>09-April-2026</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
         <is>
           <t>08-April-2026</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="AE6" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
         <is>
           <t>07-April-2026</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
+      <c r="AL6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="AD6" t="inlineStr">
+      <c r="AM6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="AE6" t="inlineStr">
+      <c r="AN6" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH6" t="inlineStr">
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>06-April-2026</t>
-        </is>
-      </c>
-      <c r="AL6" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>288</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>282</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AP6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>13-April-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>509</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>350</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>10-April-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>509</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>495</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>09-April-2026</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>509</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>496</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>08-April-2026</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>509</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="AE7" t="inlineStr">
         <is>
           <t>496</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AK7" t="inlineStr">
         <is>
           <t>07-April-2026</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
+      <c r="AL7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="AD7" t="inlineStr">
+      <c r="AM7" t="inlineStr">
         <is>
           <t>509</t>
         </is>
       </c>
-      <c r="AE7" t="inlineStr">
+      <c r="AN7" t="inlineStr">
         <is>
           <t>495</t>
         </is>
       </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG7" t="inlineStr">
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
         <is>
           <t>12</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>06-April-2026</t>
-        </is>
-      </c>
-      <c r="AL7" t="inlineStr">
-        <is>
-          <t>dsl</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>209</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>152</t>
-        </is>
-      </c>
-      <c r="AP7" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="AQ7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>30</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>13-April-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>10-April-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>09-April-2026</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>08-April-2026</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="AD8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="AE8" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="AI8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AK8" t="inlineStr">
         <is>
           <t>07-April-2026</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
+      <c r="AL8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="AD8" t="inlineStr">
+      <c r="AM8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="AE8" t="inlineStr">
+      <c r="AN8" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH8" t="inlineStr">
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AI8" t="inlineStr">
+      <c r="AR8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
-      </c>
-      <c r="AK8" t="n">
-        <v/>
-      </c>
-      <c r="AL8" t="n">
-        <v/>
-      </c>
-      <c r="AM8" t="n">
-        <v/>
-      </c>
-      <c r="AN8" t="n">
-        <v/>
-      </c>
-      <c r="AO8" t="n">
-        <v/>
-      </c>
-      <c r="AP8" t="n">
-        <v/>
-      </c>
-      <c r="AQ8" t="n">
-        <v/>
-      </c>
-      <c r="AR8" t="n">
-        <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>13-April-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>resident</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1142</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>1119</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>10-April-2026</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>1119</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
         <is>
           <t>09-April-2026</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>1135</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
         <is>
           <t>08-April-2026</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="AC9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="AD9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="AE9" t="inlineStr">
         <is>
           <t>1139</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
         <is>
           <t>07-April-2026</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
+      <c r="AL9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="AD9" t="inlineStr">
+      <c r="AM9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="AE9" t="inlineStr">
+      <c r="AN9" t="inlineStr">
         <is>
           <t>1139</t>
         </is>
       </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG9" t="inlineStr">
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK9" t="n">
-        <v/>
-      </c>
-      <c r="AL9" t="n">
-        <v/>
-      </c>
-      <c r="AM9" t="n">
-        <v/>
-      </c>
-      <c r="AN9" t="n">
-        <v/>
-      </c>
-      <c r="AO9" t="n">
-        <v/>
-      </c>
-      <c r="AP9" t="n">
-        <v/>
-      </c>
-      <c r="AQ9" t="n">
-        <v/>
-      </c>
-      <c r="AR9" t="n">
-        <v/>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>13-April-2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>dsl</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>10-April-2026</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>209</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>148</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>09-April-2026</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>209</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>178</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="AB10" t="inlineStr">
         <is>
           <t>08-April-2026</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="AC10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="AD10" t="inlineStr">
         <is>
           <t>209</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="AE10" t="inlineStr">
         <is>
           <t>163</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AK10" t="inlineStr">
         <is>
           <t>07-April-2026</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
+      <c r="AL10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="AD10" t="inlineStr">
+      <c r="AM10" t="inlineStr">
         <is>
           <t>209</t>
         </is>
       </c>
-      <c r="AE10" t="inlineStr">
+      <c r="AN10" t="inlineStr">
         <is>
           <t>178</t>
         </is>
       </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG10" t="inlineStr">
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AP10" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
+      <c r="AQ10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
         <is>
           <t>30</t>
         </is>
-      </c>
-      <c r="AK10" t="n">
-        <v/>
-      </c>
-      <c r="AL10" t="n">
-        <v/>
-      </c>
-      <c r="AM10" t="n">
-        <v/>
-      </c>
-      <c r="AN10" t="n">
-        <v/>
-      </c>
-      <c r="AO10" t="n">
-        <v/>
-      </c>
-      <c r="AP10" t="n">
-        <v/>
-      </c>
-      <c r="AQ10" t="n">
-        <v/>
-      </c>
-      <c r="AR10" t="n">
-        <v/>
       </c>
     </row>
   </sheetData>

--- a/minio-report-tracker/xlxs/dev01.xlsx
+++ b/minio-report-tracker/xlxs/dev01.xlsx
@@ -664,7 +664,7 @@
     <col width="16" customWidth="1" min="11" max="11"/>
     <col width="6" customWidth="1" min="12" max="12"/>
     <col width="6" customWidth="1" min="13" max="13"/>
-    <col width="3" customWidth="1" min="14" max="14"/>
+    <col width="5" customWidth="1" min="14" max="14"/>
     <col width="4" customWidth="1" min="15" max="15"/>
     <col width="4" customWidth="1" min="16" max="16"/>
     <col width="4" customWidth="1" min="17" max="17"/>
@@ -673,7 +673,7 @@
     <col width="16" customWidth="1" min="20" max="20"/>
     <col width="6" customWidth="1" min="21" max="21"/>
     <col width="6" customWidth="1" min="22" max="22"/>
-    <col width="5" customWidth="1" min="23" max="23"/>
+    <col width="3" customWidth="1" min="23" max="23"/>
     <col width="4" customWidth="1" min="24" max="24"/>
     <col width="4" customWidth="1" min="25" max="25"/>
     <col width="4" customWidth="1" min="26" max="26"/>
@@ -682,7 +682,7 @@
     <col width="16" customWidth="1" min="29" max="29"/>
     <col width="6" customWidth="1" min="30" max="30"/>
     <col width="6" customWidth="1" min="31" max="31"/>
-    <col width="3" customWidth="1" min="32" max="32"/>
+    <col width="5" customWidth="1" min="32" max="32"/>
     <col width="4" customWidth="1" min="33" max="33"/>
     <col width="4" customWidth="1" min="34" max="34"/>
     <col width="4" customWidth="1" min="35" max="35"/>
@@ -691,7 +691,7 @@
     <col width="16" customWidth="1" min="38" max="38"/>
     <col width="6" customWidth="1" min="39" max="39"/>
     <col width="6" customWidth="1" min="40" max="40"/>
-    <col width="5" customWidth="1" min="41" max="41"/>
+    <col width="3" customWidth="1" min="41" max="41"/>
     <col width="4" customWidth="1" min="42" max="42"/>
     <col width="4" customWidth="1" min="43" max="43"/>
     <col width="4" customWidth="1" min="44" max="44"/>
@@ -902,197 +902,197 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>14-April-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>598</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>13-April-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>597</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>10-April-2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>597</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>09-April-2026</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>408</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
         <is>
           <t>147</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="AG2" t="inlineStr">
         <is>
           <t>43</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="AH2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AI2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AK2" t="inlineStr">
         <is>
           <t>08-April-2026</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AL2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AM2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
+      <c r="AN2" t="inlineStr">
         <is>
           <t>592</t>
         </is>
       </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AH2" t="inlineStr">
+      <c r="AQ2" t="inlineStr">
         <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>07-April-2026</t>
-        </is>
-      </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>auth</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>612</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>282</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>284</t>
-        </is>
-      </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
@@ -1104,167 +1104,167 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>14-April-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>336</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>13-April-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>10-April-2026</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
         <is>
           <t>09-April-2026</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
         <is>
           <t>08-April-2026</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>idrepo</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>414</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>336</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>07-April-2026</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
@@ -1306,167 +1306,167 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>14-April-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>930</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>13-April-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
         <is>
           <t>10-April-2026</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
         <is>
           <t>09-April-2026</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="AE4" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
         <is>
           <t>08-April-2026</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>masterdata-ara</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>930</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>07-April-2026</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
@@ -1508,167 +1508,167 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>14-April-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>13-April-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
         <is>
           <t>10-April-2026</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
         <is>
           <t>09-April-2026</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="AE5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
         <is>
           <t>08-April-2026</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>masterdata-eng</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>07-April-2026</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
@@ -1710,167 +1710,167 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>14-April-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>13-April-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
         <is>
           <t>10-April-2026</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
         <is>
           <t>09-April-2026</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="AE6" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
         <is>
           <t>08-April-2026</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>masterdata-fra</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>930</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>07-April-2026</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
@@ -1912,192 +1912,192 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>14-April-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>509</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>350</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>13-April-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>509</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>350</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>116</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>10-April-2026</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>509</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>495</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>09-April-2026</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>509</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="AE7" t="inlineStr">
         <is>
           <t>496</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AK7" t="inlineStr">
         <is>
           <t>08-April-2026</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
+      <c r="AL7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="AD7" t="inlineStr">
+      <c r="AM7" t="inlineStr">
         <is>
           <t>509</t>
         </is>
       </c>
-      <c r="AE7" t="inlineStr">
+      <c r="AN7" t="inlineStr">
         <is>
           <t>496</t>
         </is>
       </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG7" t="inlineStr">
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>07-April-2026</t>
-        </is>
-      </c>
-      <c r="AL7" t="inlineStr">
-        <is>
-          <t>partner</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>509</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>495</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AP7" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
@@ -2114,167 +2114,167 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>14-April-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>13-April-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>10-April-2026</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>09-April-2026</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="AD8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="AE8" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="AI8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AK8" t="inlineStr">
         <is>
           <t>08-April-2026</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="AD8" t="inlineStr">
-        <is>
-          <t>288</t>
-        </is>
-      </c>
-      <c r="AE8" t="inlineStr">
-        <is>
-          <t>282</t>
-        </is>
-      </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>07-April-2026</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
@@ -2316,167 +2316,167 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>14-April-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>resident</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1142</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>1139</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>13-April-2026</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>1119</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
         <is>
           <t>10-April-2026</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>1119</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
         <is>
           <t>09-April-2026</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="AC9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="AD9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="AE9" t="inlineStr">
         <is>
           <t>1135</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
         <is>
           <t>08-April-2026</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>resident</t>
-        </is>
-      </c>
-      <c r="AD9" t="inlineStr">
-        <is>
-          <t>1142</t>
-        </is>
-      </c>
-      <c r="AE9" t="inlineStr">
-        <is>
-          <t>1139</t>
-        </is>
-      </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG9" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>07-April-2026</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
@@ -2518,192 +2518,192 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>14-April-2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>dsl</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>13-April-2026</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>209</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>120</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>47</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>10-April-2026</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>209</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>148</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="X10" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="AB10" t="inlineStr">
         <is>
           <t>09-April-2026</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="AC10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="AD10" t="inlineStr">
         <is>
           <t>209</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="AE10" t="inlineStr">
         <is>
           <t>178</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AK10" t="inlineStr">
         <is>
           <t>08-April-2026</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
+      <c r="AL10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="AD10" t="inlineStr">
+      <c r="AM10" t="inlineStr">
         <is>
           <t>209</t>
         </is>
       </c>
-      <c r="AE10" t="inlineStr">
+      <c r="AN10" t="inlineStr">
         <is>
           <t>163</t>
         </is>
       </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG10" t="inlineStr">
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AP10" t="inlineStr">
         <is>
           <t>16</t>
-        </is>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>07-April-2026</t>
-        </is>
-      </c>
-      <c r="AL10" t="inlineStr">
-        <is>
-          <t>dsl</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>209</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>178</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AP10" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">

--- a/minio-report-tracker/xlxs/dev01.xlsx
+++ b/minio-report-tracker/xlxs/dev01.xlsx
@@ -673,7 +673,7 @@
     <col width="16" customWidth="1" min="20" max="20"/>
     <col width="6" customWidth="1" min="21" max="21"/>
     <col width="6" customWidth="1" min="22" max="22"/>
-    <col width="3" customWidth="1" min="23" max="23"/>
+    <col width="5" customWidth="1" min="23" max="23"/>
     <col width="4" customWidth="1" min="24" max="24"/>
     <col width="4" customWidth="1" min="25" max="25"/>
     <col width="4" customWidth="1" min="26" max="26"/>
@@ -682,7 +682,7 @@
     <col width="16" customWidth="1" min="29" max="29"/>
     <col width="6" customWidth="1" min="30" max="30"/>
     <col width="6" customWidth="1" min="31" max="31"/>
-    <col width="5" customWidth="1" min="32" max="32"/>
+    <col width="3" customWidth="1" min="32" max="32"/>
     <col width="4" customWidth="1" min="33" max="33"/>
     <col width="4" customWidth="1" min="34" max="34"/>
     <col width="4" customWidth="1" min="35" max="35"/>
@@ -691,7 +691,7 @@
     <col width="16" customWidth="1" min="38" max="38"/>
     <col width="6" customWidth="1" min="39" max="39"/>
     <col width="6" customWidth="1" min="40" max="40"/>
-    <col width="3" customWidth="1" min="41" max="41"/>
+    <col width="5" customWidth="1" min="41" max="41"/>
     <col width="4" customWidth="1" min="42" max="42"/>
     <col width="4" customWidth="1" min="43" max="43"/>
     <col width="4" customWidth="1" min="44" max="44"/>
@@ -902,192 +902,192 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>15-April-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>598</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>14-April-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>13-April-2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>597</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>10-April-2026</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>597</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="AH2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AI2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AK2" t="inlineStr">
         <is>
           <t>09-April-2026</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AL2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AM2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
+      <c r="AN2" t="inlineStr">
         <is>
           <t>408</t>
         </is>
       </c>
-      <c r="AF2" t="inlineStr">
+      <c r="AO2" t="inlineStr">
         <is>
           <t>147</t>
         </is>
       </c>
-      <c r="AG2" t="inlineStr">
+      <c r="AP2" t="inlineStr">
         <is>
           <t>43</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>08-April-2026</t>
-        </is>
-      </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>auth</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>612</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>592</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>6</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
@@ -1104,167 +1104,167 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>15-April-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>336</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>14-April-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>13-April-2026</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
         <is>
           <t>10-April-2026</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
         <is>
           <t>09-April-2026</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>idrepo</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>414</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>336</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>08-April-2026</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
@@ -1306,167 +1306,167 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>15-April-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>930</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>14-April-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
         <is>
           <t>13-April-2026</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
         <is>
           <t>10-April-2026</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="AE4" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
         <is>
           <t>09-April-2026</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>masterdata-ara</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>930</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>08-April-2026</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
@@ -1508,167 +1508,167 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>15-April-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>14-April-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
         <is>
           <t>13-April-2026</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
         <is>
           <t>10-April-2026</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="AE5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
         <is>
           <t>09-April-2026</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>masterdata-eng</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>08-April-2026</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
@@ -1710,167 +1710,167 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>15-April-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>930</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>14-April-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
         <is>
           <t>13-April-2026</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
         <is>
           <t>10-April-2026</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="AE6" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
         <is>
           <t>09-April-2026</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>masterdata-fra</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>930</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>08-April-2026</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
@@ -1912,167 +1912,167 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>15-April-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>509</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>350</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>14-April-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>509</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>350</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>116</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>13-April-2026</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>509</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>350</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>116</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>10-April-2026</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>509</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="AE7" t="inlineStr">
         <is>
           <t>495</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AK7" t="inlineStr">
         <is>
           <t>09-April-2026</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>partner</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>509</t>
-        </is>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>496</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>08-April-2026</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
@@ -2114,167 +2114,167 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>15-April-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>14-April-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>13-April-2026</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>10-April-2026</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="AD8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="AE8" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="AI8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AK8" t="inlineStr">
         <is>
           <t>09-April-2026</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="AD8" t="inlineStr">
-        <is>
-          <t>288</t>
-        </is>
-      </c>
-      <c r="AE8" t="inlineStr">
-        <is>
-          <t>282</t>
-        </is>
-      </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>08-April-2026</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
@@ -2316,192 +2316,192 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>15-April-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>resident</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1142</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>1139</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>14-April-2026</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>1139</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
         <is>
           <t>13-April-2026</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>1119</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
         <is>
           <t>10-April-2026</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="AC9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="AD9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="AE9" t="inlineStr">
         <is>
           <t>1119</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
         <is>
           <t>09-April-2026</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
+      <c r="AL9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="AD9" t="inlineStr">
+      <c r="AM9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="AE9" t="inlineStr">
+      <c r="AN9" t="inlineStr">
         <is>
           <t>1135</t>
         </is>
       </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG9" t="inlineStr">
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
         <is>
           <t>7</t>
-        </is>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>08-April-2026</t>
-        </is>
-      </c>
-      <c r="AL9" t="inlineStr">
-        <is>
-          <t>resident</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>1142</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>1139</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AP9" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
@@ -2518,192 +2518,192 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>15-April-2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>dsl</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>14-April-2026</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>209</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>127</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>44</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>13-April-2026</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>209</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>120</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="X10" t="inlineStr">
         <is>
           <t>47</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="AB10" t="inlineStr">
         <is>
           <t>10-April-2026</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="AC10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="AD10" t="inlineStr">
         <is>
           <t>209</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="AE10" t="inlineStr">
         <is>
           <t>148</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
+      <c r="AF10" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
+      <c r="AG10" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AK10" t="inlineStr">
         <is>
           <t>09-April-2026</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
+      <c r="AL10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="AD10" t="inlineStr">
+      <c r="AM10" t="inlineStr">
         <is>
           <t>209</t>
         </is>
       </c>
-      <c r="AE10" t="inlineStr">
+      <c r="AN10" t="inlineStr">
         <is>
           <t>178</t>
         </is>
       </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG10" t="inlineStr">
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AP10" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>08-April-2026</t>
-        </is>
-      </c>
-      <c r="AL10" t="inlineStr">
-        <is>
-          <t>dsl</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>209</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>163</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AP10" t="inlineStr">
-        <is>
-          <t>16</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">

--- a/minio-report-tracker/xlxs/dev01.xlsx
+++ b/minio-report-tracker/xlxs/dev01.xlsx
@@ -682,7 +682,7 @@
     <col width="16" customWidth="1" min="29" max="29"/>
     <col width="6" customWidth="1" min="30" max="30"/>
     <col width="6" customWidth="1" min="31" max="31"/>
-    <col width="3" customWidth="1" min="32" max="32"/>
+    <col width="5" customWidth="1" min="32" max="32"/>
     <col width="4" customWidth="1" min="33" max="33"/>
     <col width="4" customWidth="1" min="34" max="34"/>
     <col width="4" customWidth="1" min="35" max="35"/>
@@ -691,7 +691,7 @@
     <col width="16" customWidth="1" min="38" max="38"/>
     <col width="6" customWidth="1" min="39" max="39"/>
     <col width="6" customWidth="1" min="40" max="40"/>
-    <col width="5" customWidth="1" min="41" max="41"/>
+    <col width="3" customWidth="1" min="41" max="41"/>
     <col width="4" customWidth="1" min="42" max="42"/>
     <col width="4" customWidth="1" min="43" max="43"/>
     <col width="4" customWidth="1" min="44" max="44"/>
@@ -902,192 +902,192 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>16-April-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>598</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>15-April-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>14-April-2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>13-April-2026</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>597</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="AH2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AI2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AK2" t="inlineStr">
         <is>
           <t>10-April-2026</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AL2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AM2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
+      <c r="AN2" t="inlineStr">
         <is>
           <t>597</t>
         </is>
       </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>09-April-2026</t>
-        </is>
-      </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>auth</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>612</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>408</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>147</t>
-        </is>
-      </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>43</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
@@ -1104,167 +1104,167 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>16-April-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>336</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>15-April-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>14-April-2026</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
         <is>
           <t>13-April-2026</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
         <is>
           <t>10-April-2026</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>idrepo</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>414</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>336</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>09-April-2026</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
@@ -1306,167 +1306,167 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>16-April-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>15-April-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
         <is>
           <t>14-April-2026</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
         <is>
           <t>13-April-2026</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="AE4" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
         <is>
           <t>10-April-2026</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>masterdata-ara</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>930</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>09-April-2026</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
@@ -1508,167 +1508,167 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>16-April-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>944</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>15-April-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
         <is>
           <t>14-April-2026</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
         <is>
           <t>13-April-2026</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="AE5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
         <is>
           <t>10-April-2026</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>masterdata-eng</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>09-April-2026</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
@@ -1710,167 +1710,167 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>16-April-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>15-April-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
         <is>
           <t>14-April-2026</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
         <is>
           <t>13-April-2026</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="AE6" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
         <is>
           <t>10-April-2026</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>masterdata-fra</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>930</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>09-April-2026</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
@@ -1912,192 +1912,192 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>16-April-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>509</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>350</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>15-April-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>509</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>350</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>116</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>14-April-2026</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>509</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>350</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>116</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>13-April-2026</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>509</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="AE7" t="inlineStr">
         <is>
           <t>350</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="AF7" t="inlineStr">
         <is>
           <t>116</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="AG7" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AK7" t="inlineStr">
         <is>
           <t>10-April-2026</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
+      <c r="AL7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="AD7" t="inlineStr">
+      <c r="AM7" t="inlineStr">
         <is>
           <t>509</t>
         </is>
       </c>
-      <c r="AE7" t="inlineStr">
+      <c r="AN7" t="inlineStr">
         <is>
           <t>495</t>
         </is>
       </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG7" t="inlineStr">
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>09-April-2026</t>
-        </is>
-      </c>
-      <c r="AL7" t="inlineStr">
-        <is>
-          <t>partner</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>509</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>496</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AP7" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
@@ -2114,167 +2114,167 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>16-April-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>15-April-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>14-April-2026</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>13-April-2026</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="AD8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="AE8" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="AI8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AK8" t="inlineStr">
         <is>
           <t>10-April-2026</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="AD8" t="inlineStr">
-        <is>
-          <t>288</t>
-        </is>
-      </c>
-      <c r="AE8" t="inlineStr">
-        <is>
-          <t>282</t>
-        </is>
-      </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>09-April-2026</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
@@ -2316,192 +2316,192 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>16-April-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>resident</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1142</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>1142</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>15-April-2026</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>1139</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
         <is>
           <t>14-April-2026</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>1139</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
         <is>
           <t>13-April-2026</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="AC9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="AD9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="AE9" t="inlineStr">
         <is>
           <t>1119</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
         <is>
           <t>10-April-2026</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
+      <c r="AL9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="AD9" t="inlineStr">
+      <c r="AM9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="AE9" t="inlineStr">
+      <c r="AN9" t="inlineStr">
         <is>
           <t>1119</t>
         </is>
       </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG9" t="inlineStr">
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
         <is>
           <t>23</t>
-        </is>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>09-April-2026</t>
-        </is>
-      </c>
-      <c r="AL9" t="inlineStr">
-        <is>
-          <t>resident</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>1142</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>1135</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AP9" t="inlineStr">
-        <is>
-          <t>7</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
@@ -2518,192 +2518,192 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>16-April-2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>dsl</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>178</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>15-April-2026</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>14-April-2026</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>dsl</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
         <is>
           <t>209</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>112</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>14-April-2026</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>13-April-2026</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="AD10" t="inlineStr">
         <is>
           <t>209</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>127</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>13-April-2026</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>10-April-2026</t>
+        </is>
+      </c>
+      <c r="AL10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="AM10" t="inlineStr">
         <is>
           <t>209</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
+      <c r="AN10" t="inlineStr">
+        <is>
+          <t>148</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AP10" t="inlineStr">
         <is>
           <t>30</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>10-April-2026</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>dsl</t>
-        </is>
-      </c>
-      <c r="AD10" t="inlineStr">
-        <is>
-          <t>209</t>
-        </is>
-      </c>
-      <c r="AE10" t="inlineStr">
-        <is>
-          <t>148</t>
-        </is>
-      </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AG10" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>09-April-2026</t>
-        </is>
-      </c>
-      <c r="AL10" t="inlineStr">
-        <is>
-          <t>dsl</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>209</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>178</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AP10" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">

--- a/minio-report-tracker/xlxs/dev01.xlsx
+++ b/minio-report-tracker/xlxs/dev01.xlsx
@@ -691,7 +691,7 @@
     <col width="16" customWidth="1" min="38" max="38"/>
     <col width="6" customWidth="1" min="39" max="39"/>
     <col width="6" customWidth="1" min="40" max="40"/>
-    <col width="3" customWidth="1" min="41" max="41"/>
+    <col width="5" customWidth="1" min="41" max="41"/>
     <col width="4" customWidth="1" min="42" max="42"/>
     <col width="4" customWidth="1" min="43" max="43"/>
     <col width="4" customWidth="1" min="44" max="44"/>
@@ -902,167 +902,167 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>17-April-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>598</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>16-April-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>15-April-2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>14-April-2026</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AI2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AK2" t="inlineStr">
         <is>
           <t>13-April-2026</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>auth</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>612</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>597</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>10-April-2026</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
@@ -1104,167 +1104,167 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>17-April-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>336</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>16-April-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>15-April-2026</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
         <is>
           <t>14-April-2026</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
         <is>
           <t>13-April-2026</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>idrepo</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>414</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>336</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>10-April-2026</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
@@ -1306,167 +1306,167 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>17-April-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>16-April-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
         <is>
           <t>15-April-2026</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
         <is>
           <t>14-April-2026</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="AE4" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
         <is>
           <t>13-April-2026</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>masterdata-ara</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>930</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>10-April-2026</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
@@ -1508,167 +1508,167 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>17-April-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>944</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>16-April-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
         <is>
           <t>15-April-2026</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
         <is>
           <t>14-April-2026</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="AE5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
         <is>
           <t>13-April-2026</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>masterdata-eng</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>10-April-2026</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
@@ -1710,167 +1710,167 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>17-April-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>16-April-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
         <is>
           <t>15-April-2026</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
         <is>
           <t>14-April-2026</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="AE6" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
+      <c r="AH6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
         <is>
           <t>13-April-2026</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>masterdata-fra</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>930</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>10-April-2026</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
@@ -1912,192 +1912,192 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>17-April-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>509</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>350</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>16-April-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>509</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>350</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>116</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>15-April-2026</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>509</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>350</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>116</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>14-April-2026</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>509</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="AE7" t="inlineStr">
         <is>
           <t>350</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="AF7" t="inlineStr">
         <is>
           <t>116</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="AG7" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AK7" t="inlineStr">
         <is>
           <t>13-April-2026</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
+      <c r="AL7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="AD7" t="inlineStr">
+      <c r="AM7" t="inlineStr">
         <is>
           <t>509</t>
         </is>
       </c>
-      <c r="AE7" t="inlineStr">
+      <c r="AN7" t="inlineStr">
         <is>
           <t>350</t>
         </is>
       </c>
-      <c r="AF7" t="inlineStr">
+      <c r="AO7" t="inlineStr">
         <is>
           <t>116</t>
         </is>
       </c>
-      <c r="AG7" t="inlineStr">
+      <c r="AP7" t="inlineStr">
         <is>
           <t>31</t>
-        </is>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>10-April-2026</t>
-        </is>
-      </c>
-      <c r="AL7" t="inlineStr">
-        <is>
-          <t>partner</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>509</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>495</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AP7" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
@@ -2114,167 +2114,167 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>17-April-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>16-April-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>15-April-2026</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>14-April-2026</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="AD8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="AE8" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="AI8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AK8" t="inlineStr">
         <is>
           <t>13-April-2026</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="AD8" t="inlineStr">
-        <is>
-          <t>288</t>
-        </is>
-      </c>
-      <c r="AE8" t="inlineStr">
-        <is>
-          <t>282</t>
-        </is>
-      </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>10-April-2026</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
@@ -2316,167 +2316,167 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>17-April-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>resident</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1142</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>1141</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>16-April-2026</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
         <is>
           <t>15-April-2026</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>1139</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
         <is>
           <t>14-April-2026</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="AC9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="AD9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="AE9" t="inlineStr">
         <is>
           <t>1139</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
         <is>
           <t>13-April-2026</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>resident</t>
-        </is>
-      </c>
-      <c r="AD9" t="inlineStr">
-        <is>
-          <t>1142</t>
-        </is>
-      </c>
-      <c r="AE9" t="inlineStr">
-        <is>
-          <t>1119</t>
-        </is>
-      </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG9" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>10-April-2026</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
@@ -2518,192 +2518,192 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>17-April-2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>dsl</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>191</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>16-April-2026</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>178</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
         <is>
           <t>15-April-2026</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>180</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="X10" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
         <is>
           <t>14-April-2026</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="AC10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="AD10" t="inlineStr">
         <is>
           <t>209</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="AE10" t="inlineStr">
         <is>
           <t>127</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
+      <c r="AF10" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
+      <c r="AG10" t="inlineStr">
         <is>
           <t>44</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AK10" t="inlineStr">
         <is>
           <t>13-April-2026</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
+      <c r="AL10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="AD10" t="inlineStr">
+      <c r="AM10" t="inlineStr">
         <is>
           <t>209</t>
         </is>
       </c>
-      <c r="AE10" t="inlineStr">
+      <c r="AN10" t="inlineStr">
         <is>
           <t>120</t>
         </is>
       </c>
-      <c r="AF10" t="inlineStr">
+      <c r="AO10" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="AG10" t="inlineStr">
+      <c r="AP10" t="inlineStr">
         <is>
           <t>47</t>
-        </is>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>10-April-2026</t>
-        </is>
-      </c>
-      <c r="AL10" t="inlineStr">
-        <is>
-          <t>dsl</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>209</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>148</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AP10" t="inlineStr">
-        <is>
-          <t>30</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">

--- a/minio-report-tracker/xlxs/dev01.xlsx
+++ b/minio-report-tracker/xlxs/dev01.xlsx
@@ -902,184 +902,184 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>20-April-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>597</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>17-April-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>16-April-2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>15-April-2026</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AI2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AK2" t="inlineStr">
         <is>
           <t>14-April-2026</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AL2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AM2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
+      <c r="AN2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>13-April-2026</t>
-        </is>
-      </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>auth</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>612</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>597</t>
-        </is>
-      </c>
       <c r="AO2" t="inlineStr">
         <is>
           <t>0</t>
@@ -1087,7 +1087,7 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
@@ -1104,167 +1104,167 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>20-April-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>336</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>17-April-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>16-April-2026</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
         <is>
           <t>15-April-2026</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
         <is>
           <t>14-April-2026</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>idrepo</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>414</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>336</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>13-April-2026</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
@@ -1306,167 +1306,167 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>20-April-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>17-April-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
         <is>
           <t>16-April-2026</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
         <is>
           <t>15-April-2026</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="AE4" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
         <is>
           <t>14-April-2026</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>masterdata-ara</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>930</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>13-April-2026</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
@@ -1508,167 +1508,167 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>20-April-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>944</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>17-April-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
         <is>
           <t>16-April-2026</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
         <is>
           <t>15-April-2026</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="AE5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
         <is>
           <t>14-April-2026</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>masterdata-eng</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>13-April-2026</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
@@ -1710,192 +1710,192 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>20-April-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>17-April-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
         <is>
           <t>16-April-2026</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
         <is>
           <t>15-April-2026</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="AE6" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
         <is>
           <t>14-April-2026</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
+      <c r="AL6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="AD6" t="inlineStr">
+      <c r="AM6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="AE6" t="inlineStr">
+      <c r="AN6" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG6" t="inlineStr">
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>13-April-2026</t>
-        </is>
-      </c>
-      <c r="AL6" t="inlineStr">
-        <is>
-          <t>masterdata-fra</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>930</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AP6" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
@@ -1912,167 +1912,167 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>20-April-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>509</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>350</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>17-April-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>509</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>350</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>116</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>16-April-2026</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>509</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>350</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>116</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>15-April-2026</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>509</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="AE7" t="inlineStr">
         <is>
           <t>350</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="AF7" t="inlineStr">
         <is>
           <t>116</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="AG7" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AK7" t="inlineStr">
         <is>
           <t>14-April-2026</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>partner</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>509</t>
-        </is>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>350</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
-      <c r="AG7" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>13-April-2026</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
@@ -2114,167 +2114,167 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>20-April-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>17-April-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>16-April-2026</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>15-April-2026</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="AD8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="AE8" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="AI8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AK8" t="inlineStr">
         <is>
           <t>14-April-2026</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="AD8" t="inlineStr">
-        <is>
-          <t>288</t>
-        </is>
-      </c>
-      <c r="AE8" t="inlineStr">
-        <is>
-          <t>282</t>
-        </is>
-      </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>13-April-2026</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
@@ -2316,192 +2316,192 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>20-April-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>resident</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1142</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>1142</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>17-April-2026</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>1141</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
         <is>
           <t>16-April-2026</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
         <is>
           <t>15-April-2026</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="AC9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="AD9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="AE9" t="inlineStr">
         <is>
           <t>1139</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
         <is>
           <t>14-April-2026</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
+      <c r="AL9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="AD9" t="inlineStr">
+      <c r="AM9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="AE9" t="inlineStr">
+      <c r="AN9" t="inlineStr">
         <is>
           <t>1139</t>
         </is>
       </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG9" t="inlineStr">
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
         <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>13-April-2026</t>
-        </is>
-      </c>
-      <c r="AL9" t="inlineStr">
-        <is>
-          <t>resident</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>1142</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>1119</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AP9" t="inlineStr">
-        <is>
-          <t>23</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
@@ -2518,192 +2518,192 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>20-April-2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>dsl</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>186</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>17-April-2026</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>191</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
         <is>
           <t>16-April-2026</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>178</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="X10" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
         <is>
           <t>15-April-2026</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="AC10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="AD10" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="AE10" t="inlineStr">
         <is>
           <t>180</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
+      <c r="AF10" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
+      <c r="AG10" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
         <is>
           <t>14-April-2026</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
+      <c r="AL10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="AD10" t="inlineStr">
+      <c r="AM10" t="inlineStr">
         <is>
           <t>209</t>
         </is>
       </c>
-      <c r="AE10" t="inlineStr">
+      <c r="AN10" t="inlineStr">
         <is>
           <t>127</t>
         </is>
       </c>
-      <c r="AF10" t="inlineStr">
+      <c r="AO10" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="AG10" t="inlineStr">
+      <c r="AP10" t="inlineStr">
         <is>
           <t>44</t>
-        </is>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>13-April-2026</t>
-        </is>
-      </c>
-      <c r="AL10" t="inlineStr">
-        <is>
-          <t>dsl</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>209</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AP10" t="inlineStr">
-        <is>
-          <t>47</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">

--- a/minio-report-tracker/xlxs/dev01.xlsx
+++ b/minio-report-tracker/xlxs/dev01.xlsx
@@ -902,167 +902,167 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>21-April-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>592</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>20-April-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>597</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>17-April-2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>16-April-2026</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AI2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AK2" t="inlineStr">
         <is>
           <t>15-April-2026</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>auth</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>612</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>598</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>14-April-2026</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
@@ -1104,167 +1104,167 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>21-April-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>336</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>20-April-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>17-April-2026</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
         <is>
           <t>16-April-2026</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
         <is>
           <t>15-April-2026</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>idrepo</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>414</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>336</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>14-April-2026</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
@@ -1306,167 +1306,167 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>21-April-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>20-April-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
         <is>
           <t>17-April-2026</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
         <is>
           <t>16-April-2026</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="AE4" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
+      <c r="AH4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
         <is>
           <t>15-April-2026</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>masterdata-ara</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>930</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>14-April-2026</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
@@ -1508,167 +1508,167 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>21-April-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>944</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>20-April-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
         <is>
           <t>17-April-2026</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
         <is>
           <t>16-April-2026</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="AE5" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
         <is>
           <t>15-April-2026</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>masterdata-eng</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>14-April-2026</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
@@ -1710,184 +1710,184 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>21-April-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>20-April-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
         <is>
           <t>17-April-2026</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
         <is>
           <t>16-April-2026</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="AE6" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
+      <c r="AH6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
         <is>
           <t>15-April-2026</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
+      <c r="AL6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="AD6" t="inlineStr">
+      <c r="AM6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="AE6" t="inlineStr">
+      <c r="AN6" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>14-April-2026</t>
-        </is>
-      </c>
-      <c r="AL6" t="inlineStr">
-        <is>
-          <t>masterdata-fra</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
       <c r="AO6" t="inlineStr">
         <is>
           <t>0</t>
@@ -1895,7 +1895,7 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
@@ -1912,167 +1912,167 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>21-April-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>509</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>350</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>20-April-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>509</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>350</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>116</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>17-April-2026</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>509</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>350</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>116</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>16-April-2026</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>509</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="AE7" t="inlineStr">
         <is>
           <t>350</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="AF7" t="inlineStr">
         <is>
           <t>116</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="AG7" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AK7" t="inlineStr">
         <is>
           <t>15-April-2026</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>partner</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>509</t>
-        </is>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>350</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
-      <c r="AG7" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>14-April-2026</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
@@ -2114,167 +2114,167 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>21-April-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>20-April-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>17-April-2026</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>16-April-2026</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="AD8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="AE8" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="AI8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AK8" t="inlineStr">
         <is>
           <t>15-April-2026</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="AD8" t="inlineStr">
-        <is>
-          <t>288</t>
-        </is>
-      </c>
-      <c r="AE8" t="inlineStr">
-        <is>
-          <t>282</t>
-        </is>
-      </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>14-April-2026</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
@@ -2316,167 +2316,167 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>21-April-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>resident</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1142</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>1141</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>20-April-2026</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
         <is>
           <t>17-April-2026</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>1141</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
         <is>
           <t>16-April-2026</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="AC9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="AD9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="AE9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
         <is>
           <t>15-April-2026</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>resident</t>
-        </is>
-      </c>
-      <c r="AD9" t="inlineStr">
-        <is>
-          <t>1142</t>
-        </is>
-      </c>
-      <c r="AE9" t="inlineStr">
-        <is>
-          <t>1139</t>
-        </is>
-      </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG9" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>14-April-2026</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
@@ -2518,194 +2518,194 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>21-April-2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>dsl</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>173</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>20-April-2026</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>186</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
         <is>
           <t>17-April-2026</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>191</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
         <is>
           <t>16-April-2026</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="AC10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="AD10" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="AE10" t="inlineStr">
         <is>
           <t>178</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
+      <c r="AF10" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
+      <c r="AG10" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
         <is>
           <t>15-April-2026</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
+      <c r="AL10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="AD10" t="inlineStr">
+      <c r="AM10" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="AE10" t="inlineStr">
+      <c r="AN10" t="inlineStr">
         <is>
           <t>180</t>
         </is>
       </c>
-      <c r="AF10" t="inlineStr">
+      <c r="AO10" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="AG10" t="inlineStr">
+      <c r="AP10" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>14-April-2026</t>
-        </is>
-      </c>
-      <c r="AL10" t="inlineStr">
-        <is>
-          <t>dsl</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>209</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>127</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AP10" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
       <c r="AQ10" t="inlineStr">
         <is>
           <t>0</t>
@@ -2713,7 +2713,7 @@
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>0</t>
         </is>
       </c>
     </row>

--- a/minio-report-tracker/xlxs/dev01.xlsx
+++ b/minio-report-tracker/xlxs/dev01.xlsx
@@ -902,167 +902,167 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>22-April-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>597</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>21-April-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>592</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>20-April-2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>597</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>17-April-2026</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AI2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AK2" t="inlineStr">
         <is>
           <t>16-April-2026</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>auth</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>612</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>598</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>15-April-2026</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
@@ -1104,167 +1104,167 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>22-April-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>336</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>21-April-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>20-April-2026</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
         <is>
           <t>17-April-2026</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
         <is>
           <t>16-April-2026</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>idrepo</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>414</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>336</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>15-April-2026</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
@@ -1306,192 +1306,192 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>22-April-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>21-April-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
         <is>
           <t>20-April-2026</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
         <is>
           <t>17-April-2026</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="AE4" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
+      <c r="AH4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
         <is>
           <t>16-April-2026</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
+      <c r="AL4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="AD4" t="inlineStr">
+      <c r="AM4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="AE4" t="inlineStr">
+      <c r="AN4" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr">
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>15-April-2026</t>
-        </is>
-      </c>
-      <c r="AL4" t="inlineStr">
-        <is>
-          <t>masterdata-ara</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>930</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AP4" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
@@ -1508,192 +1508,192 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>22-April-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>944</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>21-April-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
         <is>
           <t>20-April-2026</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
         <is>
           <t>17-April-2026</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="AE5" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
         <is>
           <t>16-April-2026</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
+      <c r="AL5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="AD5" t="inlineStr">
+      <c r="AM5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="AE5" t="inlineStr">
+      <c r="AN5" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG5" t="inlineStr">
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>15-April-2026</t>
-        </is>
-      </c>
-      <c r="AL5" t="inlineStr">
-        <is>
-          <t>masterdata-eng</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AP5" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
@@ -1710,192 +1710,192 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>22-April-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>21-April-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
         <is>
           <t>20-April-2026</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
         <is>
           <t>17-April-2026</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="AE6" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
+      <c r="AH6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
         <is>
           <t>16-April-2026</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
+      <c r="AL6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="AD6" t="inlineStr">
+      <c r="AM6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="AE6" t="inlineStr">
+      <c r="AN6" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG6" t="inlineStr">
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>15-April-2026</t>
-        </is>
-      </c>
-      <c r="AL6" t="inlineStr">
-        <is>
-          <t>masterdata-fra</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>930</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AP6" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
@@ -1912,167 +1912,167 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>22-April-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>509</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>350</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>21-April-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>509</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>350</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>116</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>20-April-2026</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>509</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>350</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>116</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>17-April-2026</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>509</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="AE7" t="inlineStr">
         <is>
           <t>350</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="AF7" t="inlineStr">
         <is>
           <t>116</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="AG7" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AK7" t="inlineStr">
         <is>
           <t>16-April-2026</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>partner</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>509</t>
-        </is>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>350</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
-      <c r="AG7" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>15-April-2026</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
@@ -2114,167 +2114,167 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>22-April-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>21-April-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>20-April-2026</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>17-April-2026</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="AD8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="AE8" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="AI8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AK8" t="inlineStr">
         <is>
           <t>16-April-2026</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="AD8" t="inlineStr">
-        <is>
-          <t>288</t>
-        </is>
-      </c>
-      <c r="AE8" t="inlineStr">
-        <is>
-          <t>282</t>
-        </is>
-      </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>15-April-2026</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
@@ -2316,184 +2316,184 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>22-April-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>resident</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1142</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>1142</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>21-April-2026</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>1141</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
         <is>
           <t>20-April-2026</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
         <is>
           <t>17-April-2026</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="AC9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="AD9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="AE9" t="inlineStr">
         <is>
           <t>1141</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
         <is>
           <t>16-April-2026</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
+      <c r="AL9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="AD9" t="inlineStr">
+      <c r="AM9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="AE9" t="inlineStr">
+      <c r="AN9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>15-April-2026</t>
-        </is>
-      </c>
-      <c r="AL9" t="inlineStr">
-        <is>
-          <t>resident</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>1142</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>1139</t>
-        </is>
-      </c>
       <c r="AO9" t="inlineStr">
         <is>
           <t>0</t>
@@ -2501,7 +2501,7 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
@@ -2518,192 +2518,192 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>22-April-2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>dsl</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>21-April-2026</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>173</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
         <is>
           <t>20-April-2026</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>186</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="X10" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
         <is>
           <t>17-April-2026</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="AC10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="AD10" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="AE10" t="inlineStr">
         <is>
           <t>191</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
         <is>
           <t>16-April-2026</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
+      <c r="AL10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="AD10" t="inlineStr">
+      <c r="AM10" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="AE10" t="inlineStr">
+      <c r="AN10" t="inlineStr">
         <is>
           <t>178</t>
         </is>
       </c>
-      <c r="AF10" t="inlineStr">
+      <c r="AO10" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="AG10" t="inlineStr">
+      <c r="AP10" t="inlineStr">
         <is>
           <t>14</t>
-        </is>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>15-April-2026</t>
-        </is>
-      </c>
-      <c r="AL10" t="inlineStr">
-        <is>
-          <t>dsl</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>230</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AP10" t="inlineStr">
-        <is>
-          <t>12</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">

--- a/minio-report-tracker/xlxs/dev01.xlsx
+++ b/minio-report-tracker/xlxs/dev01.xlsx
@@ -902,167 +902,167 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>23-April-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>598</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>22-April-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>597</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>21-April-2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>592</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>20-April-2026</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>597</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="AH2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AI2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AK2" t="inlineStr">
         <is>
           <t>17-April-2026</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>auth</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>612</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>598</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>16-April-2026</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
@@ -1104,167 +1104,167 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>23-April-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>336</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>22-April-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>21-April-2026</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
         <is>
           <t>20-April-2026</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
         <is>
           <t>17-April-2026</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>idrepo</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>414</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>336</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>16-April-2026</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
@@ -1306,167 +1306,167 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>23-April-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>22-April-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
         <is>
           <t>21-April-2026</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
         <is>
           <t>20-April-2026</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="AE4" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
+      <c r="AH4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
         <is>
           <t>17-April-2026</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>masterdata-ara</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>16-April-2026</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
@@ -1508,167 +1508,167 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>23-April-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>944</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>22-April-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
         <is>
           <t>21-April-2026</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
         <is>
           <t>20-April-2026</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="AE5" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
         <is>
           <t>17-April-2026</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>masterdata-eng</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>944</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>16-April-2026</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
@@ -1710,167 +1710,167 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>23-April-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>22-April-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
         <is>
           <t>21-April-2026</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
         <is>
           <t>20-April-2026</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="AE6" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
+      <c r="AH6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
         <is>
           <t>17-April-2026</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>masterdata-fra</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>16-April-2026</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
@@ -1912,167 +1912,167 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>23-April-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>509</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>350</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>22-April-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>509</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>350</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>116</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>21-April-2026</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>509</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>350</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>116</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>20-April-2026</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>509</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="AE7" t="inlineStr">
         <is>
           <t>350</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="AF7" t="inlineStr">
         <is>
           <t>116</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="AG7" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AK7" t="inlineStr">
         <is>
           <t>17-April-2026</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>partner</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>509</t>
-        </is>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>350</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
-      <c r="AG7" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>16-April-2026</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
@@ -2114,167 +2114,167 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>23-April-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>22-April-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>21-April-2026</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>20-April-2026</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="AD8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="AE8" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="AI8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AK8" t="inlineStr">
         <is>
           <t>17-April-2026</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="AD8" t="inlineStr">
-        <is>
-          <t>288</t>
-        </is>
-      </c>
-      <c r="AE8" t="inlineStr">
-        <is>
-          <t>282</t>
-        </is>
-      </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>16-April-2026</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
@@ -2316,192 +2316,192 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>23-April-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>resident</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1142</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>1142</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>22-April-2026</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
         <is>
           <t>21-April-2026</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>1141</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
         <is>
           <t>20-April-2026</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="AC9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="AD9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="AE9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
         <is>
           <t>17-April-2026</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
+      <c r="AL9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="AD9" t="inlineStr">
+      <c r="AM9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="AE9" t="inlineStr">
+      <c r="AN9" t="inlineStr">
         <is>
           <t>1141</t>
         </is>
       </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG9" t="inlineStr">
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>16-April-2026</t>
-        </is>
-      </c>
-      <c r="AL9" t="inlineStr">
-        <is>
-          <t>resident</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>1142</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>1142</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AP9" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
@@ -2518,192 +2518,192 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>23-April-2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>dsl</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>201</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>22-April-2026</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
         <is>
           <t>21-April-2026</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>173</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="X10" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
         <is>
           <t>20-April-2026</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="AC10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="AD10" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="AE10" t="inlineStr">
         <is>
           <t>186</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
+      <c r="AF10" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
+      <c r="AG10" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
         <is>
           <t>17-April-2026</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
+      <c r="AL10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="AD10" t="inlineStr">
+      <c r="AM10" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="AE10" t="inlineStr">
+      <c r="AN10" t="inlineStr">
         <is>
           <t>191</t>
         </is>
       </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG10" t="inlineStr">
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AP10" t="inlineStr">
         <is>
           <t>11</t>
-        </is>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>16-April-2026</t>
-        </is>
-      </c>
-      <c r="AL10" t="inlineStr">
-        <is>
-          <t>dsl</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>230</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>178</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AP10" t="inlineStr">
-        <is>
-          <t>14</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">

--- a/minio-report-tracker/xlxs/dev01.xlsx
+++ b/minio-report-tracker/xlxs/dev01.xlsx
@@ -653,12 +653,12 @@
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="6" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="5" customWidth="1" min="3" max="3"/>
+    <col width="5" customWidth="1" min="4" max="4"/>
     <col width="5" customWidth="1" min="5" max="5"/>
-    <col width="4" customWidth="1" min="6" max="6"/>
-    <col width="4" customWidth="1" min="7" max="7"/>
-    <col width="4" customWidth="1" min="8" max="8"/>
+    <col width="5" customWidth="1" min="6" max="6"/>
+    <col width="5" customWidth="1" min="7" max="7"/>
+    <col width="5" customWidth="1" min="8" max="8"/>
     <col width="2" customWidth="1" min="9" max="9"/>
     <col width="15" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
@@ -902,192 +902,192 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>24-April-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>23-April-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>22-April-2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>597</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>21-April-2026</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>592</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="AH2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AI2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AK2" t="inlineStr">
         <is>
           <t>20-April-2026</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AL2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AM2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
+      <c r="AN2" t="inlineStr">
         <is>
           <t>597</t>
         </is>
       </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>17-April-2026</t>
-        </is>
-      </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>auth</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>612</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>598</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
@@ -1104,167 +1104,167 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>24-April-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>944</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>23-April-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>22-April-2026</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
         <is>
           <t>21-April-2026</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
         <is>
           <t>20-April-2026</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>idrepo</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>414</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>336</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>17-April-2026</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
@@ -1306,167 +1306,167 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>24-April-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>23-April-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
         <is>
           <t>22-April-2026</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
         <is>
           <t>21-April-2026</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="AE4" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
+      <c r="AH4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
         <is>
           <t>20-April-2026</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>masterdata-ara</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>17-April-2026</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
@@ -1508,167 +1508,167 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>24-April-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>509</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>350</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>23-April-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
         <is>
           <t>22-April-2026</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
         <is>
           <t>21-April-2026</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="AE5" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
         <is>
           <t>20-April-2026</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>masterdata-eng</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>944</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>17-April-2026</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
@@ -1710,167 +1710,167 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>24-April-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>23-April-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
         <is>
           <t>22-April-2026</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
         <is>
           <t>21-April-2026</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="AE6" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
+      <c r="AH6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
         <is>
           <t>20-April-2026</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>masterdata-fra</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>17-April-2026</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
@@ -1912,167 +1912,167 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>24-April-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>dsl</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>23-April-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>509</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>350</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>116</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>22-April-2026</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>509</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>350</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>116</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>21-April-2026</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>509</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="AE7" t="inlineStr">
         <is>
           <t>350</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="AF7" t="inlineStr">
         <is>
           <t>116</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="AG7" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AK7" t="inlineStr">
         <is>
           <t>20-April-2026</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>partner</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>509</t>
-        </is>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>350</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
-      <c r="AG7" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>17-April-2026</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
@@ -2112,169 +2112,153 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" t="n">
+        <v/>
+      </c>
+      <c r="B8" t="n">
+        <v/>
+      </c>
+      <c r="C8" t="n">
+        <v/>
+      </c>
+      <c r="D8" t="n">
+        <v/>
+      </c>
+      <c r="E8" t="n">
+        <v/>
+      </c>
+      <c r="F8" t="n">
+        <v/>
+      </c>
+      <c r="G8" t="n">
+        <v/>
+      </c>
+      <c r="H8" t="n">
+        <v/>
+      </c>
+      <c r="J8" t="inlineStr">
         <is>
           <t>23-April-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>22-April-2026</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>21-April-2026</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="AD8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="AE8" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="AI8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AK8" t="inlineStr">
         <is>
           <t>20-April-2026</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="AD8" t="inlineStr">
-        <is>
-          <t>288</t>
-        </is>
-      </c>
-      <c r="AE8" t="inlineStr">
-        <is>
-          <t>282</t>
-        </is>
-      </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>17-April-2026</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
@@ -2314,186 +2298,170 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" t="n">
+        <v/>
+      </c>
+      <c r="B9" t="n">
+        <v/>
+      </c>
+      <c r="C9" t="n">
+        <v/>
+      </c>
+      <c r="D9" t="n">
+        <v/>
+      </c>
+      <c r="E9" t="n">
+        <v/>
+      </c>
+      <c r="F9" t="n">
+        <v/>
+      </c>
+      <c r="G9" t="n">
+        <v/>
+      </c>
+      <c r="H9" t="n">
+        <v/>
+      </c>
+      <c r="J9" t="inlineStr">
         <is>
           <t>23-April-2026</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
         <is>
           <t>22-April-2026</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
         <is>
           <t>21-April-2026</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="AC9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="AD9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="AE9" t="inlineStr">
         <is>
           <t>1141</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
         <is>
           <t>20-April-2026</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
+      <c r="AL9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="AD9" t="inlineStr">
+      <c r="AM9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="AE9" t="inlineStr">
+      <c r="AN9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>17-April-2026</t>
-        </is>
-      </c>
-      <c r="AL9" t="inlineStr">
-        <is>
-          <t>resident</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>1142</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>1141</t>
-        </is>
-      </c>
       <c r="AO9" t="inlineStr">
         <is>
           <t>0</t>
@@ -2501,7 +2469,7 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
@@ -2516,194 +2484,178 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" t="n">
+        <v/>
+      </c>
+      <c r="B10" t="n">
+        <v/>
+      </c>
+      <c r="C10" t="n">
+        <v/>
+      </c>
+      <c r="D10" t="n">
+        <v/>
+      </c>
+      <c r="E10" t="n">
+        <v/>
+      </c>
+      <c r="F10" t="n">
+        <v/>
+      </c>
+      <c r="G10" t="n">
+        <v/>
+      </c>
+      <c r="H10" t="n">
+        <v/>
+      </c>
+      <c r="J10" t="inlineStr">
         <is>
           <t>23-April-2026</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>201</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
         <is>
           <t>22-April-2026</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
         <is>
           <t>21-April-2026</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="AC10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="AD10" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="AE10" t="inlineStr">
         <is>
           <t>173</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
+      <c r="AF10" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
+      <c r="AG10" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
         <is>
           <t>20-April-2026</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
+      <c r="AL10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="AD10" t="inlineStr">
+      <c r="AM10" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="AE10" t="inlineStr">
+      <c r="AN10" t="inlineStr">
         <is>
           <t>186</t>
         </is>
       </c>
-      <c r="AF10" t="inlineStr">
+      <c r="AO10" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AG10" t="inlineStr">
+      <c r="AP10" t="inlineStr">
         <is>
           <t>13</t>
-        </is>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>17-April-2026</t>
-        </is>
-      </c>
-      <c r="AL10" t="inlineStr">
-        <is>
-          <t>dsl</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>230</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>191</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AP10" t="inlineStr">
-        <is>
-          <t>11</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">

--- a/minio-report-tracker/xlxs/dev01.xlsx
+++ b/minio-report-tracker/xlxs/dev01.xlsx
@@ -653,21 +653,21 @@
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="5" customWidth="1" min="3" max="3"/>
-    <col width="5" customWidth="1" min="4" max="4"/>
+    <col width="6" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
     <col width="5" customWidth="1" min="5" max="5"/>
-    <col width="5" customWidth="1" min="6" max="6"/>
-    <col width="5" customWidth="1" min="7" max="7"/>
-    <col width="5" customWidth="1" min="8" max="8"/>
+    <col width="4" customWidth="1" min="6" max="6"/>
+    <col width="4" customWidth="1" min="7" max="7"/>
+    <col width="4" customWidth="1" min="8" max="8"/>
     <col width="2" customWidth="1" min="9" max="9"/>
     <col width="15" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="6" customWidth="1" min="12" max="12"/>
-    <col width="6" customWidth="1" min="13" max="13"/>
+    <col width="5" customWidth="1" min="12" max="12"/>
+    <col width="5" customWidth="1" min="13" max="13"/>
     <col width="5" customWidth="1" min="14" max="14"/>
-    <col width="4" customWidth="1" min="15" max="15"/>
-    <col width="4" customWidth="1" min="16" max="16"/>
-    <col width="4" customWidth="1" min="17" max="17"/>
+    <col width="5" customWidth="1" min="15" max="15"/>
+    <col width="5" customWidth="1" min="16" max="16"/>
+    <col width="5" customWidth="1" min="17" max="17"/>
     <col width="2" customWidth="1" min="18" max="18"/>
     <col width="15" customWidth="1" min="19" max="19"/>
     <col width="16" customWidth="1" min="20" max="20"/>
@@ -902,192 +902,192 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>27-April-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>597</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>24-April-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
         <is>
           <t>23-April-2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>22-April-2026</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>597</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="AH2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AI2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AK2" t="inlineStr">
         <is>
           <t>21-April-2026</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AL2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AM2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
+      <c r="AN2" t="inlineStr">
         <is>
           <t>592</t>
         </is>
       </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
         <is>
           <t>6</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>20-April-2026</t>
-        </is>
-      </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>auth</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>612</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>597</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
@@ -1104,167 +1104,167 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>27-April-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>336</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>24-April-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>23-April-2026</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
         <is>
           <t>22-April-2026</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
         <is>
           <t>21-April-2026</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>idrepo</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>414</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>336</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>20-April-2026</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
@@ -1306,167 +1306,167 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>27-April-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>24-April-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
         <is>
           <t>23-April-2026</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
         <is>
           <t>22-April-2026</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="AE4" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
+      <c r="AH4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
         <is>
           <t>21-April-2026</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>masterdata-ara</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>20-April-2026</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
@@ -1508,167 +1508,167 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>27-April-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>944</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>24-April-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>509</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>350</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>116</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>23-April-2026</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
         <is>
           <t>22-April-2026</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="AE5" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
         <is>
           <t>21-April-2026</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>masterdata-eng</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>944</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>20-April-2026</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
@@ -1710,167 +1710,167 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>27-April-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>24-April-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>23-April-2026</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
         <is>
           <t>22-April-2026</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="AE6" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
+      <c r="AH6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
         <is>
           <t>21-April-2026</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>masterdata-fra</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>20-April-2026</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
@@ -1912,167 +1912,167 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>27-April-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>509</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>350</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>24-April-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>79</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>98</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
         <is>
           <t>23-April-2026</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>509</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>350</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>116</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>22-April-2026</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>509</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="AE7" t="inlineStr">
         <is>
           <t>350</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="AF7" t="inlineStr">
         <is>
           <t>116</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="AG7" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AK7" t="inlineStr">
         <is>
           <t>21-April-2026</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>partner</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>509</t>
-        </is>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>350</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
-      <c r="AG7" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>20-April-2026</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
@@ -2112,153 +2112,153 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="n">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>27-April-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
         <v/>
       </c>
-      <c r="B8" t="n">
+      <c r="K8" t="n">
         <v/>
       </c>
-      <c r="C8" t="n">
+      <c r="L8" t="n">
         <v/>
       </c>
-      <c r="D8" t="n">
+      <c r="M8" t="n">
         <v/>
       </c>
-      <c r="E8" t="n">
+      <c r="N8" t="n">
         <v/>
       </c>
-      <c r="F8" t="n">
+      <c r="O8" t="n">
         <v/>
       </c>
-      <c r="G8" t="n">
+      <c r="P8" t="n">
         <v/>
       </c>
-      <c r="H8" t="n">
+      <c r="Q8" t="n">
         <v/>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>23-April-2026</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>22-April-2026</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="AD8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="AE8" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="AI8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AK8" t="inlineStr">
         <is>
           <t>21-April-2026</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="AD8" t="inlineStr">
-        <is>
-          <t>288</t>
-        </is>
-      </c>
-      <c r="AE8" t="inlineStr">
-        <is>
-          <t>282</t>
-        </is>
-      </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>20-April-2026</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
@@ -2298,178 +2298,178 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="n">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>27-April-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>resident</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1142</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>1140</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
         <v/>
       </c>
-      <c r="B9" t="n">
+      <c r="K9" t="n">
         <v/>
       </c>
-      <c r="C9" t="n">
+      <c r="L9" t="n">
         <v/>
       </c>
-      <c r="D9" t="n">
+      <c r="M9" t="n">
         <v/>
       </c>
-      <c r="E9" t="n">
+      <c r="N9" t="n">
         <v/>
       </c>
-      <c r="F9" t="n">
+      <c r="O9" t="n">
         <v/>
       </c>
-      <c r="G9" t="n">
+      <c r="P9" t="n">
         <v/>
       </c>
-      <c r="H9" t="n">
+      <c r="Q9" t="n">
         <v/>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>23-April-2026</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
         <is>
           <t>22-April-2026</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="AC9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="AD9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="AE9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
         <is>
           <t>21-April-2026</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
+      <c r="AL9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="AD9" t="inlineStr">
+      <c r="AM9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="AE9" t="inlineStr">
+      <c r="AN9" t="inlineStr">
         <is>
           <t>1141</t>
         </is>
       </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG9" t="inlineStr">
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>20-April-2026</t>
-        </is>
-      </c>
-      <c r="AL9" t="inlineStr">
-        <is>
-          <t>resident</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>1142</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>1142</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AP9" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
@@ -2484,178 +2484,178 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="n">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>27-April-2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>dsl</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>201</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
         <v/>
       </c>
-      <c r="B10" t="n">
+      <c r="K10" t="n">
         <v/>
       </c>
-      <c r="C10" t="n">
+      <c r="L10" t="n">
         <v/>
       </c>
-      <c r="D10" t="n">
+      <c r="M10" t="n">
         <v/>
       </c>
-      <c r="E10" t="n">
+      <c r="N10" t="n">
         <v/>
       </c>
-      <c r="F10" t="n">
+      <c r="O10" t="n">
         <v/>
       </c>
-      <c r="G10" t="n">
+      <c r="P10" t="n">
         <v/>
       </c>
-      <c r="H10" t="n">
+      <c r="Q10" t="n">
         <v/>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>23-April-2026</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>201</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
         <is>
           <t>22-April-2026</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="AC10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="AD10" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="AE10" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
         <is>
           <t>21-April-2026</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
+      <c r="AL10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="AD10" t="inlineStr">
+      <c r="AM10" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="AE10" t="inlineStr">
+      <c r="AN10" t="inlineStr">
         <is>
           <t>173</t>
         </is>
       </c>
-      <c r="AF10" t="inlineStr">
+      <c r="AO10" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="AG10" t="inlineStr">
+      <c r="AP10" t="inlineStr">
         <is>
           <t>9</t>
-        </is>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>20-April-2026</t>
-        </is>
-      </c>
-      <c r="AL10" t="inlineStr">
-        <is>
-          <t>dsl</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>230</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>186</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AP10" t="inlineStr">
-        <is>
-          <t>13</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">

--- a/minio-report-tracker/xlxs/dev01.xlsx
+++ b/minio-report-tracker/xlxs/dev01.xlsx
@@ -662,21 +662,21 @@
     <col width="2" customWidth="1" min="9" max="9"/>
     <col width="15" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="5" customWidth="1" min="12" max="12"/>
-    <col width="5" customWidth="1" min="13" max="13"/>
+    <col width="6" customWidth="1" min="12" max="12"/>
+    <col width="6" customWidth="1" min="13" max="13"/>
     <col width="5" customWidth="1" min="14" max="14"/>
-    <col width="5" customWidth="1" min="15" max="15"/>
-    <col width="5" customWidth="1" min="16" max="16"/>
-    <col width="5" customWidth="1" min="17" max="17"/>
+    <col width="4" customWidth="1" min="15" max="15"/>
+    <col width="4" customWidth="1" min="16" max="16"/>
+    <col width="4" customWidth="1" min="17" max="17"/>
     <col width="2" customWidth="1" min="18" max="18"/>
     <col width="15" customWidth="1" min="19" max="19"/>
     <col width="16" customWidth="1" min="20" max="20"/>
-    <col width="6" customWidth="1" min="21" max="21"/>
-    <col width="6" customWidth="1" min="22" max="22"/>
+    <col width="5" customWidth="1" min="21" max="21"/>
+    <col width="5" customWidth="1" min="22" max="22"/>
     <col width="5" customWidth="1" min="23" max="23"/>
-    <col width="4" customWidth="1" min="24" max="24"/>
-    <col width="4" customWidth="1" min="25" max="25"/>
-    <col width="4" customWidth="1" min="26" max="26"/>
+    <col width="5" customWidth="1" min="24" max="24"/>
+    <col width="5" customWidth="1" min="25" max="25"/>
+    <col width="5" customWidth="1" min="26" max="26"/>
     <col width="2" customWidth="1" min="27" max="27"/>
     <col width="15" customWidth="1" min="28" max="28"/>
     <col width="16" customWidth="1" min="29" max="29"/>
@@ -902,192 +902,192 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>28-April-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>598</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>27-April-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>597</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>24-April-2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
         <is>
           <t>23-April-2026</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AI2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AK2" t="inlineStr">
         <is>
           <t>22-April-2026</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AL2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AM2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
+      <c r="AN2" t="inlineStr">
         <is>
           <t>597</t>
         </is>
       </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>21-April-2026</t>
-        </is>
-      </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>auth</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>612</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>592</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>6</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
@@ -1104,167 +1104,167 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>28-April-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>336</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>27-April-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>24-April-2026</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
         <is>
           <t>23-April-2026</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
         <is>
           <t>22-April-2026</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>idrepo</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>414</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>336</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>21-April-2026</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
@@ -1306,167 +1306,167 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>28-April-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>27-April-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
         <is>
           <t>24-April-2026</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
         <is>
           <t>23-April-2026</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="AE4" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
+      <c r="AH4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
         <is>
           <t>22-April-2026</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>masterdata-ara</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>21-April-2026</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
@@ -1508,167 +1508,167 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>28-April-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>944</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>27-April-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
         <is>
           <t>24-April-2026</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>509</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>350</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>116</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="AB5" t="inlineStr">
         <is>
           <t>23-April-2026</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="AE5" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
         <is>
           <t>22-April-2026</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>masterdata-eng</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>944</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>21-April-2026</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
@@ -1710,167 +1710,167 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>28-April-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>27-April-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
         <is>
           <t>24-April-2026</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="Z6" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="AB6" t="inlineStr">
         <is>
           <t>23-April-2026</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="AE6" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
+      <c r="AH6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
         <is>
           <t>22-April-2026</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>masterdata-fra</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>21-April-2026</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
@@ -1912,167 +1912,167 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>28-April-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>509</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>350</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>27-April-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>509</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>350</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>116</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>24-April-2026</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>79</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>98</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
         <is>
           <t>23-April-2026</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>509</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="AE7" t="inlineStr">
         <is>
           <t>350</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="AF7" t="inlineStr">
         <is>
           <t>116</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="AG7" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AK7" t="inlineStr">
         <is>
           <t>22-April-2026</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>partner</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>509</t>
-        </is>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>350</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
-      <c r="AG7" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>21-April-2026</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
@@ -2114,151 +2114,151 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>28-April-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>27-April-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J8" t="n">
+      <c r="S8" t="n">
         <v/>
       </c>
-      <c r="K8" t="n">
+      <c r="T8" t="n">
         <v/>
       </c>
-      <c r="L8" t="n">
+      <c r="U8" t="n">
         <v/>
       </c>
-      <c r="M8" t="n">
+      <c r="V8" t="n">
         <v/>
       </c>
-      <c r="N8" t="n">
+      <c r="W8" t="n">
         <v/>
       </c>
-      <c r="O8" t="n">
+      <c r="X8" t="n">
         <v/>
       </c>
-      <c r="P8" t="n">
+      <c r="Y8" t="n">
         <v/>
       </c>
-      <c r="Q8" t="n">
+      <c r="Z8" t="n">
         <v/>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>23-April-2026</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="AD8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="AE8" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="AI8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AK8" t="inlineStr">
         <is>
           <t>22-April-2026</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="AD8" t="inlineStr">
-        <is>
-          <t>288</t>
-        </is>
-      </c>
-      <c r="AE8" t="inlineStr">
-        <is>
-          <t>282</t>
-        </is>
-      </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>21-April-2026</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
@@ -2300,168 +2300,168 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>28-April-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>resident</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1142</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>1142</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>27-April-2026</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>1140</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J9" t="n">
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S9" t="n">
         <v/>
       </c>
-      <c r="K9" t="n">
+      <c r="T9" t="n">
         <v/>
       </c>
-      <c r="L9" t="n">
+      <c r="U9" t="n">
         <v/>
       </c>
-      <c r="M9" t="n">
+      <c r="V9" t="n">
         <v/>
       </c>
-      <c r="N9" t="n">
+      <c r="W9" t="n">
         <v/>
       </c>
-      <c r="O9" t="n">
+      <c r="X9" t="n">
         <v/>
       </c>
-      <c r="P9" t="n">
+      <c r="Y9" t="n">
         <v/>
       </c>
-      <c r="Q9" t="n">
+      <c r="Z9" t="n">
         <v/>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="AB9" t="inlineStr">
         <is>
           <t>23-April-2026</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="AC9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="AD9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="AE9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
         <is>
           <t>22-April-2026</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
+      <c r="AL9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="AD9" t="inlineStr">
+      <c r="AM9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="AE9" t="inlineStr">
+      <c r="AN9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>21-April-2026</t>
-        </is>
-      </c>
-      <c r="AL9" t="inlineStr">
-        <is>
-          <t>resident</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>1142</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>1141</t>
-        </is>
-      </c>
       <c r="AO9" t="inlineStr">
         <is>
           <t>0</t>
@@ -2469,7 +2469,7 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
@@ -2486,176 +2486,176 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>28-April-2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>dsl</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>201</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>27-April-2026</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>201</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J10" t="n">
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S10" t="n">
         <v/>
       </c>
-      <c r="K10" t="n">
+      <c r="T10" t="n">
         <v/>
       </c>
-      <c r="L10" t="n">
+      <c r="U10" t="n">
         <v/>
       </c>
-      <c r="M10" t="n">
+      <c r="V10" t="n">
         <v/>
       </c>
-      <c r="N10" t="n">
+      <c r="W10" t="n">
         <v/>
       </c>
-      <c r="O10" t="n">
+      <c r="X10" t="n">
         <v/>
       </c>
-      <c r="P10" t="n">
+      <c r="Y10" t="n">
         <v/>
       </c>
-      <c r="Q10" t="n">
+      <c r="Z10" t="n">
         <v/>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="AB10" t="inlineStr">
         <is>
           <t>23-April-2026</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="AC10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="AD10" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="AE10" t="inlineStr">
         <is>
           <t>201</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
         <is>
           <t>22-April-2026</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
+      <c r="AL10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="AD10" t="inlineStr">
+      <c r="AM10" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="AE10" t="inlineStr">
+      <c r="AN10" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG10" t="inlineStr">
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AP10" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>21-April-2026</t>
-        </is>
-      </c>
-      <c r="AL10" t="inlineStr">
-        <is>
-          <t>dsl</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>230</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>173</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="AP10" t="inlineStr">
-        <is>
-          <t>9</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">

--- a/minio-report-tracker/xlxs/dev01.xlsx
+++ b/minio-report-tracker/xlxs/dev01.xlsx
@@ -653,12 +653,12 @@
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="6" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="5" customWidth="1" min="3" max="3"/>
+    <col width="5" customWidth="1" min="4" max="4"/>
     <col width="5" customWidth="1" min="5" max="5"/>
-    <col width="4" customWidth="1" min="6" max="6"/>
-    <col width="4" customWidth="1" min="7" max="7"/>
-    <col width="4" customWidth="1" min="8" max="8"/>
+    <col width="5" customWidth="1" min="6" max="6"/>
+    <col width="5" customWidth="1" min="7" max="7"/>
+    <col width="5" customWidth="1" min="8" max="8"/>
     <col width="2" customWidth="1" min="9" max="9"/>
     <col width="15" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
@@ -671,21 +671,21 @@
     <col width="2" customWidth="1" min="18" max="18"/>
     <col width="15" customWidth="1" min="19" max="19"/>
     <col width="16" customWidth="1" min="20" max="20"/>
-    <col width="5" customWidth="1" min="21" max="21"/>
-    <col width="5" customWidth="1" min="22" max="22"/>
+    <col width="6" customWidth="1" min="21" max="21"/>
+    <col width="6" customWidth="1" min="22" max="22"/>
     <col width="5" customWidth="1" min="23" max="23"/>
-    <col width="5" customWidth="1" min="24" max="24"/>
-    <col width="5" customWidth="1" min="25" max="25"/>
-    <col width="5" customWidth="1" min="26" max="26"/>
+    <col width="4" customWidth="1" min="24" max="24"/>
+    <col width="4" customWidth="1" min="25" max="25"/>
+    <col width="4" customWidth="1" min="26" max="26"/>
     <col width="2" customWidth="1" min="27" max="27"/>
     <col width="15" customWidth="1" min="28" max="28"/>
     <col width="16" customWidth="1" min="29" max="29"/>
-    <col width="6" customWidth="1" min="30" max="30"/>
-    <col width="6" customWidth="1" min="31" max="31"/>
+    <col width="5" customWidth="1" min="30" max="30"/>
+    <col width="5" customWidth="1" min="31" max="31"/>
     <col width="5" customWidth="1" min="32" max="32"/>
-    <col width="4" customWidth="1" min="33" max="33"/>
-    <col width="4" customWidth="1" min="34" max="34"/>
-    <col width="4" customWidth="1" min="35" max="35"/>
+    <col width="5" customWidth="1" min="33" max="33"/>
+    <col width="5" customWidth="1" min="34" max="34"/>
+    <col width="5" customWidth="1" min="35" max="35"/>
     <col width="2" customWidth="1" min="36" max="36"/>
     <col width="15" customWidth="1" min="37" max="37"/>
     <col width="16" customWidth="1" min="38" max="38"/>
@@ -902,184 +902,184 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>29-April-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>28-April-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>27-April-2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>597</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>24-April-2026</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="AH2" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
         <is>
           <t>23-April-2026</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AL2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AM2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
+      <c r="AN2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>22-April-2026</t>
-        </is>
-      </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>auth</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>612</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>597</t>
-        </is>
-      </c>
       <c r="AO2" t="inlineStr">
         <is>
           <t>0</t>
@@ -1087,7 +1087,7 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
@@ -1104,167 +1104,167 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>29-April-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>944</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>28-April-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>27-April-2026</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
         <is>
           <t>24-April-2026</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
         <is>
           <t>23-April-2026</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>idrepo</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>414</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>336</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>22-April-2026</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
@@ -1306,167 +1306,167 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>29-April-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>28-April-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
         <is>
           <t>27-April-2026</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
         <is>
           <t>24-April-2026</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="AE4" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
+      <c r="AH4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
         <is>
           <t>23-April-2026</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>masterdata-ara</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>22-April-2026</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
@@ -1508,167 +1508,167 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>29-April-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>509</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>342</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>28-April-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
         <is>
           <t>27-April-2026</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
         <is>
           <t>24-April-2026</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>509</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="AE5" t="inlineStr">
         <is>
           <t>350</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="AF5" t="inlineStr">
         <is>
           <t>116</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="AG5" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AK5" t="inlineStr">
         <is>
           <t>23-April-2026</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>masterdata-eng</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>944</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>22-April-2026</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
@@ -1710,167 +1710,167 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>29-April-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>28-April-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
         <is>
           <t>27-April-2026</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
         <is>
           <t>24-April-2026</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="AE6" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
+      <c r="AI6" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AK6" t="inlineStr">
         <is>
           <t>23-April-2026</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>masterdata-fra</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>22-April-2026</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
@@ -1912,167 +1912,167 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>29-April-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>dsl</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>28-April-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>509</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>350</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>116</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>27-April-2026</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>509</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>350</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>116</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>24-April-2026</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="AE7" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="AF7" t="inlineStr">
         <is>
           <t>79</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="AG7" t="inlineStr">
         <is>
           <t>98</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
         <is>
           <t>23-April-2026</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>partner</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>509</t>
-        </is>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>350</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
-      <c r="AG7" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>22-April-2026</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
@@ -2112,153 +2112,137 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" t="n">
+        <v/>
+      </c>
+      <c r="B8" t="n">
+        <v/>
+      </c>
+      <c r="C8" t="n">
+        <v/>
+      </c>
+      <c r="D8" t="n">
+        <v/>
+      </c>
+      <c r="E8" t="n">
+        <v/>
+      </c>
+      <c r="F8" t="n">
+        <v/>
+      </c>
+      <c r="G8" t="n">
+        <v/>
+      </c>
+      <c r="H8" t="n">
+        <v/>
+      </c>
+      <c r="J8" t="inlineStr">
         <is>
           <t>28-April-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>27-April-2026</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="S8" t="n">
-        <v/>
-      </c>
-      <c r="T8" t="n">
-        <v/>
-      </c>
-      <c r="U8" t="n">
-        <v/>
-      </c>
-      <c r="V8" t="n">
-        <v/>
-      </c>
-      <c r="W8" t="n">
-        <v/>
-      </c>
-      <c r="X8" t="n">
-        <v/>
-      </c>
-      <c r="Y8" t="n">
-        <v/>
-      </c>
-      <c r="Z8" t="n">
-        <v/>
-      </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AB8" t="n">
+        <v/>
+      </c>
+      <c r="AC8" t="n">
+        <v/>
+      </c>
+      <c r="AD8" t="n">
+        <v/>
+      </c>
+      <c r="AE8" t="n">
+        <v/>
+      </c>
+      <c r="AF8" t="n">
+        <v/>
+      </c>
+      <c r="AG8" t="n">
+        <v/>
+      </c>
+      <c r="AH8" t="n">
+        <v/>
+      </c>
+      <c r="AI8" t="n">
+        <v/>
+      </c>
+      <c r="AK8" t="inlineStr">
         <is>
           <t>23-April-2026</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="AD8" t="inlineStr">
-        <is>
-          <t>288</t>
-        </is>
-      </c>
-      <c r="AE8" t="inlineStr">
-        <is>
-          <t>282</t>
-        </is>
-      </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>22-April-2026</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
@@ -2298,153 +2282,137 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" t="n">
+        <v/>
+      </c>
+      <c r="B9" t="n">
+        <v/>
+      </c>
+      <c r="C9" t="n">
+        <v/>
+      </c>
+      <c r="D9" t="n">
+        <v/>
+      </c>
+      <c r="E9" t="n">
+        <v/>
+      </c>
+      <c r="F9" t="n">
+        <v/>
+      </c>
+      <c r="G9" t="n">
+        <v/>
+      </c>
+      <c r="H9" t="n">
+        <v/>
+      </c>
+      <c r="J9" t="inlineStr">
         <is>
           <t>28-April-2026</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
         <is>
           <t>27-April-2026</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>1140</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S9" t="n">
-        <v/>
-      </c>
-      <c r="T9" t="n">
-        <v/>
-      </c>
-      <c r="U9" t="n">
-        <v/>
-      </c>
-      <c r="V9" t="n">
-        <v/>
-      </c>
-      <c r="W9" t="n">
-        <v/>
-      </c>
-      <c r="X9" t="n">
-        <v/>
-      </c>
-      <c r="Y9" t="n">
-        <v/>
-      </c>
-      <c r="Z9" t="n">
-        <v/>
-      </c>
-      <c r="AB9" t="inlineStr">
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB9" t="n">
+        <v/>
+      </c>
+      <c r="AC9" t="n">
+        <v/>
+      </c>
+      <c r="AD9" t="n">
+        <v/>
+      </c>
+      <c r="AE9" t="n">
+        <v/>
+      </c>
+      <c r="AF9" t="n">
+        <v/>
+      </c>
+      <c r="AG9" t="n">
+        <v/>
+      </c>
+      <c r="AH9" t="n">
+        <v/>
+      </c>
+      <c r="AI9" t="n">
+        <v/>
+      </c>
+      <c r="AK9" t="inlineStr">
         <is>
           <t>23-April-2026</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>resident</t>
-        </is>
-      </c>
-      <c r="AD9" t="inlineStr">
-        <is>
-          <t>1142</t>
-        </is>
-      </c>
-      <c r="AE9" t="inlineStr">
-        <is>
-          <t>1142</t>
-        </is>
-      </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>22-April-2026</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
@@ -2484,178 +2452,162 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" t="n">
+        <v/>
+      </c>
+      <c r="B10" t="n">
+        <v/>
+      </c>
+      <c r="C10" t="n">
+        <v/>
+      </c>
+      <c r="D10" t="n">
+        <v/>
+      </c>
+      <c r="E10" t="n">
+        <v/>
+      </c>
+      <c r="F10" t="n">
+        <v/>
+      </c>
+      <c r="G10" t="n">
+        <v/>
+      </c>
+      <c r="H10" t="n">
+        <v/>
+      </c>
+      <c r="J10" t="inlineStr">
         <is>
           <t>28-April-2026</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>201</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
         <is>
           <t>27-April-2026</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>201</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S10" t="n">
-        <v/>
-      </c>
-      <c r="T10" t="n">
-        <v/>
-      </c>
-      <c r="U10" t="n">
-        <v/>
-      </c>
-      <c r="V10" t="n">
-        <v/>
-      </c>
-      <c r="W10" t="n">
-        <v/>
-      </c>
-      <c r="X10" t="n">
-        <v/>
-      </c>
-      <c r="Y10" t="n">
-        <v/>
-      </c>
-      <c r="Z10" t="n">
-        <v/>
-      </c>
-      <c r="AB10" t="inlineStr">
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB10" t="n">
+        <v/>
+      </c>
+      <c r="AC10" t="n">
+        <v/>
+      </c>
+      <c r="AD10" t="n">
+        <v/>
+      </c>
+      <c r="AE10" t="n">
+        <v/>
+      </c>
+      <c r="AF10" t="n">
+        <v/>
+      </c>
+      <c r="AG10" t="n">
+        <v/>
+      </c>
+      <c r="AH10" t="n">
+        <v/>
+      </c>
+      <c r="AI10" t="n">
+        <v/>
+      </c>
+      <c r="AK10" t="inlineStr">
         <is>
           <t>23-April-2026</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
+      <c r="AL10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="AD10" t="inlineStr">
+      <c r="AM10" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="AE10" t="inlineStr">
+      <c r="AN10" t="inlineStr">
         <is>
           <t>201</t>
         </is>
       </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG10" t="inlineStr">
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AP10" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>22-April-2026</t>
-        </is>
-      </c>
-      <c r="AL10" t="inlineStr">
-        <is>
-          <t>dsl</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>230</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AP10" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">

--- a/minio-report-tracker/xlxs/dev01.xlsx
+++ b/minio-report-tracker/xlxs/dev01.xlsx
@@ -653,21 +653,21 @@
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="5" customWidth="1" min="3" max="3"/>
-    <col width="5" customWidth="1" min="4" max="4"/>
+    <col width="6" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
     <col width="5" customWidth="1" min="5" max="5"/>
-    <col width="5" customWidth="1" min="6" max="6"/>
-    <col width="5" customWidth="1" min="7" max="7"/>
-    <col width="5" customWidth="1" min="8" max="8"/>
+    <col width="4" customWidth="1" min="6" max="6"/>
+    <col width="4" customWidth="1" min="7" max="7"/>
+    <col width="4" customWidth="1" min="8" max="8"/>
     <col width="2" customWidth="1" min="9" max="9"/>
     <col width="15" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="6" customWidth="1" min="12" max="12"/>
-    <col width="6" customWidth="1" min="13" max="13"/>
+    <col width="5" customWidth="1" min="12" max="12"/>
+    <col width="5" customWidth="1" min="13" max="13"/>
     <col width="5" customWidth="1" min="14" max="14"/>
-    <col width="4" customWidth="1" min="15" max="15"/>
-    <col width="4" customWidth="1" min="16" max="16"/>
-    <col width="4" customWidth="1" min="17" max="17"/>
+    <col width="5" customWidth="1" min="15" max="15"/>
+    <col width="5" customWidth="1" min="16" max="16"/>
+    <col width="5" customWidth="1" min="17" max="17"/>
     <col width="2" customWidth="1" min="18" max="18"/>
     <col width="15" customWidth="1" min="19" max="19"/>
     <col width="16" customWidth="1" min="20" max="20"/>
@@ -680,21 +680,21 @@
     <col width="2" customWidth="1" min="27" max="27"/>
     <col width="15" customWidth="1" min="28" max="28"/>
     <col width="16" customWidth="1" min="29" max="29"/>
-    <col width="5" customWidth="1" min="30" max="30"/>
-    <col width="5" customWidth="1" min="31" max="31"/>
+    <col width="6" customWidth="1" min="30" max="30"/>
+    <col width="6" customWidth="1" min="31" max="31"/>
     <col width="5" customWidth="1" min="32" max="32"/>
-    <col width="5" customWidth="1" min="33" max="33"/>
-    <col width="5" customWidth="1" min="34" max="34"/>
-    <col width="5" customWidth="1" min="35" max="35"/>
+    <col width="4" customWidth="1" min="33" max="33"/>
+    <col width="4" customWidth="1" min="34" max="34"/>
+    <col width="4" customWidth="1" min="35" max="35"/>
     <col width="2" customWidth="1" min="36" max="36"/>
     <col width="15" customWidth="1" min="37" max="37"/>
     <col width="16" customWidth="1" min="38" max="38"/>
-    <col width="6" customWidth="1" min="39" max="39"/>
-    <col width="6" customWidth="1" min="40" max="40"/>
+    <col width="5" customWidth="1" min="39" max="39"/>
+    <col width="5" customWidth="1" min="40" max="40"/>
     <col width="5" customWidth="1" min="41" max="41"/>
-    <col width="4" customWidth="1" min="42" max="42"/>
-    <col width="4" customWidth="1" min="43" max="43"/>
-    <col width="4" customWidth="1" min="44" max="44"/>
+    <col width="5" customWidth="1" min="42" max="42"/>
+    <col width="5" customWidth="1" min="43" max="43"/>
+    <col width="5" customWidth="1" min="44" max="44"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -902,399 +902,399 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>30-April-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>598</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>29-April-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
         <is>
           <t>28-April-2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>27-April-2026</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>597</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="AH2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AI2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AK2" t="inlineStr">
         <is>
           <t>24-April-2026</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AL2" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AM2" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
+      <c r="AN2" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AH2" t="inlineStr">
+      <c r="AQ2" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>23-April-2026</t>
-        </is>
-      </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>auth</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>612</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>598</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>30-April-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>336</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>29-April-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>28-April-2026</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
         <is>
           <t>27-April-2026</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
         <is>
           <t>24-April-2026</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
+      <c r="AL3" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="AD3" t="inlineStr">
+      <c r="AM3" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="AE3" t="inlineStr">
+      <c r="AN3" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>23-April-2026</t>
-        </is>
-      </c>
-      <c r="AL3" t="inlineStr">
-        <is>
-          <t>idrepo</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>414</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>336</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AP3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
@@ -1306,172 +1306,172 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>30-April-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>29-April-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
         <is>
           <t>28-April-2026</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
         <is>
           <t>27-April-2026</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="AE4" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
+      <c r="AH4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
         <is>
           <t>24-April-2026</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
+      <c r="AL4" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>23-April-2026</t>
-        </is>
-      </c>
-      <c r="AL4" t="inlineStr">
-        <is>
-          <t>masterdata-ara</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
@@ -1508,598 +1508,598 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>30-April-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>944</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>29-April-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>509</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>342</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>116</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>39</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>28-April-2026</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
         <is>
           <t>27-April-2026</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="AE5" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
         <is>
           <t>24-April-2026</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
+      <c r="AL5" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="AD5" t="inlineStr">
+      <c r="AM5" t="inlineStr">
         <is>
           <t>509</t>
         </is>
       </c>
-      <c r="AE5" t="inlineStr">
+      <c r="AN5" t="inlineStr">
         <is>
           <t>350</t>
         </is>
       </c>
-      <c r="AF5" t="inlineStr">
+      <c r="AO5" t="inlineStr">
         <is>
           <t>116</t>
         </is>
       </c>
-      <c r="AG5" t="inlineStr">
+      <c r="AP5" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
         <is>
           <t>12</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>23-April-2026</t>
-        </is>
-      </c>
-      <c r="AL5" t="inlineStr">
-        <is>
-          <t>masterdata-eng</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>944</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AP5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AQ5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>30-April-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>29-April-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>101</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>161</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>28-April-2026</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
         <is>
           <t>27-April-2026</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="AE6" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
+      <c r="AH6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
         <is>
           <t>24-April-2026</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
+      <c r="AL6" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="AD6" t="inlineStr">
+      <c r="AM6" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="AE6" t="inlineStr">
+      <c r="AN6" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH6" t="inlineStr">
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AI6" t="inlineStr">
+      <c r="AR6" t="inlineStr">
         <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>23-April-2026</t>
-        </is>
-      </c>
-      <c r="AL6" t="inlineStr">
-        <is>
-          <t>masterdata-fra</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AP6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AQ6" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>30-April-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>509</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>350</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>29-April-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>106</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>94</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
         <is>
           <t>28-April-2026</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>509</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>350</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>116</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>27-April-2026</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>509</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="AE7" t="inlineStr">
         <is>
           <t>350</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="AF7" t="inlineStr">
         <is>
           <t>116</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="AG7" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AK7" t="inlineStr">
         <is>
           <t>24-April-2026</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
+      <c r="AL7" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="AD7" t="inlineStr">
+      <c r="AM7" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="AE7" t="inlineStr">
+      <c r="AN7" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="AF7" t="inlineStr">
+      <c r="AO7" t="inlineStr">
         <is>
           <t>79</t>
         </is>
       </c>
-      <c r="AG7" t="inlineStr">
+      <c r="AP7" t="inlineStr">
         <is>
           <t>98</t>
         </is>
       </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>23-April-2026</t>
-        </is>
-      </c>
-      <c r="AL7" t="inlineStr">
-        <is>
-          <t>partner</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>509</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>350</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
-      <c r="AP7" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
       <c r="AQ7" t="inlineStr">
         <is>
           <t>0</t>
@@ -2107,518 +2107,518 @@
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="n">
-        <v/>
-      </c>
-      <c r="B8" t="n">
-        <v/>
-      </c>
-      <c r="C8" t="n">
-        <v/>
-      </c>
-      <c r="D8" t="n">
-        <v/>
-      </c>
-      <c r="E8" t="n">
-        <v/>
-      </c>
-      <c r="F8" t="n">
-        <v/>
-      </c>
-      <c r="G8" t="n">
-        <v/>
-      </c>
-      <c r="H8" t="n">
-        <v/>
-      </c>
-      <c r="J8" t="inlineStr">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>30-April-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v/>
+      </c>
+      <c r="K8" t="n">
+        <v/>
+      </c>
+      <c r="L8" t="n">
+        <v/>
+      </c>
+      <c r="M8" t="n">
+        <v/>
+      </c>
+      <c r="N8" t="n">
+        <v/>
+      </c>
+      <c r="O8" t="n">
+        <v/>
+      </c>
+      <c r="P8" t="n">
+        <v/>
+      </c>
+      <c r="Q8" t="n">
+        <v/>
+      </c>
+      <c r="S8" t="inlineStr">
         <is>
           <t>28-April-2026</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>27-April-2026</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="AD8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="AE8" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="AI8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AB8" t="n">
-        <v/>
-      </c>
-      <c r="AC8" t="n">
-        <v/>
-      </c>
-      <c r="AD8" t="n">
-        <v/>
-      </c>
-      <c r="AE8" t="n">
-        <v/>
-      </c>
-      <c r="AF8" t="n">
-        <v/>
-      </c>
-      <c r="AG8" t="n">
-        <v/>
-      </c>
-      <c r="AH8" t="n">
-        <v/>
-      </c>
-      <c r="AI8" t="n">
-        <v/>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>23-April-2026</t>
-        </is>
-      </c>
-      <c r="AL8" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>288</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>282</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AP8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AK8" t="n">
+        <v/>
+      </c>
+      <c r="AL8" t="n">
+        <v/>
+      </c>
+      <c r="AM8" t="n">
+        <v/>
+      </c>
+      <c r="AN8" t="n">
+        <v/>
+      </c>
+      <c r="AO8" t="n">
+        <v/>
+      </c>
+      <c r="AP8" t="n">
+        <v/>
+      </c>
+      <c r="AQ8" t="n">
+        <v/>
+      </c>
+      <c r="AR8" t="n">
+        <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="n">
-        <v/>
-      </c>
-      <c r="B9" t="n">
-        <v/>
-      </c>
-      <c r="C9" t="n">
-        <v/>
-      </c>
-      <c r="D9" t="n">
-        <v/>
-      </c>
-      <c r="E9" t="n">
-        <v/>
-      </c>
-      <c r="F9" t="n">
-        <v/>
-      </c>
-      <c r="G9" t="n">
-        <v/>
-      </c>
-      <c r="H9" t="n">
-        <v/>
-      </c>
-      <c r="J9" t="inlineStr">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>30-April-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>resident</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1142</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>1142</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v/>
+      </c>
+      <c r="K9" t="n">
+        <v/>
+      </c>
+      <c r="L9" t="n">
+        <v/>
+      </c>
+      <c r="M9" t="n">
+        <v/>
+      </c>
+      <c r="N9" t="n">
+        <v/>
+      </c>
+      <c r="O9" t="n">
+        <v/>
+      </c>
+      <c r="P9" t="n">
+        <v/>
+      </c>
+      <c r="Q9" t="n">
+        <v/>
+      </c>
+      <c r="S9" t="inlineStr">
         <is>
           <t>28-April-2026</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
         <is>
           <t>27-April-2026</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="AC9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="AD9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="AE9" t="inlineStr">
         <is>
           <t>1140</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB9" t="n">
-        <v/>
-      </c>
-      <c r="AC9" t="n">
-        <v/>
-      </c>
-      <c r="AD9" t="n">
-        <v/>
-      </c>
-      <c r="AE9" t="n">
-        <v/>
-      </c>
-      <c r="AF9" t="n">
-        <v/>
-      </c>
-      <c r="AG9" t="n">
-        <v/>
-      </c>
-      <c r="AH9" t="n">
-        <v/>
-      </c>
-      <c r="AI9" t="n">
-        <v/>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>23-April-2026</t>
-        </is>
-      </c>
-      <c r="AL9" t="inlineStr">
-        <is>
-          <t>resident</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>1142</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>1142</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AP9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK9" t="n">
+        <v/>
+      </c>
+      <c r="AL9" t="n">
+        <v/>
+      </c>
+      <c r="AM9" t="n">
+        <v/>
+      </c>
+      <c r="AN9" t="n">
+        <v/>
+      </c>
+      <c r="AO9" t="n">
+        <v/>
+      </c>
+      <c r="AP9" t="n">
+        <v/>
+      </c>
+      <c r="AQ9" t="n">
+        <v/>
+      </c>
+      <c r="AR9" t="n">
+        <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="n">
-        <v/>
-      </c>
-      <c r="B10" t="n">
-        <v/>
-      </c>
-      <c r="C10" t="n">
-        <v/>
-      </c>
-      <c r="D10" t="n">
-        <v/>
-      </c>
-      <c r="E10" t="n">
-        <v/>
-      </c>
-      <c r="F10" t="n">
-        <v/>
-      </c>
-      <c r="G10" t="n">
-        <v/>
-      </c>
-      <c r="H10" t="n">
-        <v/>
-      </c>
-      <c r="J10" t="inlineStr">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>30-April-2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>dsl</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v/>
+      </c>
+      <c r="K10" t="n">
+        <v/>
+      </c>
+      <c r="L10" t="n">
+        <v/>
+      </c>
+      <c r="M10" t="n">
+        <v/>
+      </c>
+      <c r="N10" t="n">
+        <v/>
+      </c>
+      <c r="O10" t="n">
+        <v/>
+      </c>
+      <c r="P10" t="n">
+        <v/>
+      </c>
+      <c r="Q10" t="n">
+        <v/>
+      </c>
+      <c r="S10" t="inlineStr">
         <is>
           <t>28-April-2026</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>201</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
         <is>
           <t>27-April-2026</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="AC10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="AD10" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="AE10" t="inlineStr">
         <is>
           <t>201</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB10" t="n">
-        <v/>
-      </c>
-      <c r="AC10" t="n">
-        <v/>
-      </c>
-      <c r="AD10" t="n">
-        <v/>
-      </c>
-      <c r="AE10" t="n">
-        <v/>
-      </c>
-      <c r="AF10" t="n">
-        <v/>
-      </c>
-      <c r="AG10" t="n">
-        <v/>
-      </c>
-      <c r="AH10" t="n">
-        <v/>
-      </c>
-      <c r="AI10" t="n">
-        <v/>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>23-April-2026</t>
-        </is>
-      </c>
-      <c r="AL10" t="inlineStr">
-        <is>
-          <t>dsl</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>230</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>201</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AP10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AQ10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK10" t="n">
+        <v/>
+      </c>
+      <c r="AL10" t="n">
+        <v/>
+      </c>
+      <c r="AM10" t="n">
+        <v/>
+      </c>
+      <c r="AN10" t="n">
+        <v/>
+      </c>
+      <c r="AO10" t="n">
+        <v/>
+      </c>
+      <c r="AP10" t="n">
+        <v/>
+      </c>
+      <c r="AQ10" t="n">
+        <v/>
+      </c>
+      <c r="AR10" t="n">
+        <v/>
       </c>
     </row>
   </sheetData>

--- a/minio-report-tracker/xlxs/dev01.xlsx
+++ b/minio-report-tracker/xlxs/dev01.xlsx
@@ -651,7 +651,7 @@
   <dimension ref="A1:AR10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="6" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
@@ -662,21 +662,21 @@
     <col width="2" customWidth="1" min="9" max="9"/>
     <col width="15" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="5" customWidth="1" min="12" max="12"/>
-    <col width="5" customWidth="1" min="13" max="13"/>
+    <col width="6" customWidth="1" min="12" max="12"/>
+    <col width="6" customWidth="1" min="13" max="13"/>
     <col width="5" customWidth="1" min="14" max="14"/>
-    <col width="5" customWidth="1" min="15" max="15"/>
-    <col width="5" customWidth="1" min="16" max="16"/>
-    <col width="5" customWidth="1" min="17" max="17"/>
+    <col width="4" customWidth="1" min="15" max="15"/>
+    <col width="4" customWidth="1" min="16" max="16"/>
+    <col width="4" customWidth="1" min="17" max="17"/>
     <col width="2" customWidth="1" min="18" max="18"/>
     <col width="15" customWidth="1" min="19" max="19"/>
     <col width="16" customWidth="1" min="20" max="20"/>
-    <col width="6" customWidth="1" min="21" max="21"/>
-    <col width="6" customWidth="1" min="22" max="22"/>
+    <col width="5" customWidth="1" min="21" max="21"/>
+    <col width="5" customWidth="1" min="22" max="22"/>
     <col width="5" customWidth="1" min="23" max="23"/>
-    <col width="4" customWidth="1" min="24" max="24"/>
-    <col width="4" customWidth="1" min="25" max="25"/>
-    <col width="4" customWidth="1" min="26" max="26"/>
+    <col width="5" customWidth="1" min="24" max="24"/>
+    <col width="5" customWidth="1" min="25" max="25"/>
+    <col width="5" customWidth="1" min="26" max="26"/>
     <col width="2" customWidth="1" min="27" max="27"/>
     <col width="15" customWidth="1" min="28" max="28"/>
     <col width="16" customWidth="1" min="29" max="29"/>
@@ -689,12 +689,12 @@
     <col width="2" customWidth="1" min="36" max="36"/>
     <col width="15" customWidth="1" min="37" max="37"/>
     <col width="16" customWidth="1" min="38" max="38"/>
-    <col width="5" customWidth="1" min="39" max="39"/>
-    <col width="5" customWidth="1" min="40" max="40"/>
+    <col width="6" customWidth="1" min="39" max="39"/>
+    <col width="6" customWidth="1" min="40" max="40"/>
     <col width="5" customWidth="1" min="41" max="41"/>
-    <col width="5" customWidth="1" min="42" max="42"/>
-    <col width="5" customWidth="1" min="43" max="43"/>
-    <col width="5" customWidth="1" min="44" max="44"/>
+    <col width="4" customWidth="1" min="42" max="42"/>
+    <col width="4" customWidth="1" min="43" max="43"/>
+    <col width="4" customWidth="1" min="44" max="44"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -902,399 +902,399 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>01-May-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>597</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>30-April-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>29-April-2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
         <is>
           <t>28-April-2026</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AI2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AK2" t="inlineStr">
         <is>
           <t>27-April-2026</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AL2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AM2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
+      <c r="AN2" t="inlineStr">
         <is>
           <t>597</t>
         </is>
       </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AH2" t="inlineStr">
+      <c r="AQ2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AI2" t="inlineStr">
+      <c r="AR2" t="inlineStr">
         <is>
           <t>9</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>24-April-2026</t>
-        </is>
-      </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>masterdata-ara</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>01-May-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>336</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>30-April-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>29-April-2026</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
         <is>
           <t>28-April-2026</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
         <is>
           <t>27-April-2026</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
+      <c r="AL3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="AD3" t="inlineStr">
+      <c r="AM3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="AE3" t="inlineStr">
+      <c r="AN3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
         <is>
           <t>78</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>24-April-2026</t>
-        </is>
-      </c>
-      <c r="AL3" t="inlineStr">
-        <is>
-          <t>masterdata-eng</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>944</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AP3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AQ3" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
@@ -1306,172 +1306,172 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>01-May-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>30-April-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
         <is>
           <t>29-April-2026</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
         <is>
           <t>28-April-2026</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="AE4" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
+      <c r="AH4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
         <is>
           <t>27-April-2026</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
+      <c r="AL4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>24-April-2026</t>
-        </is>
-      </c>
-      <c r="AL4" t="inlineStr">
-        <is>
-          <t>masterdata-fra</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
@@ -1508,194 +1508,194 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>01-May-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>944</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>30-April-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
         <is>
           <t>29-April-2026</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>509</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>342</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>116</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>39</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="AB5" t="inlineStr">
         <is>
           <t>28-April-2026</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="AE5" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
         <is>
           <t>27-April-2026</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
+      <c r="AL5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="AD5" t="inlineStr">
+      <c r="AM5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="AE5" t="inlineStr">
+      <c r="AN5" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG5" t="inlineStr">
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>24-April-2026</t>
-        </is>
-      </c>
-      <c r="AL5" t="inlineStr">
-        <is>
-          <t>partner</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>509</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>350</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
-      <c r="AP5" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
       <c r="AQ5" t="inlineStr">
         <is>
           <t>0</t>
@@ -1703,922 +1703,970 @@
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>01-May-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>30-April-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
         <is>
           <t>29-April-2026</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>101</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>161</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="Z6" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="AB6" t="inlineStr">
         <is>
           <t>28-April-2026</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="AE6" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
+      <c r="AH6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
         <is>
           <t>27-April-2026</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
+      <c r="AL6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="AD6" t="inlineStr">
+      <c r="AM6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="AE6" t="inlineStr">
+      <c r="AN6" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG6" t="inlineStr">
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AH6" t="inlineStr">
+      <c r="AQ6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>24-April-2026</t>
-        </is>
-      </c>
-      <c r="AL6" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>288</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>282</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AP6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>01-May-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>509</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>350</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>30-April-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>509</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>350</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>116</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>29-April-2026</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>106</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>94</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
         <is>
           <t>28-April-2026</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>509</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="AE7" t="inlineStr">
         <is>
           <t>350</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="AF7" t="inlineStr">
         <is>
           <t>116</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="AG7" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AK7" t="inlineStr">
         <is>
           <t>27-April-2026</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
+      <c r="AL7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="AD7" t="inlineStr">
+      <c r="AM7" t="inlineStr">
         <is>
           <t>509</t>
         </is>
       </c>
-      <c r="AE7" t="inlineStr">
+      <c r="AN7" t="inlineStr">
         <is>
           <t>350</t>
         </is>
       </c>
-      <c r="AF7" t="inlineStr">
+      <c r="AO7" t="inlineStr">
         <is>
           <t>116</t>
         </is>
       </c>
-      <c r="AG7" t="inlineStr">
+      <c r="AP7" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
         <is>
           <t>12</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>24-April-2026</t>
-        </is>
-      </c>
-      <c r="AL7" t="inlineStr">
-        <is>
-          <t>dsl</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>230</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
-      <c r="AP7" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
-      <c r="AQ7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>01-May-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>30-April-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J8" t="n">
+      <c r="S8" t="n">
         <v/>
       </c>
-      <c r="K8" t="n">
+      <c r="T8" t="n">
         <v/>
       </c>
-      <c r="L8" t="n">
+      <c r="U8" t="n">
         <v/>
       </c>
-      <c r="M8" t="n">
+      <c r="V8" t="n">
         <v/>
       </c>
-      <c r="N8" t="n">
+      <c r="W8" t="n">
         <v/>
       </c>
-      <c r="O8" t="n">
+      <c r="X8" t="n">
         <v/>
       </c>
-      <c r="P8" t="n">
+      <c r="Y8" t="n">
         <v/>
       </c>
-      <c r="Q8" t="n">
+      <c r="Z8" t="n">
         <v/>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>28-April-2026</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="AD8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="AE8" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="AI8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AK8" t="inlineStr">
         <is>
           <t>27-April-2026</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
+      <c r="AL8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="AD8" t="inlineStr">
+      <c r="AM8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="AE8" t="inlineStr">
+      <c r="AN8" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH8" t="inlineStr">
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AI8" t="inlineStr">
+      <c r="AR8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
-      </c>
-      <c r="AK8" t="n">
-        <v/>
-      </c>
-      <c r="AL8" t="n">
-        <v/>
-      </c>
-      <c r="AM8" t="n">
-        <v/>
-      </c>
-      <c r="AN8" t="n">
-        <v/>
-      </c>
-      <c r="AO8" t="n">
-        <v/>
-      </c>
-      <c r="AP8" t="n">
-        <v/>
-      </c>
-      <c r="AQ8" t="n">
-        <v/>
-      </c>
-      <c r="AR8" t="n">
-        <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>01-May-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>resident</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1142</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>1142</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>30-April-2026</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J9" t="n">
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S9" t="n">
         <v/>
       </c>
-      <c r="K9" t="n">
+      <c r="T9" t="n">
         <v/>
       </c>
-      <c r="L9" t="n">
+      <c r="U9" t="n">
         <v/>
       </c>
-      <c r="M9" t="n">
+      <c r="V9" t="n">
         <v/>
       </c>
-      <c r="N9" t="n">
+      <c r="W9" t="n">
         <v/>
       </c>
-      <c r="O9" t="n">
+      <c r="X9" t="n">
         <v/>
       </c>
-      <c r="P9" t="n">
+      <c r="Y9" t="n">
         <v/>
       </c>
-      <c r="Q9" t="n">
+      <c r="Z9" t="n">
         <v/>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="AB9" t="inlineStr">
         <is>
           <t>28-April-2026</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="AC9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="AD9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="AE9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
         <is>
           <t>27-April-2026</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
+      <c r="AL9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="AD9" t="inlineStr">
+      <c r="AM9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="AE9" t="inlineStr">
+      <c r="AN9" t="inlineStr">
         <is>
           <t>1140</t>
         </is>
       </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG9" t="inlineStr">
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK9" t="n">
-        <v/>
-      </c>
-      <c r="AL9" t="n">
-        <v/>
-      </c>
-      <c r="AM9" t="n">
-        <v/>
-      </c>
-      <c r="AN9" t="n">
-        <v/>
-      </c>
-      <c r="AO9" t="n">
-        <v/>
-      </c>
-      <c r="AP9" t="n">
-        <v/>
-      </c>
-      <c r="AQ9" t="n">
-        <v/>
-      </c>
-      <c r="AR9" t="n">
-        <v/>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>01-May-2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>dsl</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>201</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>30-April-2026</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J10" t="n">
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S10" t="n">
         <v/>
       </c>
-      <c r="K10" t="n">
+      <c r="T10" t="n">
         <v/>
       </c>
-      <c r="L10" t="n">
+      <c r="U10" t="n">
         <v/>
       </c>
-      <c r="M10" t="n">
+      <c r="V10" t="n">
         <v/>
       </c>
-      <c r="N10" t="n">
+      <c r="W10" t="n">
         <v/>
       </c>
-      <c r="O10" t="n">
+      <c r="X10" t="n">
         <v/>
       </c>
-      <c r="P10" t="n">
+      <c r="Y10" t="n">
         <v/>
       </c>
-      <c r="Q10" t="n">
+      <c r="Z10" t="n">
         <v/>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="AB10" t="inlineStr">
         <is>
           <t>28-April-2026</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="AC10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="AD10" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="AE10" t="inlineStr">
         <is>
           <t>201</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
         <is>
           <t>27-April-2026</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
+      <c r="AL10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="AD10" t="inlineStr">
+      <c r="AM10" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="AE10" t="inlineStr">
+      <c r="AN10" t="inlineStr">
         <is>
           <t>201</t>
         </is>
       </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG10" t="inlineStr">
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AP10" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK10" t="n">
-        <v/>
-      </c>
-      <c r="AL10" t="n">
-        <v/>
-      </c>
-      <c r="AM10" t="n">
-        <v/>
-      </c>
-      <c r="AN10" t="n">
-        <v/>
-      </c>
-      <c r="AO10" t="n">
-        <v/>
-      </c>
-      <c r="AP10" t="n">
-        <v/>
-      </c>
-      <c r="AQ10" t="n">
-        <v/>
-      </c>
-      <c r="AR10" t="n">
-        <v/>
+      <c r="AQ10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/minio-report-tracker/xlxs/dev01.xlsx
+++ b/minio-report-tracker/xlxs/dev01.xlsx
@@ -660,7 +660,7 @@
     <col width="4" customWidth="1" min="7" max="7"/>
     <col width="4" customWidth="1" min="8" max="8"/>
     <col width="2" customWidth="1" min="9" max="9"/>
-    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
     <col width="6" customWidth="1" min="12" max="12"/>
     <col width="6" customWidth="1" min="13" max="13"/>
@@ -671,21 +671,21 @@
     <col width="2" customWidth="1" min="18" max="18"/>
     <col width="15" customWidth="1" min="19" max="19"/>
     <col width="16" customWidth="1" min="20" max="20"/>
-    <col width="5" customWidth="1" min="21" max="21"/>
-    <col width="5" customWidth="1" min="22" max="22"/>
+    <col width="6" customWidth="1" min="21" max="21"/>
+    <col width="6" customWidth="1" min="22" max="22"/>
     <col width="5" customWidth="1" min="23" max="23"/>
-    <col width="5" customWidth="1" min="24" max="24"/>
-    <col width="5" customWidth="1" min="25" max="25"/>
-    <col width="5" customWidth="1" min="26" max="26"/>
+    <col width="4" customWidth="1" min="24" max="24"/>
+    <col width="4" customWidth="1" min="25" max="25"/>
+    <col width="4" customWidth="1" min="26" max="26"/>
     <col width="2" customWidth="1" min="27" max="27"/>
     <col width="15" customWidth="1" min="28" max="28"/>
     <col width="16" customWidth="1" min="29" max="29"/>
-    <col width="6" customWidth="1" min="30" max="30"/>
-    <col width="6" customWidth="1" min="31" max="31"/>
+    <col width="5" customWidth="1" min="30" max="30"/>
+    <col width="5" customWidth="1" min="31" max="31"/>
     <col width="5" customWidth="1" min="32" max="32"/>
-    <col width="4" customWidth="1" min="33" max="33"/>
-    <col width="4" customWidth="1" min="34" max="34"/>
-    <col width="4" customWidth="1" min="35" max="35"/>
+    <col width="5" customWidth="1" min="33" max="33"/>
+    <col width="5" customWidth="1" min="34" max="34"/>
+    <col width="5" customWidth="1" min="35" max="35"/>
     <col width="2" customWidth="1" min="36" max="36"/>
     <col width="15" customWidth="1" min="37" max="37"/>
     <col width="16" customWidth="1" min="38" max="38"/>
@@ -902,184 +902,184 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>04-May-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>597</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>01-May-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>597</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>30-April-2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>29-April-2026</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="AH2" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
         <is>
           <t>28-April-2026</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AL2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AM2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
+      <c r="AN2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>27-April-2026</t>
-        </is>
-      </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>auth</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>612</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>597</t>
-        </is>
-      </c>
       <c r="AO2" t="inlineStr">
         <is>
           <t>0</t>
@@ -1087,7 +1087,7 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
@@ -1104,167 +1104,167 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>04-May-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>336</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>01-May-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>30-April-2026</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
         <is>
           <t>29-April-2026</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
         <is>
           <t>28-April-2026</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>idrepo</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>414</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>336</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>27-April-2026</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
@@ -1306,167 +1306,167 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>04-May-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>01-May-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
         <is>
           <t>30-April-2026</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
         <is>
           <t>29-April-2026</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="AE4" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
+      <c r="AH4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
         <is>
           <t>28-April-2026</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>masterdata-ara</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>27-April-2026</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
@@ -1508,167 +1508,167 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>04-May-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>944</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>01-May-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
         <is>
           <t>30-April-2026</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
         <is>
           <t>29-April-2026</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>509</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="AE5" t="inlineStr">
         <is>
           <t>342</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="AF5" t="inlineStr">
         <is>
           <t>116</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="AG5" t="inlineStr">
         <is>
           <t>39</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AK5" t="inlineStr">
         <is>
           <t>28-April-2026</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>masterdata-eng</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>944</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>27-April-2026</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
@@ -1710,167 +1710,167 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>04-May-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>01-May-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
         <is>
           <t>30-April-2026</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
         <is>
           <t>29-April-2026</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="AE6" t="inlineStr">
         <is>
           <t>101</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="AF6" t="inlineStr">
         <is>
           <t>161</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="AG6" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
+      <c r="AH6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
+      <c r="AI6" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AK6" t="inlineStr">
         <is>
           <t>28-April-2026</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>masterdata-fra</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>27-April-2026</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
@@ -1912,167 +1912,167 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>04-May-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>509</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>350</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>01-May-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>509</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>350</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>116</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>30-April-2026</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>509</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>350</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>116</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>29-April-2026</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="AE7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="AF7" t="inlineStr">
         <is>
           <t>106</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="AG7" t="inlineStr">
         <is>
           <t>94</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
         <is>
           <t>28-April-2026</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>partner</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>509</t>
-        </is>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>350</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
-      <c r="AG7" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>27-April-2026</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
@@ -2114,151 +2114,151 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>04-May-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>01-May-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>30-April-2026</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="S8" t="n">
+      <c r="AB8" t="n">
         <v/>
       </c>
-      <c r="T8" t="n">
+      <c r="AC8" t="n">
         <v/>
       </c>
-      <c r="U8" t="n">
+      <c r="AD8" t="n">
         <v/>
       </c>
-      <c r="V8" t="n">
+      <c r="AE8" t="n">
         <v/>
       </c>
-      <c r="W8" t="n">
+      <c r="AF8" t="n">
         <v/>
       </c>
-      <c r="X8" t="n">
+      <c r="AG8" t="n">
         <v/>
       </c>
-      <c r="Y8" t="n">
+      <c r="AH8" t="n">
         <v/>
       </c>
-      <c r="Z8" t="n">
+      <c r="AI8" t="n">
         <v/>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AK8" t="inlineStr">
         <is>
           <t>28-April-2026</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="AD8" t="inlineStr">
-        <is>
-          <t>288</t>
-        </is>
-      </c>
-      <c r="AE8" t="inlineStr">
-        <is>
-          <t>282</t>
-        </is>
-      </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>27-April-2026</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
@@ -2300,168 +2300,168 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>04-May-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>resident</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1142</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>1137</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>01-May-2026</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
         <is>
           <t>30-April-2026</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S9" t="n">
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB9" t="n">
         <v/>
       </c>
-      <c r="T9" t="n">
+      <c r="AC9" t="n">
         <v/>
       </c>
-      <c r="U9" t="n">
+      <c r="AD9" t="n">
         <v/>
       </c>
-      <c r="V9" t="n">
+      <c r="AE9" t="n">
         <v/>
       </c>
-      <c r="W9" t="n">
+      <c r="AF9" t="n">
         <v/>
       </c>
-      <c r="X9" t="n">
+      <c r="AG9" t="n">
         <v/>
       </c>
-      <c r="Y9" t="n">
+      <c r="AH9" t="n">
         <v/>
       </c>
-      <c r="Z9" t="n">
+      <c r="AI9" t="n">
         <v/>
       </c>
-      <c r="AB9" t="inlineStr">
+      <c r="AK9" t="inlineStr">
         <is>
           <t>28-April-2026</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
+      <c r="AL9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="AD9" t="inlineStr">
+      <c r="AM9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="AE9" t="inlineStr">
+      <c r="AN9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>27-April-2026</t>
-        </is>
-      </c>
-      <c r="AL9" t="inlineStr">
-        <is>
-          <t>resident</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>1142</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>1140</t>
-        </is>
-      </c>
       <c r="AO9" t="inlineStr">
         <is>
           <t>0</t>
@@ -2469,7 +2469,7 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
@@ -2486,168 +2486,168 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>04-May-2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>dsl</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>201</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>01-May-2026</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>201</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
         <is>
           <t>30-April-2026</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S10" t="n">
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB10" t="n">
         <v/>
       </c>
-      <c r="T10" t="n">
+      <c r="AC10" t="n">
         <v/>
       </c>
-      <c r="U10" t="n">
+      <c r="AD10" t="n">
         <v/>
       </c>
-      <c r="V10" t="n">
+      <c r="AE10" t="n">
         <v/>
       </c>
-      <c r="W10" t="n">
+      <c r="AF10" t="n">
         <v/>
       </c>
-      <c r="X10" t="n">
+      <c r="AG10" t="n">
         <v/>
       </c>
-      <c r="Y10" t="n">
+      <c r="AH10" t="n">
         <v/>
       </c>
-      <c r="Z10" t="n">
+      <c r="AI10" t="n">
         <v/>
       </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AK10" t="inlineStr">
         <is>
           <t>28-April-2026</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
+      <c r="AL10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="AD10" t="inlineStr">
+      <c r="AM10" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="AE10" t="inlineStr">
+      <c r="AN10" t="inlineStr">
         <is>
           <t>201</t>
         </is>
       </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>27-April-2026</t>
-        </is>
-      </c>
-      <c r="AL10" t="inlineStr">
-        <is>
-          <t>dsl</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>230</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>201</t>
-        </is>
-      </c>
       <c r="AO10" t="inlineStr">
         <is>
           <t>0</t>
@@ -2655,7 +2655,7 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">

--- a/minio-report-tracker/xlxs/dev01.xlsx
+++ b/minio-report-tracker/xlxs/dev01.xlsx
@@ -669,7 +669,7 @@
     <col width="4" customWidth="1" min="16" max="16"/>
     <col width="4" customWidth="1" min="17" max="17"/>
     <col width="2" customWidth="1" min="18" max="18"/>
-    <col width="15" customWidth="1" min="19" max="19"/>
+    <col width="13" customWidth="1" min="19" max="19"/>
     <col width="16" customWidth="1" min="20" max="20"/>
     <col width="6" customWidth="1" min="21" max="21"/>
     <col width="6" customWidth="1" min="22" max="22"/>
@@ -680,21 +680,21 @@
     <col width="2" customWidth="1" min="27" max="27"/>
     <col width="15" customWidth="1" min="28" max="28"/>
     <col width="16" customWidth="1" min="29" max="29"/>
-    <col width="5" customWidth="1" min="30" max="30"/>
-    <col width="5" customWidth="1" min="31" max="31"/>
+    <col width="6" customWidth="1" min="30" max="30"/>
+    <col width="6" customWidth="1" min="31" max="31"/>
     <col width="5" customWidth="1" min="32" max="32"/>
-    <col width="5" customWidth="1" min="33" max="33"/>
-    <col width="5" customWidth="1" min="34" max="34"/>
-    <col width="5" customWidth="1" min="35" max="35"/>
+    <col width="4" customWidth="1" min="33" max="33"/>
+    <col width="4" customWidth="1" min="34" max="34"/>
+    <col width="4" customWidth="1" min="35" max="35"/>
     <col width="2" customWidth="1" min="36" max="36"/>
     <col width="15" customWidth="1" min="37" max="37"/>
     <col width="16" customWidth="1" min="38" max="38"/>
-    <col width="6" customWidth="1" min="39" max="39"/>
-    <col width="6" customWidth="1" min="40" max="40"/>
+    <col width="5" customWidth="1" min="39" max="39"/>
+    <col width="5" customWidth="1" min="40" max="40"/>
     <col width="5" customWidth="1" min="41" max="41"/>
-    <col width="4" customWidth="1" min="42" max="42"/>
-    <col width="4" customWidth="1" min="43" max="43"/>
-    <col width="4" customWidth="1" min="44" max="44"/>
+    <col width="5" customWidth="1" min="42" max="42"/>
+    <col width="5" customWidth="1" min="43" max="43"/>
+    <col width="5" customWidth="1" min="44" max="44"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -902,399 +902,399 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>05-May-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>597</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>04-May-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>597</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>01-May-2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>597</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>30-April-2026</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AI2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AK2" t="inlineStr">
         <is>
           <t>29-April-2026</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AL2" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AM2" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
+      <c r="AN2" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AH2" t="inlineStr">
+      <c r="AQ2" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>28-April-2026</t>
-        </is>
-      </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>auth</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>612</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>598</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>05-May-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>336</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>04-May-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>01-May-2026</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
         <is>
           <t>30-April-2026</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
         <is>
           <t>29-April-2026</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
+      <c r="AL3" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="AD3" t="inlineStr">
+      <c r="AM3" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="AE3" t="inlineStr">
+      <c r="AN3" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>28-April-2026</t>
-        </is>
-      </c>
-      <c r="AL3" t="inlineStr">
-        <is>
-          <t>idrepo</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>414</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>336</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AP3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
@@ -1306,172 +1306,172 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>05-May-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>928</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>04-May-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
         <is>
           <t>01-May-2026</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
         <is>
           <t>30-April-2026</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="AE4" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
+      <c r="AH4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
         <is>
           <t>29-April-2026</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
+      <c r="AL4" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>28-April-2026</t>
-        </is>
-      </c>
-      <c r="AL4" t="inlineStr">
-        <is>
-          <t>masterdata-ara</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
@@ -1508,598 +1508,598 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>05-May-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>944</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>04-May-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
         <is>
           <t>01-May-2026</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
         <is>
           <t>30-April-2026</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="AE5" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
         <is>
           <t>29-April-2026</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
+      <c r="AL5" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="AD5" t="inlineStr">
+      <c r="AM5" t="inlineStr">
         <is>
           <t>509</t>
         </is>
       </c>
-      <c r="AE5" t="inlineStr">
+      <c r="AN5" t="inlineStr">
         <is>
           <t>342</t>
         </is>
       </c>
-      <c r="AF5" t="inlineStr">
+      <c r="AO5" t="inlineStr">
         <is>
           <t>116</t>
         </is>
       </c>
-      <c r="AG5" t="inlineStr">
+      <c r="AP5" t="inlineStr">
         <is>
           <t>39</t>
         </is>
       </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
         <is>
           <t>12</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>28-April-2026</t>
-        </is>
-      </c>
-      <c r="AL5" t="inlineStr">
-        <is>
-          <t>masterdata-eng</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>944</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AP5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AQ5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>05-May-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>04-May-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
         <is>
           <t>01-May-2026</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
         <is>
           <t>30-April-2026</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="AE6" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
+      <c r="AH6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
         <is>
           <t>29-April-2026</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
+      <c r="AL6" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="AD6" t="inlineStr">
+      <c r="AM6" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="AE6" t="inlineStr">
+      <c r="AN6" t="inlineStr">
         <is>
           <t>101</t>
         </is>
       </c>
-      <c r="AF6" t="inlineStr">
+      <c r="AO6" t="inlineStr">
         <is>
           <t>161</t>
         </is>
       </c>
-      <c r="AG6" t="inlineStr">
+      <c r="AP6" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="AH6" t="inlineStr">
+      <c r="AQ6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AI6" t="inlineStr">
+      <c r="AR6" t="inlineStr">
         <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>28-April-2026</t>
-        </is>
-      </c>
-      <c r="AL6" t="inlineStr">
-        <is>
-          <t>masterdata-fra</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AP6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AQ6" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>05-May-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>509</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>350</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>04-May-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>509</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>350</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>116</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>01-May-2026</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>509</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>350</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>116</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>30-April-2026</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>509</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="AE7" t="inlineStr">
         <is>
           <t>350</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="AF7" t="inlineStr">
         <is>
           <t>116</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="AG7" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AK7" t="inlineStr">
         <is>
           <t>29-April-2026</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
+      <c r="AL7" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="AD7" t="inlineStr">
+      <c r="AM7" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="AE7" t="inlineStr">
+      <c r="AN7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AF7" t="inlineStr">
+      <c r="AO7" t="inlineStr">
         <is>
           <t>106</t>
         </is>
       </c>
-      <c r="AG7" t="inlineStr">
+      <c r="AP7" t="inlineStr">
         <is>
           <t>94</t>
         </is>
       </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>28-April-2026</t>
-        </is>
-      </c>
-      <c r="AL7" t="inlineStr">
-        <is>
-          <t>partner</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>509</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>350</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
-      <c r="AP7" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
       <c r="AQ7" t="inlineStr">
         <is>
           <t>0</t>
@@ -2107,566 +2107,566 @@
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>05-May-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>04-May-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>01-May-2026</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>30-April-2026</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="AD8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="AE8" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="AI8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AB8" t="n">
+      <c r="AK8" t="n">
         <v/>
       </c>
-      <c r="AC8" t="n">
+      <c r="AL8" t="n">
         <v/>
       </c>
-      <c r="AD8" t="n">
+      <c r="AM8" t="n">
         <v/>
       </c>
-      <c r="AE8" t="n">
+      <c r="AN8" t="n">
         <v/>
       </c>
-      <c r="AF8" t="n">
+      <c r="AO8" t="n">
         <v/>
       </c>
-      <c r="AG8" t="n">
+      <c r="AP8" t="n">
         <v/>
       </c>
-      <c r="AH8" t="n">
+      <c r="AQ8" t="n">
         <v/>
       </c>
-      <c r="AI8" t="n">
+      <c r="AR8" t="n">
         <v/>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>28-April-2026</t>
-        </is>
-      </c>
-      <c r="AL8" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>288</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>282</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AP8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>05-May-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>resident</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1142</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>1142</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>04-May-2026</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>1137</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
         <is>
           <t>01-May-2026</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
         <is>
           <t>30-April-2026</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="AC9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="AD9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="AE9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB9" t="n">
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK9" t="n">
         <v/>
       </c>
-      <c r="AC9" t="n">
+      <c r="AL9" t="n">
         <v/>
       </c>
-      <c r="AD9" t="n">
+      <c r="AM9" t="n">
         <v/>
       </c>
-      <c r="AE9" t="n">
+      <c r="AN9" t="n">
         <v/>
       </c>
-      <c r="AF9" t="n">
+      <c r="AO9" t="n">
         <v/>
       </c>
-      <c r="AG9" t="n">
+      <c r="AP9" t="n">
         <v/>
       </c>
-      <c r="AH9" t="n">
+      <c r="AQ9" t="n">
         <v/>
       </c>
-      <c r="AI9" t="n">
+      <c r="AR9" t="n">
         <v/>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>28-April-2026</t>
-        </is>
-      </c>
-      <c r="AL9" t="inlineStr">
-        <is>
-          <t>resident</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>1142</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>1142</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AP9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>05-May-2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>dsl</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>201</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>04-May-2026</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>201</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
         <is>
           <t>01-May-2026</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>201</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
         <is>
           <t>30-April-2026</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="AC10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="AD10" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="AE10" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB10" t="n">
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK10" t="n">
         <v/>
       </c>
-      <c r="AC10" t="n">
+      <c r="AL10" t="n">
         <v/>
       </c>
-      <c r="AD10" t="n">
+      <c r="AM10" t="n">
         <v/>
       </c>
-      <c r="AE10" t="n">
+      <c r="AN10" t="n">
         <v/>
       </c>
-      <c r="AF10" t="n">
+      <c r="AO10" t="n">
         <v/>
       </c>
-      <c r="AG10" t="n">
+      <c r="AP10" t="n">
         <v/>
       </c>
-      <c r="AH10" t="n">
+      <c r="AQ10" t="n">
         <v/>
       </c>
-      <c r="AI10" t="n">
+      <c r="AR10" t="n">
         <v/>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>28-April-2026</t>
-        </is>
-      </c>
-      <c r="AL10" t="inlineStr">
-        <is>
-          <t>dsl</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>230</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>201</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AP10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
       </c>
     </row>
   </sheetData>

--- a/minio-report-tracker/xlxs/dev01.xlsx
+++ b/minio-report-tracker/xlxs/dev01.xlsx
@@ -678,7 +678,7 @@
     <col width="4" customWidth="1" min="25" max="25"/>
     <col width="4" customWidth="1" min="26" max="26"/>
     <col width="2" customWidth="1" min="27" max="27"/>
-    <col width="15" customWidth="1" min="28" max="28"/>
+    <col width="13" customWidth="1" min="28" max="28"/>
     <col width="16" customWidth="1" min="29" max="29"/>
     <col width="6" customWidth="1" min="30" max="30"/>
     <col width="6" customWidth="1" min="31" max="31"/>
@@ -689,12 +689,12 @@
     <col width="2" customWidth="1" min="36" max="36"/>
     <col width="15" customWidth="1" min="37" max="37"/>
     <col width="16" customWidth="1" min="38" max="38"/>
-    <col width="5" customWidth="1" min="39" max="39"/>
-    <col width="5" customWidth="1" min="40" max="40"/>
+    <col width="6" customWidth="1" min="39" max="39"/>
+    <col width="6" customWidth="1" min="40" max="40"/>
     <col width="5" customWidth="1" min="41" max="41"/>
-    <col width="5" customWidth="1" min="42" max="42"/>
-    <col width="5" customWidth="1" min="43" max="43"/>
-    <col width="5" customWidth="1" min="44" max="44"/>
+    <col width="4" customWidth="1" min="42" max="42"/>
+    <col width="4" customWidth="1" min="43" max="43"/>
+    <col width="4" customWidth="1" min="44" max="44"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -902,399 +902,399 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>06-May-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>594</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>05-May-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>597</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>04-May-2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>597</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>01-May-2026</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>597</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="AH2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AI2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AK2" t="inlineStr">
         <is>
           <t>30-April-2026</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AL2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AM2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
+      <c r="AN2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AI2" t="inlineStr">
+      <c r="AR2" t="inlineStr">
         <is>
           <t>9</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>29-April-2026</t>
-        </is>
-      </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>masterdata-ara</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>06-May-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>336</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>05-May-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>04-May-2026</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
         <is>
           <t>01-May-2026</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
         <is>
           <t>30-April-2026</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
+      <c r="AL3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="AD3" t="inlineStr">
+      <c r="AM3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="AE3" t="inlineStr">
+      <c r="AN3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
         <is>
           <t>78</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>29-April-2026</t>
-        </is>
-      </c>
-      <c r="AL3" t="inlineStr">
-        <is>
-          <t>masterdata-eng</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>944</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AP3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AQ3" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
@@ -1306,172 +1306,172 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>06-May-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>928</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>05-May-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>928</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
         <is>
           <t>04-May-2026</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
         <is>
           <t>01-May-2026</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="AE4" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
+      <c r="AH4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
         <is>
           <t>30-April-2026</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
+      <c r="AL4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>29-April-2026</t>
-        </is>
-      </c>
-      <c r="AL4" t="inlineStr">
-        <is>
-          <t>masterdata-fra</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
@@ -1508,194 +1508,194 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>06-May-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>944</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>05-May-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
         <is>
           <t>04-May-2026</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
         <is>
           <t>01-May-2026</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="AE5" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
         <is>
           <t>30-April-2026</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
+      <c r="AL5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="AD5" t="inlineStr">
+      <c r="AM5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="AE5" t="inlineStr">
+      <c r="AN5" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG5" t="inlineStr">
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>29-April-2026</t>
-        </is>
-      </c>
-      <c r="AL5" t="inlineStr">
-        <is>
-          <t>partner</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>509</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>342</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
-      <c r="AP5" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
       <c r="AQ5" t="inlineStr">
         <is>
           <t>0</t>
@@ -1703,970 +1703,1018 @@
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>06-May-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>05-May-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
         <is>
           <t>04-May-2026</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
         <is>
           <t>01-May-2026</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="AE6" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
+      <c r="AH6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
         <is>
           <t>30-April-2026</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
+      <c r="AL6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="AD6" t="inlineStr">
+      <c r="AM6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="AE6" t="inlineStr">
+      <c r="AN6" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG6" t="inlineStr">
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AH6" t="inlineStr">
+      <c r="AQ6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>29-April-2026</t>
-        </is>
-      </c>
-      <c r="AL6" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>288</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>161</t>
-        </is>
-      </c>
-      <c r="AP6" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="AQ6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>06-May-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>509</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>350</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>05-May-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>509</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>350</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>116</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>04-May-2026</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>509</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>350</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>116</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>01-May-2026</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>509</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="AE7" t="inlineStr">
         <is>
           <t>350</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="AF7" t="inlineStr">
         <is>
           <t>116</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="AG7" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AK7" t="inlineStr">
         <is>
           <t>30-April-2026</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
+      <c r="AL7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="AD7" t="inlineStr">
+      <c r="AM7" t="inlineStr">
         <is>
           <t>509</t>
         </is>
       </c>
-      <c r="AE7" t="inlineStr">
+      <c r="AN7" t="inlineStr">
         <is>
           <t>350</t>
         </is>
       </c>
-      <c r="AF7" t="inlineStr">
+      <c r="AO7" t="inlineStr">
         <is>
           <t>116</t>
         </is>
       </c>
-      <c r="AG7" t="inlineStr">
+      <c r="AP7" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
         <is>
           <t>12</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>29-April-2026</t>
-        </is>
-      </c>
-      <c r="AL7" t="inlineStr">
-        <is>
-          <t>dsl</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>230</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>106</t>
-        </is>
-      </c>
-      <c r="AP7" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
-      <c r="AQ7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>06-May-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>05-May-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>04-May-2026</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>01-May-2026</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="AD8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="AE8" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="AI8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AK8" t="inlineStr">
         <is>
           <t>30-April-2026</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
+      <c r="AL8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="AD8" t="inlineStr">
+      <c r="AM8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="AE8" t="inlineStr">
+      <c r="AN8" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH8" t="inlineStr">
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AI8" t="inlineStr">
+      <c r="AR8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
-      </c>
-      <c r="AK8" t="n">
-        <v/>
-      </c>
-      <c r="AL8" t="n">
-        <v/>
-      </c>
-      <c r="AM8" t="n">
-        <v/>
-      </c>
-      <c r="AN8" t="n">
-        <v/>
-      </c>
-      <c r="AO8" t="n">
-        <v/>
-      </c>
-      <c r="AP8" t="n">
-        <v/>
-      </c>
-      <c r="AQ8" t="n">
-        <v/>
-      </c>
-      <c r="AR8" t="n">
-        <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>06-May-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>resident</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1142</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>1141</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>05-May-2026</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
         <is>
           <t>04-May-2026</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>1137</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="X9" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
         <is>
           <t>01-May-2026</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="AC9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="AD9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="AE9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
         <is>
           <t>30-April-2026</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
+      <c r="AL9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="AD9" t="inlineStr">
+      <c r="AM9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="AE9" t="inlineStr">
+      <c r="AN9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK9" t="n">
-        <v/>
-      </c>
-      <c r="AL9" t="n">
-        <v/>
-      </c>
-      <c r="AM9" t="n">
-        <v/>
-      </c>
-      <c r="AN9" t="n">
-        <v/>
-      </c>
-      <c r="AO9" t="n">
-        <v/>
-      </c>
-      <c r="AP9" t="n">
-        <v/>
-      </c>
-      <c r="AQ9" t="n">
-        <v/>
-      </c>
-      <c r="AR9" t="n">
-        <v/>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>06-May-2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>dsl</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>05-May-2026</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>201</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
         <is>
           <t>04-May-2026</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>201</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
         <is>
           <t>01-May-2026</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="AC10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="AD10" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="AE10" t="inlineStr">
         <is>
           <t>201</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
         <is>
           <t>30-April-2026</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
+      <c r="AL10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="AD10" t="inlineStr">
+      <c r="AM10" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="AE10" t="inlineStr">
+      <c r="AN10" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG10" t="inlineStr">
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AP10" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK10" t="n">
-        <v/>
-      </c>
-      <c r="AL10" t="n">
-        <v/>
-      </c>
-      <c r="AM10" t="n">
-        <v/>
-      </c>
-      <c r="AN10" t="n">
-        <v/>
-      </c>
-      <c r="AO10" t="n">
-        <v/>
-      </c>
-      <c r="AP10" t="n">
-        <v/>
-      </c>
-      <c r="AQ10" t="n">
-        <v/>
-      </c>
-      <c r="AR10" t="n">
-        <v/>
+      <c r="AQ10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/minio-report-tracker/xlxs/dev01.xlsx
+++ b/minio-report-tracker/xlxs/dev01.xlsx
@@ -656,9 +656,9 @@
     <col width="6" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="5" customWidth="1" min="5" max="5"/>
-    <col width="4" customWidth="1" min="6" max="6"/>
-    <col width="4" customWidth="1" min="7" max="7"/>
-    <col width="4" customWidth="1" min="8" max="8"/>
+    <col width="5" customWidth="1" min="6" max="6"/>
+    <col width="5" customWidth="1" min="7" max="7"/>
+    <col width="5" customWidth="1" min="8" max="8"/>
     <col width="2" customWidth="1" min="9" max="9"/>
     <col width="13" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
@@ -687,7 +687,7 @@
     <col width="4" customWidth="1" min="34" max="34"/>
     <col width="4" customWidth="1" min="35" max="35"/>
     <col width="2" customWidth="1" min="36" max="36"/>
-    <col width="15" customWidth="1" min="37" max="37"/>
+    <col width="13" customWidth="1" min="37" max="37"/>
     <col width="16" customWidth="1" min="38" max="38"/>
     <col width="6" customWidth="1" min="39" max="39"/>
     <col width="6" customWidth="1" min="40" max="40"/>
@@ -902,192 +902,192 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>07-May-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>598</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>06-May-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>594</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>05-May-2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>597</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>04-May-2026</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>597</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="AH2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AI2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AK2" t="inlineStr">
         <is>
           <t>01-May-2026</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AL2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AM2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
+      <c r="AN2" t="inlineStr">
         <is>
           <t>597</t>
         </is>
       </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>30-April-2026</t>
-        </is>
-      </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>auth</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>612</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>598</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
@@ -1104,167 +1104,167 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>07-May-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>336</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>06-May-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>05-May-2026</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
         <is>
           <t>04-May-2026</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
         <is>
           <t>01-May-2026</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>idrepo</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>414</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>336</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>30-April-2026</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
@@ -1306,167 +1306,167 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>07-May-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>06-May-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>928</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
         <is>
           <t>05-May-2026</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>928</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
         <is>
           <t>04-May-2026</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="AE4" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
+      <c r="AH4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
         <is>
           <t>01-May-2026</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>masterdata-ara</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>30-April-2026</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
@@ -1508,167 +1508,167 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>07-May-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>944</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>06-May-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
         <is>
           <t>05-May-2026</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
         <is>
           <t>04-May-2026</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="AE5" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
         <is>
           <t>01-May-2026</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>masterdata-eng</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>944</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>30-April-2026</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
@@ -1710,167 +1710,167 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>07-May-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>06-May-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
         <is>
           <t>05-May-2026</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
         <is>
           <t>04-May-2026</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="AE6" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
+      <c r="AH6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
         <is>
           <t>01-May-2026</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>masterdata-fra</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>30-April-2026</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
@@ -1912,167 +1912,167 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>07-May-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>509</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>350</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>06-May-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>509</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>350</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>116</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>05-May-2026</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>509</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>350</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>116</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>04-May-2026</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>509</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="AE7" t="inlineStr">
         <is>
           <t>350</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="AF7" t="inlineStr">
         <is>
           <t>116</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="AG7" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AK7" t="inlineStr">
         <is>
           <t>01-May-2026</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>partner</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>509</t>
-        </is>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>350</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
-      <c r="AG7" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>30-April-2026</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
@@ -2114,167 +2114,167 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>07-May-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>resident</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>1142</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>1142</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>06-May-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>05-May-2026</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>04-May-2026</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="AD8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="AE8" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="AI8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AK8" t="inlineStr">
         <is>
           <t>01-May-2026</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="AD8" t="inlineStr">
-        <is>
-          <t>288</t>
-        </is>
-      </c>
-      <c r="AE8" t="inlineStr">
-        <is>
-          <t>282</t>
-        </is>
-      </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>30-April-2026</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
@@ -2316,167 +2316,167 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>07-May-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>dsl</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>197</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>06-May-2026</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>1141</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
         <is>
           <t>05-May-2026</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
         <is>
           <t>04-May-2026</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="AC9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="AD9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="AE9" t="inlineStr">
         <is>
           <t>1137</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="AF9" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="AG9" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
         <is>
           <t>01-May-2026</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>resident</t>
-        </is>
-      </c>
-      <c r="AD9" t="inlineStr">
-        <is>
-          <t>1142</t>
-        </is>
-      </c>
-      <c r="AE9" t="inlineStr">
-        <is>
-          <t>1142</t>
-        </is>
-      </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>30-April-2026</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
@@ -2516,186 +2516,170 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" t="n">
+        <v/>
+      </c>
+      <c r="B10" t="n">
+        <v/>
+      </c>
+      <c r="C10" t="n">
+        <v/>
+      </c>
+      <c r="D10" t="n">
+        <v/>
+      </c>
+      <c r="E10" t="n">
+        <v/>
+      </c>
+      <c r="F10" t="n">
+        <v/>
+      </c>
+      <c r="G10" t="n">
+        <v/>
+      </c>
+      <c r="H10" t="n">
+        <v/>
+      </c>
+      <c r="J10" t="inlineStr">
         <is>
           <t>06-May-2026</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
         <is>
           <t>05-May-2026</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>201</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
         <is>
           <t>04-May-2026</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="AC10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="AD10" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="AE10" t="inlineStr">
         <is>
           <t>201</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
         <is>
           <t>01-May-2026</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
+      <c r="AL10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="AD10" t="inlineStr">
+      <c r="AM10" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="AE10" t="inlineStr">
+      <c r="AN10" t="inlineStr">
         <is>
           <t>201</t>
         </is>
       </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>30-April-2026</t>
-        </is>
-      </c>
-      <c r="AL10" t="inlineStr">
-        <is>
-          <t>dsl</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>230</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
       <c r="AO10" t="inlineStr">
         <is>
           <t>0</t>
@@ -2703,7 +2687,7 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">

--- a/minio-report-tracker/xlxs/dev01.xlsx
+++ b/minio-report-tracker/xlxs/dev01.xlsx
@@ -221,6 +221,81 @@
       </nvPicPr>
       <blipFill>
         <a:blip cstate="print" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>88</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="7620000" cy="3810000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>110</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="7620000" cy="3810000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>132</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="7620000" cy="3810000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -523,17 +598,26 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:Q8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="5" customWidth="1" min="3" max="3"/>
-    <col width="5" customWidth="1" min="4" max="4"/>
+    <col width="6" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
     <col width="5" customWidth="1" min="5" max="5"/>
     <col width="4" customWidth="1" min="6" max="6"/>
     <col width="4" customWidth="1" min="7" max="7"/>
     <col width="4" customWidth="1" min="8" max="8"/>
+    <col width="2" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="5" customWidth="1" min="12" max="12"/>
+    <col width="5" customWidth="1" min="13" max="13"/>
+    <col width="5" customWidth="1" min="14" max="14"/>
+    <col width="5" customWidth="1" min="15" max="15"/>
+    <col width="5" customWidth="1" min="16" max="16"/>
+    <col width="5" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -577,44 +661,124 @@
           <t>KI</t>
         </is>
       </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Module</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>KI</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>13-May-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>598</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>12-May-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -623,40 +787,80 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>13-May-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>12-May-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -665,40 +869,80 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>13-May-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>944</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>12-May-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -707,43 +951,281 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>13-May-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>12-May-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>509</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>350</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>116</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
         <is>
           <t>12</t>
         </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>13-May-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>509</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>350</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v/>
+      </c>
+      <c r="K6" t="n">
+        <v/>
+      </c>
+      <c r="L6" t="n">
+        <v/>
+      </c>
+      <c r="M6" t="n">
+        <v/>
+      </c>
+      <c r="N6" t="n">
+        <v/>
+      </c>
+      <c r="O6" t="n">
+        <v/>
+      </c>
+      <c r="P6" t="n">
+        <v/>
+      </c>
+      <c r="Q6" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>13-May-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>resident</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>1142</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>1141</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v/>
+      </c>
+      <c r="K7" t="n">
+        <v/>
+      </c>
+      <c r="L7" t="n">
+        <v/>
+      </c>
+      <c r="M7" t="n">
+        <v/>
+      </c>
+      <c r="N7" t="n">
+        <v/>
+      </c>
+      <c r="O7" t="n">
+        <v/>
+      </c>
+      <c r="P7" t="n">
+        <v/>
+      </c>
+      <c r="Q7" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>13-May-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>dsl</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>196</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v/>
+      </c>
+      <c r="K8" t="n">
+        <v/>
+      </c>
+      <c r="L8" t="n">
+        <v/>
+      </c>
+      <c r="M8" t="n">
+        <v/>
+      </c>
+      <c r="N8" t="n">
+        <v/>
+      </c>
+      <c r="O8" t="n">
+        <v/>
+      </c>
+      <c r="P8" t="n">
+        <v/>
+      </c>
+      <c r="Q8" t="n">
+        <v/>
       </c>
     </row>
   </sheetData>

--- a/minio-report-tracker/xlxs/dev01.xlsx
+++ b/minio-report-tracker/xlxs/dev01.xlsx
@@ -306,6 +306,31 @@
     </pic>
     <clientData/>
   </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>154</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="7620000" cy="3810000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
 </wsDr>
 </file>
 
@@ -598,7 +623,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q8"/>
+  <dimension ref="A1:Z9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -606,18 +631,27 @@
     <col width="6" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="5" customWidth="1" min="5" max="5"/>
-    <col width="4" customWidth="1" min="6" max="6"/>
-    <col width="4" customWidth="1" min="7" max="7"/>
-    <col width="4" customWidth="1" min="8" max="8"/>
+    <col width="5" customWidth="1" min="6" max="6"/>
+    <col width="5" customWidth="1" min="7" max="7"/>
+    <col width="5" customWidth="1" min="8" max="8"/>
     <col width="2" customWidth="1" min="9" max="9"/>
     <col width="13" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="5" customWidth="1" min="12" max="12"/>
-    <col width="5" customWidth="1" min="13" max="13"/>
+    <col width="6" customWidth="1" min="12" max="12"/>
+    <col width="6" customWidth="1" min="13" max="13"/>
     <col width="5" customWidth="1" min="14" max="14"/>
-    <col width="5" customWidth="1" min="15" max="15"/>
-    <col width="5" customWidth="1" min="16" max="16"/>
-    <col width="5" customWidth="1" min="17" max="17"/>
+    <col width="4" customWidth="1" min="15" max="15"/>
+    <col width="4" customWidth="1" min="16" max="16"/>
+    <col width="4" customWidth="1" min="17" max="17"/>
+    <col width="2" customWidth="1" min="18" max="18"/>
+    <col width="13" customWidth="1" min="19" max="19"/>
+    <col width="16" customWidth="1" min="20" max="20"/>
+    <col width="5" customWidth="1" min="21" max="21"/>
+    <col width="5" customWidth="1" min="22" max="22"/>
+    <col width="5" customWidth="1" min="23" max="23"/>
+    <col width="5" customWidth="1" min="24" max="24"/>
+    <col width="5" customWidth="1" min="25" max="25"/>
+    <col width="5" customWidth="1" min="26" max="26"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -701,84 +735,164 @@
           <t>KI</t>
         </is>
       </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Module</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>KI</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>14-May-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>597</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>13-May-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>12-May-2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -787,80 +901,120 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>14-May-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>13-May-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>masterdata-ara</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>336</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>12-May-2026</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>944</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>12-May-2026</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>masterdata-eng</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>944</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -869,80 +1023,120 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>14-May-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>944</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>13-May-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>masterdata-eng</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>944</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
         <is>
           <t>12-May-2026</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="Z4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -951,80 +1145,120 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>14-May-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>13-May-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>masterdata-fra</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>944</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
         <is>
           <t>12-May-2026</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>509</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>350</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>116</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
         <is>
           <t>12</t>
         </is>
@@ -1033,198 +1267,408 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>14-May-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>509</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>350</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>13-May-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>partner</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>509</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>350</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J6" t="n">
-        <v/>
-      </c>
-      <c r="K6" t="n">
-        <v/>
-      </c>
-      <c r="L6" t="n">
-        <v/>
-      </c>
-      <c r="M6" t="n">
-        <v/>
-      </c>
-      <c r="N6" t="n">
-        <v/>
-      </c>
-      <c r="O6" t="n">
-        <v/>
-      </c>
-      <c r="P6" t="n">
-        <v/>
-      </c>
-      <c r="Q6" t="n">
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S6" t="n">
+        <v/>
+      </c>
+      <c r="T6" t="n">
+        <v/>
+      </c>
+      <c r="U6" t="n">
+        <v/>
+      </c>
+      <c r="V6" t="n">
+        <v/>
+      </c>
+      <c r="W6" t="n">
+        <v/>
+      </c>
+      <c r="X6" t="n">
+        <v/>
+      </c>
+      <c r="Y6" t="n">
+        <v/>
+      </c>
+      <c r="Z6" t="n">
         <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>14-May-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>resident</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>1142</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>1142</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>13-May-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>resident</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>1142</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>1141</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J7" t="n">
-        <v/>
-      </c>
-      <c r="K7" t="n">
-        <v/>
-      </c>
-      <c r="L7" t="n">
-        <v/>
-      </c>
-      <c r="M7" t="n">
-        <v/>
-      </c>
-      <c r="N7" t="n">
-        <v/>
-      </c>
-      <c r="O7" t="n">
-        <v/>
-      </c>
-      <c r="P7" t="n">
-        <v/>
-      </c>
-      <c r="Q7" t="n">
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>509</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>350</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="S7" t="n">
+        <v/>
+      </c>
+      <c r="T7" t="n">
+        <v/>
+      </c>
+      <c r="U7" t="n">
+        <v/>
+      </c>
+      <c r="V7" t="n">
+        <v/>
+      </c>
+      <c r="W7" t="n">
+        <v/>
+      </c>
+      <c r="X7" t="n">
+        <v/>
+      </c>
+      <c r="Y7" t="n">
+        <v/>
+      </c>
+      <c r="Z7" t="n">
         <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>14-May-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>dsl</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>201</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>13-May-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>resident</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>1142</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>1141</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S8" t="n">
+        <v/>
+      </c>
+      <c r="T8" t="n">
+        <v/>
+      </c>
+      <c r="U8" t="n">
+        <v/>
+      </c>
+      <c r="V8" t="n">
+        <v/>
+      </c>
+      <c r="W8" t="n">
+        <v/>
+      </c>
+      <c r="X8" t="n">
+        <v/>
+      </c>
+      <c r="Y8" t="n">
+        <v/>
+      </c>
+      <c r="Z8" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v/>
+      </c>
+      <c r="B9" t="n">
+        <v/>
+      </c>
+      <c r="C9" t="n">
+        <v/>
+      </c>
+      <c r="D9" t="n">
+        <v/>
+      </c>
+      <c r="E9" t="n">
+        <v/>
+      </c>
+      <c r="F9" t="n">
+        <v/>
+      </c>
+      <c r="G9" t="n">
+        <v/>
+      </c>
+      <c r="H9" t="n">
+        <v/>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>13-May-2026</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>196</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J8" t="n">
-        <v/>
-      </c>
-      <c r="K8" t="n">
-        <v/>
-      </c>
-      <c r="L8" t="n">
-        <v/>
-      </c>
-      <c r="M8" t="n">
-        <v/>
-      </c>
-      <c r="N8" t="n">
-        <v/>
-      </c>
-      <c r="O8" t="n">
-        <v/>
-      </c>
-      <c r="P8" t="n">
-        <v/>
-      </c>
-      <c r="Q8" t="n">
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S9" t="n">
+        <v/>
+      </c>
+      <c r="T9" t="n">
+        <v/>
+      </c>
+      <c r="U9" t="n">
+        <v/>
+      </c>
+      <c r="V9" t="n">
+        <v/>
+      </c>
+      <c r="W9" t="n">
+        <v/>
+      </c>
+      <c r="X9" t="n">
+        <v/>
+      </c>
+      <c r="Y9" t="n">
+        <v/>
+      </c>
+      <c r="Z9" t="n">
         <v/>
       </c>
     </row>

--- a/minio-report-tracker/xlxs/dev01.xlsx
+++ b/minio-report-tracker/xlxs/dev01.xlsx
@@ -331,6 +331,31 @@
     </pic>
     <clientData/>
   </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>176</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="7620000" cy="3810000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="9" name="Image 9" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
 </wsDr>
 </file>
 
@@ -623,7 +648,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z9"/>
+  <dimension ref="A1:AI10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -631,9 +656,9 @@
     <col width="6" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="5" customWidth="1" min="5" max="5"/>
-    <col width="5" customWidth="1" min="6" max="6"/>
-    <col width="5" customWidth="1" min="7" max="7"/>
-    <col width="5" customWidth="1" min="8" max="8"/>
+    <col width="4" customWidth="1" min="6" max="6"/>
+    <col width="4" customWidth="1" min="7" max="7"/>
+    <col width="4" customWidth="1" min="8" max="8"/>
     <col width="2" customWidth="1" min="9" max="9"/>
     <col width="13" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
@@ -646,12 +671,21 @@
     <col width="2" customWidth="1" min="18" max="18"/>
     <col width="13" customWidth="1" min="19" max="19"/>
     <col width="16" customWidth="1" min="20" max="20"/>
-    <col width="5" customWidth="1" min="21" max="21"/>
-    <col width="5" customWidth="1" min="22" max="22"/>
+    <col width="6" customWidth="1" min="21" max="21"/>
+    <col width="6" customWidth="1" min="22" max="22"/>
     <col width="5" customWidth="1" min="23" max="23"/>
     <col width="5" customWidth="1" min="24" max="24"/>
     <col width="5" customWidth="1" min="25" max="25"/>
     <col width="5" customWidth="1" min="26" max="26"/>
+    <col width="2" customWidth="1" min="27" max="27"/>
+    <col width="13" customWidth="1" min="28" max="28"/>
+    <col width="16" customWidth="1" min="29" max="29"/>
+    <col width="5" customWidth="1" min="30" max="30"/>
+    <col width="5" customWidth="1" min="31" max="31"/>
+    <col width="5" customWidth="1" min="32" max="32"/>
+    <col width="5" customWidth="1" min="33" max="33"/>
+    <col width="5" customWidth="1" min="34" max="34"/>
+    <col width="5" customWidth="1" min="35" max="35"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -775,124 +809,204 @@
           <t>KI</t>
         </is>
       </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>Module</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>KI</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>15-May-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>592</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>14-May-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>597</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>13-May-2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>12-May-2026</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="AH2" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AI2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -901,120 +1015,160 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>15-May-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>336</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>14-May-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>masterdata-ara</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>336</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>13-May-2026</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>336</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>12-May-2026</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>944</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>13-May-2026</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>idrepo</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>414</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>336</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>12-May-2026</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>masterdata-eng</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>944</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1023,120 +1177,160 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>15-May-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>14-May-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>masterdata-eng</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>944</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
         <is>
           <t>13-May-2026</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
         <is>
           <t>12-May-2026</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="AE4" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
+      <c r="AH4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="AI4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1145,120 +1339,160 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>15-May-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>944</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>14-May-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>masterdata-fra</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>944</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
         <is>
           <t>13-May-2026</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
         <is>
           <t>12-May-2026</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>509</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="AE5" t="inlineStr">
         <is>
           <t>350</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="AF5" t="inlineStr">
         <is>
           <t>116</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="AG5" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
         <is>
           <t>12</t>
         </is>
@@ -1267,408 +1501,714 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>15-May-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>14-May-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>partner</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>509</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>350</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
         <is>
           <t>13-May-2026</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S6" t="n">
-        <v/>
-      </c>
-      <c r="T6" t="n">
-        <v/>
-      </c>
-      <c r="U6" t="n">
-        <v/>
-      </c>
-      <c r="V6" t="n">
-        <v/>
-      </c>
-      <c r="W6" t="n">
-        <v/>
-      </c>
-      <c r="X6" t="n">
-        <v/>
-      </c>
-      <c r="Y6" t="n">
-        <v/>
-      </c>
-      <c r="Z6" t="n">
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB6" t="n">
+        <v/>
+      </c>
+      <c r="AC6" t="n">
+        <v/>
+      </c>
+      <c r="AD6" t="n">
+        <v/>
+      </c>
+      <c r="AE6" t="n">
+        <v/>
+      </c>
+      <c r="AF6" t="n">
+        <v/>
+      </c>
+      <c r="AG6" t="n">
+        <v/>
+      </c>
+      <c r="AH6" t="n">
+        <v/>
+      </c>
+      <c r="AI6" t="n">
         <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>15-May-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>509</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>350</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>14-May-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>resident</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>1142</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>1142</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>509</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>350</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
         <is>
           <t>13-May-2026</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>509</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>350</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>116</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="S7" t="n">
-        <v/>
-      </c>
-      <c r="T7" t="n">
-        <v/>
-      </c>
-      <c r="U7" t="n">
-        <v/>
-      </c>
-      <c r="V7" t="n">
-        <v/>
-      </c>
-      <c r="W7" t="n">
-        <v/>
-      </c>
-      <c r="X7" t="n">
-        <v/>
-      </c>
-      <c r="Y7" t="n">
-        <v/>
-      </c>
-      <c r="Z7" t="n">
+      <c r="AB7" t="n">
+        <v/>
+      </c>
+      <c r="AC7" t="n">
+        <v/>
+      </c>
+      <c r="AD7" t="n">
+        <v/>
+      </c>
+      <c r="AE7" t="n">
+        <v/>
+      </c>
+      <c r="AF7" t="n">
+        <v/>
+      </c>
+      <c r="AG7" t="n">
+        <v/>
+      </c>
+      <c r="AH7" t="n">
+        <v/>
+      </c>
+      <c r="AI7" t="n">
         <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>15-May-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>14-May-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>dsl</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>230</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>201</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
         <is>
           <t>13-May-2026</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>1141</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S8" t="n">
-        <v/>
-      </c>
-      <c r="T8" t="n">
-        <v/>
-      </c>
-      <c r="U8" t="n">
-        <v/>
-      </c>
-      <c r="V8" t="n">
-        <v/>
-      </c>
-      <c r="W8" t="n">
-        <v/>
-      </c>
-      <c r="X8" t="n">
-        <v/>
-      </c>
-      <c r="Y8" t="n">
-        <v/>
-      </c>
-      <c r="Z8" t="n">
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB8" t="n">
+        <v/>
+      </c>
+      <c r="AC8" t="n">
+        <v/>
+      </c>
+      <c r="AD8" t="n">
+        <v/>
+      </c>
+      <c r="AE8" t="n">
+        <v/>
+      </c>
+      <c r="AF8" t="n">
+        <v/>
+      </c>
+      <c r="AG8" t="n">
+        <v/>
+      </c>
+      <c r="AH8" t="n">
+        <v/>
+      </c>
+      <c r="AI8" t="n">
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="n">
-        <v/>
-      </c>
-      <c r="B9" t="n">
-        <v/>
-      </c>
-      <c r="C9" t="n">
-        <v/>
-      </c>
-      <c r="D9" t="n">
-        <v/>
-      </c>
-      <c r="E9" t="n">
-        <v/>
-      </c>
-      <c r="F9" t="n">
-        <v/>
-      </c>
-      <c r="G9" t="n">
-        <v/>
-      </c>
-      <c r="H9" t="n">
-        <v/>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>15-May-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>resident</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1142</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>1138</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
+          <t>14-May-2026</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>resident</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>1142</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>1142</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
           <t>13-May-2026</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>196</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S9" t="n">
-        <v/>
-      </c>
-      <c r="T9" t="n">
-        <v/>
-      </c>
-      <c r="U9" t="n">
-        <v/>
-      </c>
-      <c r="V9" t="n">
-        <v/>
-      </c>
-      <c r="W9" t="n">
-        <v/>
-      </c>
-      <c r="X9" t="n">
-        <v/>
-      </c>
-      <c r="Y9" t="n">
-        <v/>
-      </c>
-      <c r="Z9" t="n">
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB9" t="n">
+        <v/>
+      </c>
+      <c r="AC9" t="n">
+        <v/>
+      </c>
+      <c r="AD9" t="n">
+        <v/>
+      </c>
+      <c r="AE9" t="n">
+        <v/>
+      </c>
+      <c r="AF9" t="n">
+        <v/>
+      </c>
+      <c r="AG9" t="n">
+        <v/>
+      </c>
+      <c r="AH9" t="n">
+        <v/>
+      </c>
+      <c r="AI9" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>15-May-2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>dsl</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>201</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>14-May-2026</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>dsl</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>201</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S10" t="n">
+        <v/>
+      </c>
+      <c r="T10" t="n">
+        <v/>
+      </c>
+      <c r="U10" t="n">
+        <v/>
+      </c>
+      <c r="V10" t="n">
+        <v/>
+      </c>
+      <c r="W10" t="n">
+        <v/>
+      </c>
+      <c r="X10" t="n">
+        <v/>
+      </c>
+      <c r="Y10" t="n">
+        <v/>
+      </c>
+      <c r="Z10" t="n">
+        <v/>
+      </c>
+      <c r="AB10" t="n">
+        <v/>
+      </c>
+      <c r="AC10" t="n">
+        <v/>
+      </c>
+      <c r="AD10" t="n">
+        <v/>
+      </c>
+      <c r="AE10" t="n">
+        <v/>
+      </c>
+      <c r="AF10" t="n">
+        <v/>
+      </c>
+      <c r="AG10" t="n">
+        <v/>
+      </c>
+      <c r="AH10" t="n">
+        <v/>
+      </c>
+      <c r="AI10" t="n">
         <v/>
       </c>
     </row>

--- a/minio-report-tracker/xlxs/dev01.xlsx
+++ b/minio-report-tracker/xlxs/dev01.xlsx
@@ -648,7 +648,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI10"/>
+  <dimension ref="A1:Z10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -670,22 +670,13 @@
     <col width="4" customWidth="1" min="17" max="17"/>
     <col width="2" customWidth="1" min="18" max="18"/>
     <col width="13" customWidth="1" min="19" max="19"/>
-    <col width="16" customWidth="1" min="20" max="20"/>
-    <col width="6" customWidth="1" min="21" max="21"/>
-    <col width="6" customWidth="1" min="22" max="22"/>
+    <col width="8" customWidth="1" min="20" max="20"/>
+    <col width="5" customWidth="1" min="21" max="21"/>
+    <col width="5" customWidth="1" min="22" max="22"/>
     <col width="5" customWidth="1" min="23" max="23"/>
     <col width="5" customWidth="1" min="24" max="24"/>
     <col width="5" customWidth="1" min="25" max="25"/>
     <col width="5" customWidth="1" min="26" max="26"/>
-    <col width="2" customWidth="1" min="27" max="27"/>
-    <col width="13" customWidth="1" min="28" max="28"/>
-    <col width="16" customWidth="1" min="29" max="29"/>
-    <col width="5" customWidth="1" min="30" max="30"/>
-    <col width="5" customWidth="1" min="31" max="31"/>
-    <col width="5" customWidth="1" min="32" max="32"/>
-    <col width="5" customWidth="1" min="33" max="33"/>
-    <col width="5" customWidth="1" min="34" max="34"/>
-    <col width="5" customWidth="1" min="35" max="35"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -809,146 +800,106 @@
           <t>KI</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>Module</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
-          <t>KI</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>18-May-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>598</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>15-May-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>592</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>14-May-2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>auth</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>612</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>597</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>13-May-2026</t>
-        </is>
-      </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>auth</t>
+          <t>idrepo</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>612</t>
+          <t>414</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>598</t>
+          <t>336</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
@@ -963,50 +914,10 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>78</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>12-May-2026</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>masterdata-ara</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1015,102 +926,102 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>18-May-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>336</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>15-May-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>14-May-2026</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>idrepo</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>414</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>336</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>13-May-2026</t>
-        </is>
-      </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>idrepo</t>
+          <t>prereg</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>414</t>
+          <t>288</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>336</t>
+          <t>282</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -1125,288 +1036,192 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>12-May-2026</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>masterdata-eng</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>944</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>18-May-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>15-May-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>14-May-2026</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>masterdata-ara</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="Q4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>13-May-2026</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>masterdata-ara</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>12-May-2026</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>masterdata-fra</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="S4" t="n">
+        <v/>
+      </c>
+      <c r="T4" t="n">
+        <v/>
+      </c>
+      <c r="U4" t="n">
+        <v/>
+      </c>
+      <c r="V4" t="n">
+        <v/>
+      </c>
+      <c r="W4" t="n">
+        <v/>
+      </c>
+      <c r="X4" t="n">
+        <v/>
+      </c>
+      <c r="Y4" t="n">
+        <v/>
+      </c>
+      <c r="Z4" t="n">
+        <v/>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>18-May-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>944</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>15-May-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>14-May-2026</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>masterdata-eng</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>944</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>0</t>
@@ -1417,596 +1232,420 @@
           <t>0</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>13-May-2026</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>masterdata-eng</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>944</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>12-May-2026</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>partner</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>509</t>
-        </is>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>350</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
+      <c r="S5" t="n">
+        <v/>
+      </c>
+      <c r="T5" t="n">
+        <v/>
+      </c>
+      <c r="U5" t="n">
+        <v/>
+      </c>
+      <c r="V5" t="n">
+        <v/>
+      </c>
+      <c r="W5" t="n">
+        <v/>
+      </c>
+      <c r="X5" t="n">
+        <v/>
+      </c>
+      <c r="Y5" t="n">
+        <v/>
+      </c>
+      <c r="Z5" t="n">
+        <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>18-May-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>15-May-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>14-May-2026</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>masterdata-fra</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="Q6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>13-May-2026</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>masterdata-fra</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB6" t="n">
-        <v/>
-      </c>
-      <c r="AC6" t="n">
-        <v/>
-      </c>
-      <c r="AD6" t="n">
-        <v/>
-      </c>
-      <c r="AE6" t="n">
-        <v/>
-      </c>
-      <c r="AF6" t="n">
-        <v/>
-      </c>
-      <c r="AG6" t="n">
-        <v/>
-      </c>
-      <c r="AH6" t="n">
-        <v/>
-      </c>
-      <c r="AI6" t="n">
+      <c r="S6" t="n">
+        <v/>
+      </c>
+      <c r="T6" t="n">
+        <v/>
+      </c>
+      <c r="U6" t="n">
+        <v/>
+      </c>
+      <c r="V6" t="n">
+        <v/>
+      </c>
+      <c r="W6" t="n">
+        <v/>
+      </c>
+      <c r="X6" t="n">
+        <v/>
+      </c>
+      <c r="Y6" t="n">
+        <v/>
+      </c>
+      <c r="Z6" t="n">
         <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>18-May-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>509</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>350</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>15-May-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>509</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>350</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>116</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>14-May-2026</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>partner</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>509</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>350</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>13-May-2026</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>partner</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>509</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>350</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AB7" t="n">
-        <v/>
-      </c>
-      <c r="AC7" t="n">
-        <v/>
-      </c>
-      <c r="AD7" t="n">
-        <v/>
-      </c>
-      <c r="AE7" t="n">
-        <v/>
-      </c>
-      <c r="AF7" t="n">
-        <v/>
-      </c>
-      <c r="AG7" t="n">
-        <v/>
-      </c>
-      <c r="AH7" t="n">
-        <v/>
-      </c>
-      <c r="AI7" t="n">
+      <c r="S7" t="n">
+        <v/>
+      </c>
+      <c r="T7" t="n">
+        <v/>
+      </c>
+      <c r="U7" t="n">
+        <v/>
+      </c>
+      <c r="V7" t="n">
+        <v/>
+      </c>
+      <c r="W7" t="n">
+        <v/>
+      </c>
+      <c r="X7" t="n">
+        <v/>
+      </c>
+      <c r="Y7" t="n">
+        <v/>
+      </c>
+      <c r="Z7" t="n">
         <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>18-May-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>15-May-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>14-May-2026</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>288</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>282</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>13-May-2026</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>resident</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>1142</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>1141</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB8" t="n">
-        <v/>
-      </c>
-      <c r="AC8" t="n">
-        <v/>
-      </c>
-      <c r="AD8" t="n">
-        <v/>
-      </c>
-      <c r="AE8" t="n">
-        <v/>
-      </c>
-      <c r="AF8" t="n">
-        <v/>
-      </c>
-      <c r="AG8" t="n">
-        <v/>
-      </c>
-      <c r="AH8" t="n">
-        <v/>
-      </c>
-      <c r="AI8" t="n">
+      <c r="S8" t="n">
+        <v/>
+      </c>
+      <c r="T8" t="n">
+        <v/>
+      </c>
+      <c r="U8" t="n">
+        <v/>
+      </c>
+      <c r="V8" t="n">
+        <v/>
+      </c>
+      <c r="W8" t="n">
+        <v/>
+      </c>
+      <c r="X8" t="n">
+        <v/>
+      </c>
+      <c r="Y8" t="n">
+        <v/>
+      </c>
+      <c r="Z8" t="n">
         <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>18-May-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>resident</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1142</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>1139</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>15-May-2026</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>1138</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>14-May-2026</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>resident</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>1142</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>1142</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>0</t>
@@ -2017,132 +1656,92 @@
           <t>0</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>13-May-2026</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>dsl</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>230</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>196</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB9" t="n">
-        <v/>
-      </c>
-      <c r="AC9" t="n">
-        <v/>
-      </c>
-      <c r="AD9" t="n">
-        <v/>
-      </c>
-      <c r="AE9" t="n">
-        <v/>
-      </c>
-      <c r="AF9" t="n">
-        <v/>
-      </c>
-      <c r="AG9" t="n">
-        <v/>
-      </c>
-      <c r="AH9" t="n">
-        <v/>
-      </c>
-      <c r="AI9" t="n">
+      <c r="S9" t="n">
+        <v/>
+      </c>
+      <c r="T9" t="n">
+        <v/>
+      </c>
+      <c r="U9" t="n">
+        <v/>
+      </c>
+      <c r="V9" t="n">
+        <v/>
+      </c>
+      <c r="W9" t="n">
+        <v/>
+      </c>
+      <c r="X9" t="n">
+        <v/>
+      </c>
+      <c r="Y9" t="n">
+        <v/>
+      </c>
+      <c r="Z9" t="n">
         <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>18-May-2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>dsl</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>15-May-2026</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>201</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>14-May-2026</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>dsl</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>230</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>201</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr">
         <is>
           <t>0</t>
@@ -2185,30 +1784,6 @@
         <v/>
       </c>
       <c r="Z10" t="n">
-        <v/>
-      </c>
-      <c r="AB10" t="n">
-        <v/>
-      </c>
-      <c r="AC10" t="n">
-        <v/>
-      </c>
-      <c r="AD10" t="n">
-        <v/>
-      </c>
-      <c r="AE10" t="n">
-        <v/>
-      </c>
-      <c r="AF10" t="n">
-        <v/>
-      </c>
-      <c r="AG10" t="n">
-        <v/>
-      </c>
-      <c r="AH10" t="n">
-        <v/>
-      </c>
-      <c r="AI10" t="n">
         <v/>
       </c>
     </row>

--- a/minio-report-tracker/xlxs/dev01.xlsx
+++ b/minio-report-tracker/xlxs/dev01.xlsx
@@ -670,9 +670,9 @@
     <col width="4" customWidth="1" min="17" max="17"/>
     <col width="2" customWidth="1" min="18" max="18"/>
     <col width="13" customWidth="1" min="19" max="19"/>
-    <col width="8" customWidth="1" min="20" max="20"/>
-    <col width="5" customWidth="1" min="21" max="21"/>
-    <col width="5" customWidth="1" min="22" max="22"/>
+    <col width="10" customWidth="1" min="20" max="20"/>
+    <col width="6" customWidth="1" min="21" max="21"/>
+    <col width="6" customWidth="1" min="22" max="22"/>
     <col width="5" customWidth="1" min="23" max="23"/>
     <col width="5" customWidth="1" min="24" max="24"/>
     <col width="5" customWidth="1" min="25" max="25"/>
@@ -804,224 +804,224 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>19-May-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>597</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>18-May-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>15-May-2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>592</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>597</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>9</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>14-May-2026</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>idrepo</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>414</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>336</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>19-May-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>336</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>18-May-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>15-May-2026</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>idrepo</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>414</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>336</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>14-May-2026</t>
-        </is>
-      </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>prereg</t>
+          <t>resident</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>1142</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>282</t>
+          <t>1142</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -1036,59 +1036,59 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>19-May-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>18-May-2026</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>masterdata-ara</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>15-May-2026</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1154,47 +1154,47 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>19-May-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>944</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>18-May-2026</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>masterdata-eng</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>944</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>15-May-2026</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1260,47 +1260,47 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>19-May-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>18-May-2026</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>masterdata-fra</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>15-May-2026</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1366,47 +1366,47 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>19-May-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>509</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>350</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>18-May-2026</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>partner</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>509</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>350</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>15-May-2026</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1472,47 +1472,47 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>19-May-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>18-May-2026</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>288</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>282</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>15-May-2026</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1578,72 +1578,72 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>19-May-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>resident</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1142</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>1139</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>18-May-2026</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>1139</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
         <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>15-May-2026</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>resident</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>1142</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>1138</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1684,72 +1684,72 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>19-May-2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>dsl</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>18-May-2026</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>15-May-2026</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>dsl</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>230</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>201</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">

--- a/minio-report-tracker/xlxs/dev01.xlsx
+++ b/minio-report-tracker/xlxs/dev01.xlsx
@@ -670,13 +670,13 @@
     <col width="4" customWidth="1" min="17" max="17"/>
     <col width="2" customWidth="1" min="18" max="18"/>
     <col width="13" customWidth="1" min="19" max="19"/>
-    <col width="10" customWidth="1" min="20" max="20"/>
+    <col width="16" customWidth="1" min="20" max="20"/>
     <col width="6" customWidth="1" min="21" max="21"/>
     <col width="6" customWidth="1" min="22" max="22"/>
     <col width="5" customWidth="1" min="23" max="23"/>
-    <col width="5" customWidth="1" min="24" max="24"/>
-    <col width="5" customWidth="1" min="25" max="25"/>
-    <col width="5" customWidth="1" min="26" max="26"/>
+    <col width="4" customWidth="1" min="24" max="24"/>
+    <col width="4" customWidth="1" min="25" max="25"/>
+    <col width="4" customWidth="1" min="26" max="26"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -804,104 +804,104 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>20-May-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>591</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>19-May-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>597</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>18-May-2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>15-May-2026</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>auth</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>612</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>597</t>
-        </is>
-      </c>
       <c r="W2" t="inlineStr">
         <is>
           <t>0</t>
@@ -909,7 +909,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -926,117 +926,117 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>20-May-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>336</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>19-May-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>18-May-2026</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
         <is>
           <t>78</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>15-May-2026</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>resident</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>1142</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>1142</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -1048,743 +1048,855 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>20-May-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>928</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>19-May-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
         <is>
           <t>18-May-2026</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" t="n">
-        <v/>
-      </c>
-      <c r="T4" t="n">
-        <v/>
-      </c>
-      <c r="U4" t="n">
-        <v/>
-      </c>
-      <c r="V4" t="n">
-        <v/>
-      </c>
-      <c r="W4" t="n">
-        <v/>
-      </c>
-      <c r="X4" t="n">
-        <v/>
-      </c>
-      <c r="Y4" t="n">
-        <v/>
-      </c>
-      <c r="Z4" t="n">
-        <v/>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>20-May-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>944</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>19-May-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
         <is>
           <t>18-May-2026</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S5" t="n">
-        <v/>
-      </c>
-      <c r="T5" t="n">
-        <v/>
-      </c>
-      <c r="U5" t="n">
-        <v/>
-      </c>
-      <c r="V5" t="n">
-        <v/>
-      </c>
-      <c r="W5" t="n">
-        <v/>
-      </c>
-      <c r="X5" t="n">
-        <v/>
-      </c>
-      <c r="Y5" t="n">
-        <v/>
-      </c>
-      <c r="Z5" t="n">
-        <v/>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>20-May-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>19-May-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
         <is>
           <t>18-May-2026</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S6" t="n">
-        <v/>
-      </c>
-      <c r="T6" t="n">
-        <v/>
-      </c>
-      <c r="U6" t="n">
-        <v/>
-      </c>
-      <c r="V6" t="n">
-        <v/>
-      </c>
-      <c r="W6" t="n">
-        <v/>
-      </c>
-      <c r="X6" t="n">
-        <v/>
-      </c>
-      <c r="Y6" t="n">
-        <v/>
-      </c>
-      <c r="Z6" t="n">
-        <v/>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>20-May-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>509</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>350</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>19-May-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>509</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>350</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>116</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>18-May-2026</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>509</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>350</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>116</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
-      </c>
-      <c r="S7" t="n">
-        <v/>
-      </c>
-      <c r="T7" t="n">
-        <v/>
-      </c>
-      <c r="U7" t="n">
-        <v/>
-      </c>
-      <c r="V7" t="n">
-        <v/>
-      </c>
-      <c r="W7" t="n">
-        <v/>
-      </c>
-      <c r="X7" t="n">
-        <v/>
-      </c>
-      <c r="Y7" t="n">
-        <v/>
-      </c>
-      <c r="Z7" t="n">
-        <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>20-May-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>19-May-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>18-May-2026</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
-      </c>
-      <c r="S8" t="n">
-        <v/>
-      </c>
-      <c r="T8" t="n">
-        <v/>
-      </c>
-      <c r="U8" t="n">
-        <v/>
-      </c>
-      <c r="V8" t="n">
-        <v/>
-      </c>
-      <c r="W8" t="n">
-        <v/>
-      </c>
-      <c r="X8" t="n">
-        <v/>
-      </c>
-      <c r="Y8" t="n">
-        <v/>
-      </c>
-      <c r="Z8" t="n">
-        <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>20-May-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>resident</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1142</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>1142</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>19-May-2026</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>1139</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
         <is>
           <t>18-May-2026</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>1139</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S9" t="n">
-        <v/>
-      </c>
-      <c r="T9" t="n">
-        <v/>
-      </c>
-      <c r="U9" t="n">
-        <v/>
-      </c>
-      <c r="V9" t="n">
-        <v/>
-      </c>
-      <c r="W9" t="n">
-        <v/>
-      </c>
-      <c r="X9" t="n">
-        <v/>
-      </c>
-      <c r="Y9" t="n">
-        <v/>
-      </c>
-      <c r="Z9" t="n">
-        <v/>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>20-May-2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>dsl</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>201</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>19-May-2026</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
         <is>
           <t>18-May-2026</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S10" t="n">
-        <v/>
-      </c>
-      <c r="T10" t="n">
-        <v/>
-      </c>
-      <c r="U10" t="n">
-        <v/>
-      </c>
-      <c r="V10" t="n">
-        <v/>
-      </c>
-      <c r="W10" t="n">
-        <v/>
-      </c>
-      <c r="X10" t="n">
-        <v/>
-      </c>
-      <c r="Y10" t="n">
-        <v/>
-      </c>
-      <c r="Z10" t="n">
-        <v/>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/minio-report-tracker/xlxs/dev01.xlsx
+++ b/minio-report-tracker/xlxs/dev01.xlsx
@@ -648,7 +648,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z10"/>
+  <dimension ref="A1:AI10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -677,6 +677,15 @@
     <col width="4" customWidth="1" min="24" max="24"/>
     <col width="4" customWidth="1" min="25" max="25"/>
     <col width="4" customWidth="1" min="26" max="26"/>
+    <col width="2" customWidth="1" min="27" max="27"/>
+    <col width="13" customWidth="1" min="28" max="28"/>
+    <col width="16" customWidth="1" min="29" max="29"/>
+    <col width="6" customWidth="1" min="30" max="30"/>
+    <col width="6" customWidth="1" min="31" max="31"/>
+    <col width="5" customWidth="1" min="32" max="32"/>
+    <col width="4" customWidth="1" min="33" max="33"/>
+    <col width="4" customWidth="1" min="34" max="34"/>
+    <col width="4" customWidth="1" min="35" max="35"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -800,124 +809,204 @@
           <t>KI</t>
         </is>
       </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>Module</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>KI</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>21-May-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>598</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>20-May-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>591</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>19-May-2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>597</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>18-May-2026</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AI2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
@@ -926,120 +1015,160 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>21-May-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>336</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>20-May-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>19-May-2026</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
         <is>
           <t>18-May-2026</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="AI3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1048,120 +1177,160 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>21-May-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>20-May-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>928</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
         <is>
           <t>19-May-2026</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
         <is>
           <t>18-May-2026</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="AE4" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
+      <c r="AH4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="AI4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1170,120 +1339,160 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>21-May-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>944</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>20-May-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
         <is>
           <t>19-May-2026</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
         <is>
           <t>18-May-2026</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="AE5" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1292,120 +1501,160 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>21-May-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>20-May-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
         <is>
           <t>19-May-2026</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
         <is>
           <t>18-May-2026</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="AE6" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
+      <c r="AH6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
+      <c r="AI6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1414,120 +1663,160 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>21-May-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>509</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>350</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>20-May-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>509</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>350</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>116</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>19-May-2026</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>509</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>350</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>116</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>18-May-2026</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>509</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="AE7" t="inlineStr">
         <is>
           <t>350</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="AF7" t="inlineStr">
         <is>
           <t>116</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="AG7" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
@@ -1536,120 +1825,160 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>21-May-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>20-May-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>19-May-2026</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>18-May-2026</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="AD8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="AE8" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="AI8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -1658,120 +1987,160 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>21-May-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>resident</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1142</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>1141</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>20-May-2026</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
         <is>
           <t>19-May-2026</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>1139</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
         <is>
           <t>18-May-2026</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="AC9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="AD9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="AE9" t="inlineStr">
         <is>
           <t>1139</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1780,120 +2149,160 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>21-May-2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>dsl</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>20-May-2026</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>201</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
         <is>
           <t>19-May-2026</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
         <is>
           <t>18-May-2026</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="AC10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="AD10" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="AE10" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
         <is>
           <t>0</t>
         </is>

--- a/minio-report-tracker/xlxs/dev01.xlsx
+++ b/minio-report-tracker/xlxs/dev01.xlsx
@@ -648,17 +648,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI10"/>
+  <dimension ref="A1:AR10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="6" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="5" customWidth="1" min="3" max="3"/>
+    <col width="5" customWidth="1" min="4" max="4"/>
     <col width="5" customWidth="1" min="5" max="5"/>
-    <col width="4" customWidth="1" min="6" max="6"/>
-    <col width="4" customWidth="1" min="7" max="7"/>
-    <col width="4" customWidth="1" min="8" max="8"/>
+    <col width="5" customWidth="1" min="6" max="6"/>
+    <col width="5" customWidth="1" min="7" max="7"/>
+    <col width="5" customWidth="1" min="8" max="8"/>
     <col width="2" customWidth="1" min="9" max="9"/>
     <col width="13" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
@@ -686,6 +686,15 @@
     <col width="4" customWidth="1" min="33" max="33"/>
     <col width="4" customWidth="1" min="34" max="34"/>
     <col width="4" customWidth="1" min="35" max="35"/>
+    <col width="2" customWidth="1" min="36" max="36"/>
+    <col width="13" customWidth="1" min="37" max="37"/>
+    <col width="10" customWidth="1" min="38" max="38"/>
+    <col width="6" customWidth="1" min="39" max="39"/>
+    <col width="6" customWidth="1" min="40" max="40"/>
+    <col width="5" customWidth="1" min="41" max="41"/>
+    <col width="5" customWidth="1" min="42" max="42"/>
+    <col width="5" customWidth="1" min="43" max="43"/>
+    <col width="5" customWidth="1" min="44" max="44"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -849,644 +858,724 @@
           <t>KI</t>
         </is>
       </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>Module</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>KI</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>22-May-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>dsl</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>21-May-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>20-May-2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>591</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>19-May-2026</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>597</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="AH2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AI2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AK2" t="inlineStr">
         <is>
           <t>18-May-2026</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>auth</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>612</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>598</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>9</t>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>resident</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>1142</t>
+        </is>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>1142</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" t="n">
+        <v/>
+      </c>
+      <c r="B3" t="n">
+        <v/>
+      </c>
+      <c r="C3" t="n">
+        <v/>
+      </c>
+      <c r="D3" t="n">
+        <v/>
+      </c>
+      <c r="E3" t="n">
+        <v/>
+      </c>
+      <c r="F3" t="n">
+        <v/>
+      </c>
+      <c r="G3" t="n">
+        <v/>
+      </c>
+      <c r="H3" t="n">
+        <v/>
+      </c>
+      <c r="J3" t="inlineStr">
         <is>
           <t>21-May-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>20-May-2026</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
         <is>
           <t>19-May-2026</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>18-May-2026</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>idrepo</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>414</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>336</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
       <c r="AI3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
+      </c>
+      <c r="AK3" t="n">
+        <v/>
+      </c>
+      <c r="AL3" t="n">
+        <v/>
+      </c>
+      <c r="AM3" t="n">
+        <v/>
+      </c>
+      <c r="AN3" t="n">
+        <v/>
+      </c>
+      <c r="AO3" t="n">
+        <v/>
+      </c>
+      <c r="AP3" t="n">
+        <v/>
+      </c>
+      <c r="AQ3" t="n">
+        <v/>
+      </c>
+      <c r="AR3" t="n">
+        <v/>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" t="n">
+        <v/>
+      </c>
+      <c r="B4" t="n">
+        <v/>
+      </c>
+      <c r="C4" t="n">
+        <v/>
+      </c>
+      <c r="D4" t="n">
+        <v/>
+      </c>
+      <c r="E4" t="n">
+        <v/>
+      </c>
+      <c r="F4" t="n">
+        <v/>
+      </c>
+      <c r="G4" t="n">
+        <v/>
+      </c>
+      <c r="H4" t="n">
+        <v/>
+      </c>
+      <c r="J4" t="inlineStr">
         <is>
           <t>21-May-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
         <is>
           <t>20-May-2026</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>928</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
         <is>
           <t>19-May-2026</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="AE4" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
+      <c r="AH4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>18-May-2026</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>masterdata-ara</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="AI4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
+      </c>
+      <c r="AK4" t="n">
+        <v/>
+      </c>
+      <c r="AL4" t="n">
+        <v/>
+      </c>
+      <c r="AM4" t="n">
+        <v/>
+      </c>
+      <c r="AN4" t="n">
+        <v/>
+      </c>
+      <c r="AO4" t="n">
+        <v/>
+      </c>
+      <c r="AP4" t="n">
+        <v/>
+      </c>
+      <c r="AQ4" t="n">
+        <v/>
+      </c>
+      <c r="AR4" t="n">
+        <v/>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" t="n">
+        <v/>
+      </c>
+      <c r="B5" t="n">
+        <v/>
+      </c>
+      <c r="C5" t="n">
+        <v/>
+      </c>
+      <c r="D5" t="n">
+        <v/>
+      </c>
+      <c r="E5" t="n">
+        <v/>
+      </c>
+      <c r="F5" t="n">
+        <v/>
+      </c>
+      <c r="G5" t="n">
+        <v/>
+      </c>
+      <c r="H5" t="n">
+        <v/>
+      </c>
+      <c r="J5" t="inlineStr">
         <is>
           <t>21-May-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
         <is>
           <t>20-May-2026</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
         <is>
           <t>19-May-2026</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="AE5" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>18-May-2026</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>masterdata-eng</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>944</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AH5" t="inlineStr">
         <is>
           <t>0</t>
@@ -1496,645 +1585,677 @@
         <is>
           <t>0</t>
         </is>
+      </c>
+      <c r="AK5" t="n">
+        <v/>
+      </c>
+      <c r="AL5" t="n">
+        <v/>
+      </c>
+      <c r="AM5" t="n">
+        <v/>
+      </c>
+      <c r="AN5" t="n">
+        <v/>
+      </c>
+      <c r="AO5" t="n">
+        <v/>
+      </c>
+      <c r="AP5" t="n">
+        <v/>
+      </c>
+      <c r="AQ5" t="n">
+        <v/>
+      </c>
+      <c r="AR5" t="n">
+        <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" t="n">
+        <v/>
+      </c>
+      <c r="B6" t="n">
+        <v/>
+      </c>
+      <c r="C6" t="n">
+        <v/>
+      </c>
+      <c r="D6" t="n">
+        <v/>
+      </c>
+      <c r="E6" t="n">
+        <v/>
+      </c>
+      <c r="F6" t="n">
+        <v/>
+      </c>
+      <c r="G6" t="n">
+        <v/>
+      </c>
+      <c r="H6" t="n">
+        <v/>
+      </c>
+      <c r="J6" t="inlineStr">
         <is>
           <t>21-May-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
         <is>
           <t>20-May-2026</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
         <is>
           <t>19-May-2026</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="AE6" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
+      <c r="AH6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>18-May-2026</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>masterdata-fra</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="AI6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
+      </c>
+      <c r="AK6" t="n">
+        <v/>
+      </c>
+      <c r="AL6" t="n">
+        <v/>
+      </c>
+      <c r="AM6" t="n">
+        <v/>
+      </c>
+      <c r="AN6" t="n">
+        <v/>
+      </c>
+      <c r="AO6" t="n">
+        <v/>
+      </c>
+      <c r="AP6" t="n">
+        <v/>
+      </c>
+      <c r="AQ6" t="n">
+        <v/>
+      </c>
+      <c r="AR6" t="n">
+        <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" t="n">
+        <v/>
+      </c>
+      <c r="B7" t="n">
+        <v/>
+      </c>
+      <c r="C7" t="n">
+        <v/>
+      </c>
+      <c r="D7" t="n">
+        <v/>
+      </c>
+      <c r="E7" t="n">
+        <v/>
+      </c>
+      <c r="F7" t="n">
+        <v/>
+      </c>
+      <c r="G7" t="n">
+        <v/>
+      </c>
+      <c r="H7" t="n">
+        <v/>
+      </c>
+      <c r="J7" t="inlineStr">
         <is>
           <t>21-May-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>509</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>350</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>116</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>20-May-2026</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>509</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>350</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>116</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>19-May-2026</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>509</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="AE7" t="inlineStr">
         <is>
           <t>350</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="AF7" t="inlineStr">
         <is>
           <t>116</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="AG7" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>18-May-2026</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>partner</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>509</t>
-        </is>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>350</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
-      <c r="AG7" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
+      <c r="AK7" t="n">
+        <v/>
+      </c>
+      <c r="AL7" t="n">
+        <v/>
+      </c>
+      <c r="AM7" t="n">
+        <v/>
+      </c>
+      <c r="AN7" t="n">
+        <v/>
+      </c>
+      <c r="AO7" t="n">
+        <v/>
+      </c>
+      <c r="AP7" t="n">
+        <v/>
+      </c>
+      <c r="AQ7" t="n">
+        <v/>
+      </c>
+      <c r="AR7" t="n">
+        <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" t="n">
+        <v/>
+      </c>
+      <c r="B8" t="n">
+        <v/>
+      </c>
+      <c r="C8" t="n">
+        <v/>
+      </c>
+      <c r="D8" t="n">
+        <v/>
+      </c>
+      <c r="E8" t="n">
+        <v/>
+      </c>
+      <c r="F8" t="n">
+        <v/>
+      </c>
+      <c r="G8" t="n">
+        <v/>
+      </c>
+      <c r="H8" t="n">
+        <v/>
+      </c>
+      <c r="J8" t="inlineStr">
         <is>
           <t>21-May-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>20-May-2026</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>19-May-2026</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="AD8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="AE8" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="AI8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>18-May-2026</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="AD8" t="inlineStr">
-        <is>
-          <t>288</t>
-        </is>
-      </c>
-      <c r="AE8" t="inlineStr">
-        <is>
-          <t>282</t>
-        </is>
-      </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AK8" t="n">
+        <v/>
+      </c>
+      <c r="AL8" t="n">
+        <v/>
+      </c>
+      <c r="AM8" t="n">
+        <v/>
+      </c>
+      <c r="AN8" t="n">
+        <v/>
+      </c>
+      <c r="AO8" t="n">
+        <v/>
+      </c>
+      <c r="AP8" t="n">
+        <v/>
+      </c>
+      <c r="AQ8" t="n">
+        <v/>
+      </c>
+      <c r="AR8" t="n">
+        <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" t="n">
+        <v/>
+      </c>
+      <c r="B9" t="n">
+        <v/>
+      </c>
+      <c r="C9" t="n">
+        <v/>
+      </c>
+      <c r="D9" t="n">
+        <v/>
+      </c>
+      <c r="E9" t="n">
+        <v/>
+      </c>
+      <c r="F9" t="n">
+        <v/>
+      </c>
+      <c r="G9" t="n">
+        <v/>
+      </c>
+      <c r="H9" t="n">
+        <v/>
+      </c>
+      <c r="J9" t="inlineStr">
         <is>
           <t>21-May-2026</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>1141</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
         <is>
           <t>20-May-2026</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
         <is>
           <t>19-May-2026</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="AC9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="AD9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="AE9" t="inlineStr">
         <is>
           <t>1139</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>18-May-2026</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>resident</t>
-        </is>
-      </c>
-      <c r="AD9" t="inlineStr">
-        <is>
-          <t>1142</t>
-        </is>
-      </c>
-      <c r="AE9" t="inlineStr">
-        <is>
-          <t>1139</t>
-        </is>
-      </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG9" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AH9" t="inlineStr">
         <is>
           <t>0</t>
@@ -2144,159 +2265,167 @@
         <is>
           <t>0</t>
         </is>
+      </c>
+      <c r="AK9" t="n">
+        <v/>
+      </c>
+      <c r="AL9" t="n">
+        <v/>
+      </c>
+      <c r="AM9" t="n">
+        <v/>
+      </c>
+      <c r="AN9" t="n">
+        <v/>
+      </c>
+      <c r="AO9" t="n">
+        <v/>
+      </c>
+      <c r="AP9" t="n">
+        <v/>
+      </c>
+      <c r="AQ9" t="n">
+        <v/>
+      </c>
+      <c r="AR9" t="n">
+        <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" t="n">
+        <v/>
+      </c>
+      <c r="B10" t="n">
+        <v/>
+      </c>
+      <c r="C10" t="n">
+        <v/>
+      </c>
+      <c r="D10" t="n">
+        <v/>
+      </c>
+      <c r="E10" t="n">
+        <v/>
+      </c>
+      <c r="F10" t="n">
+        <v/>
+      </c>
+      <c r="G10" t="n">
+        <v/>
+      </c>
+      <c r="H10" t="n">
+        <v/>
+      </c>
+      <c r="J10" t="inlineStr">
         <is>
           <t>21-May-2026</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
         <is>
           <t>20-May-2026</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>201</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
         <is>
           <t>19-May-2026</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="AC10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="AD10" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="AE10" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>18-May-2026</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>dsl</t>
-        </is>
-      </c>
-      <c r="AD10" t="inlineStr">
-        <is>
-          <t>230</t>
-        </is>
-      </c>
-      <c r="AE10" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AH10" t="inlineStr">
         <is>
           <t>0</t>
@@ -2306,6 +2435,30 @@
         <is>
           <t>0</t>
         </is>
+      </c>
+      <c r="AK10" t="n">
+        <v/>
+      </c>
+      <c r="AL10" t="n">
+        <v/>
+      </c>
+      <c r="AM10" t="n">
+        <v/>
+      </c>
+      <c r="AN10" t="n">
+        <v/>
+      </c>
+      <c r="AO10" t="n">
+        <v/>
+      </c>
+      <c r="AP10" t="n">
+        <v/>
+      </c>
+      <c r="AQ10" t="n">
+        <v/>
+      </c>
+      <c r="AR10" t="n">
+        <v/>
       </c>
     </row>
   </sheetData>
